--- a/data/exports/validation_study/packets/week-1/packet-1.xlsx
+++ b/data/exports/validation_study/packets/week-1/packet-1.xlsx
@@ -544,7 +544,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2. 'techniques' sheet - the 18 attacks, mechanisms and defenses we recorded from your papers.</t>
+          <t>2. 'techniques' sheet - the 16 attacks, mechanisms and defenses we recorded from your papers.</t>
         </is>
       </c>
     </row>
@@ -2284,11 +2284,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Memory-R2 - Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents.pdf</t>
+          <t>data/papers/ASIDE - Architectural Separation of Instructions and Data in Language Models.pdf</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>data/papers/From Memory to Skills - Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents.pdf</t>
+          <t>data/papers/Language Models Need Sleep - Learning to Self-Modify and Consolidate Memories.pdf</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -2344,15 +2344,15 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICML</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Activation-aware Probe-Query - Effective Key-Value Retrieval for Long-Context LLMs Inference.pdf</t>
+          <t>data/papers/Taming Knowledge Conflicts in Language Models.pdf</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>SoutheastCon</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence.pdf</t>
+          <t>data/papers/Evaluating Prompt Injection Defenses for Educational LLM Tutors - Security-Usability-Latency Trade-offs.pdf</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -2400,15 +2400,15 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026 6th International Conference on Artificial Intelligence and Industrial Technology Applications (AIITA)</t>
+          <t>Journal of Cybersecurity and Privacy</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>data/papers/A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems.pdf</t>
+          <t>data/papers/Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning.pdf</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -2420,19 +2420,23 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems.pdf</t>
+          <t>data/papers/PlugMem - A Task-Agnostic Plugin Memory Module for LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -2444,15 +2448,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>AIP Conference Proceedings</t>
+          <t>CAIS</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -2460,7 +2464,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Signed-Prompt - A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications.pdf</t>
+          <t>data/papers/Improving Coherence and Persistence in Agentic AI for System Optimization.pdf</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -2472,7 +2476,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2480,7 +2484,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -2488,7 +2492,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>data/papers/ClinQueryAgent - A Conversational Agent for Population Health Management.pdf</t>
+          <t>data/papers/Overcoming the Retrieval Barrier - Indirect Prompt Injection in the Wild for LLM Systems.pdf</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -2500,11 +2504,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -2512,11 +2516,11 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Prompt Overflow - What the Guardrail Inspects Is Not What the Model Infers.pdf</t>
+          <t>data/papers/Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations.pdf</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -2528,23 +2532,23 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Computer fraud &amp; security</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Securing the Boundary - Trust Context Separation in Privileged AI Agent Systems.pdf</t>
+          <t>data/papers/When Your Reviewer is an LLM - Biases, Divergence, and Prompt Injection Risks in Peer Review.pdf</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -2556,11 +2560,11 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2572,7 +2576,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations.pdf</t>
+          <t>data/papers/Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching.pdf</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -2584,15 +2588,15 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>International Conference on Evaluation of Novel Approaches to Software Engineering</t>
+          <t>ACM CCS</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -2600,7 +2604,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>data/papers/A Trace-Based Assurance Framework for Agentic AI Orchestration - Contracts, Testing, and Governance.pdf</t>
+          <t>data/papers/SecAlign - Defending Against Prompt Injection with Preference Optimization.pdf</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
@@ -2612,15 +2616,15 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2024 IEEE Security and Privacy Workshops (SPW)</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -2628,7 +2632,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications.pdf</t>
+          <t>data/papers/Owner-Harm - A Missing Threat Model for AI Agent Safety.pdf</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
@@ -2640,11 +2644,11 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -2656,7 +2660,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>data/papers/ToolSelf - Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation.pdf</t>
+          <t>data/papers/ChatInject - Abusing Chat Templates for Prompt Injection in LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
@@ -2668,15 +2672,15 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>NDSS</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -2684,7 +2688,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>data/papers/ADEMA - A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents.pdf</t>
+          <t>data/papers/Prompt Injection Attack to Tool Selection in LLM Agents.pdf</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2712,7 +2716,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>data/papers/MemEvoBench - Benchmarking Memory MisEvolution in LLM Agents.pdf</t>
+          <t>data/papers/From Prompt Injection to Persistent Control - Defending Agentic Harness Against Trojan Backdoors.pdf</t>
         </is>
       </c>
       <c r="G17" s="5" t="n"/>
@@ -2796,7 +2800,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2819,7 +2823,7 @@
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2833,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2844,7 +2848,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -2852,7 +2856,7 @@
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2866,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2885,7 +2889,7 @@
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2899,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2918,7 +2922,7 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2932,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2943,7 +2947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F6" s="5" t="n"/>
@@ -2951,7 +2955,7 @@
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2965,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
@@ -2984,7 +2988,7 @@
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2998,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3009,7 +3013,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F8" s="5" t="n"/>
@@ -3017,7 +3021,7 @@
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3031,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3050,7 +3054,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3064,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3083,7 +3087,7 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3097,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3108,7 +3112,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F11" s="5" t="n"/>
@@ -3116,7 +3120,7 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3130,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3149,7 +3153,7 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3163,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3174,7 +3178,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>The code is stated to be released via a linked repository: the corresponding-author footnote states 'The code is available for access via this repository,' though the specific URL text was not captured in the extracted plain text (likely a hyperlink not rendered by pdftotext).</t>
+          <t>Y - code at https://github.com/egozverev/aside</t>
         </is>
       </c>
       <c r="F13" s="5" t="n"/>
@@ -3182,7 +3186,7 @@
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3196,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3207,7 +3211,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Qwen2.5-7B-Instruct is used as the shared backbone for both the fact extractor and memory manager (jointly trained via role-specific prompts) and as the primary answer agent for fair comparison against baselines; Qwen2.5-3B is used in scaling/ablation experiments; GPT-OSS-120B is swapped in as an alternative frozen answer agent in a variant ('Memory-R2 (GPT-OSS)') to test whether a smaller trained model can rival a much larger untrained one; GPT-4o is used to generate distractor/negative answer options during data construction, and gpt-4o-mini serves as the LLM-as-a-Judge for the J (judge accuracy) metric.</t>
+          <t>Llama 3.1; Llama 2; Qwen 3; Qwen 2.5; Mistral models (multiple sizes each, per model family)</t>
         </is>
       </c>
       <c r="F14" s="5" t="n"/>
@@ -3215,7 +3219,7 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3229,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3240,7 +3244,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Primary benchmark is LoCoMo (long-horizon conversational memory QA), with results broken down by question category (Multi-hop, Open Domain, Single Hop, Temporal). Out-of-distribution generalization is additionally tested on LongMemEval (LongMemEval-oracle and LongMemEval-s variants), MSC-Self-Instruct, and MemBench, evaluated zero-shot after training only on LoCoMo.</t>
+          <t>SEP dataset (9,160 instruction/input pairs, Zverev et al. 2025) for separation scoring; AlpacaEval 1.0 for utility; TensorTrust, Gandalf, Purple, RuLES for direct-attack ASR; BIPIA-text, BIPIA-code, StruQ-ID, StruQ-OOD for indirect-attack ASR.</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -3248,7 +3252,7 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3262,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3273,7 +3277,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>On LoCoMo (Table 1), under a backbone-controlled comparison (Qwen2.5-7B-Instruct for all methods), Memory-R2 achieves the best overall performance among training-free and trained baselines: overall F1 50.60, BLEU-1 44.01, and Judge score 80.99, versus the closest RL baseline Memory-R1's F1 43.14 / B1 36.44 / J 61.51, and versus training-free methods like MemoryOS (F1 34.64) and Mem0 (F1 30.61). A GPT-OSS-120B answer-agent variant of Memory-R2 (Memory-R2 (OSS)) achieves even higher overall F1 (49.67) and J (87.10) using a much larger frozen model, but the paper highlights that the RL-finetuned 7B Memory-R2 still surpasses this 120B variant on F1 and B1, showing 'targeted training outweighs raw model scale.' On out-of-distribution generalization -- despite being trained on only two LoCoMo conversations -- Memory-R2 shows strong zero-shot transfer: on LongMemEval-oracle, F1 improves from 27.88 (baseline) to 50.60, with especially pronounced gains for the smaller Qwen2.5-3B backbone. The method also improves inference efficiency: Memory-R2 reduces total completion tokens and latency for both Qwen2.5-3B and Qwen2.5-7B relative to baselines, with the 3B efficiency gain driven mainly by shorter generations and the 7B gain additionally driven by more stable/consistent generation behavior. Curriculum-stage analysis (Figure 10) shows LoGo-GRPO consistently outperforms standard GRPO across all four question categories and all three curriculum stages (8, 16, 32 sessions), with the largest and still-growing advantage on long-horizon question types (Multi-hop, Temporal) as the session range increases.</t>
+          <t>Instruction-tuning with ASIDE's fixed 90-degree data-token rotation lowers indirect-injection ASR versus a Vanilla delimiter-based baseline: BIPIA-text 14.7%-&gt;4.9%, BIPIA-code 15.3%-&gt;8.8%, StruQ-ID 45.6%-&gt;28.1%, StruQ-OOD 45%-&gt;36% (averages across models), while a competing architectural method (ISE) is within 0.1-2% of Vanilla on the same benchmarks and gives essentially no improvement. Gains come with matched utility and without any dedicated safety training or adversarial examples.</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
@@ -3281,7 +3285,7 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3295,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3306,7 +3310,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Training-free memory baselines: RAG, A-MEM, Mem0, MemoryOS. Trained/RL baselines: MEM1, MemAgent, and Memory-R1 (the most closely related prior RL-based memory-agent training method, against which Memory-R2 is directly framed as an improvement). All baselines are evaluated with Qwen2.5-7B-Instruct as the base model for fair, backbone-controlled comparison, with numbers for some prior methods (marked with a dagger) taken as reported in the original Memory-R1 paper.</t>
+          <t>Vanilla (standard single-embedding architecture) and ISE (Wu et al. 2024, learnable role-offset embeddings).</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
@@ -3314,7 +3318,7 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3328,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3339,7 +3343,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a reinforcement-learning training-methodology paper for memory-augmented LLM agents, not a security paper; the incidental failure mode of interest is unfair/biased credit assignment during RL training -- because different rollouts write, update, or delete different memory content, they no longer share the same intermediate memory state, violating the group-relative comparison assumption behind methods like GRPO and causing noisy or biased training signals for memory-construction operations (a training-dynamics failure mode, not an adversarial one).</t>
+          <t>Single-turn (instruction, injection) pairs where token functional role (instruction vs. data) is known at input time by system design (e.g., an email client always labels email contents as data); no adaptive/optimization-based attacker is evaluated, and the setting excludes general chatbots where role must be inferred at runtime.</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -3347,7 +3351,7 @@
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3361,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3372,7 +3376,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The paper contains an explicit appendix section 'D Limitations and Future Work': 'Our study focuses on long-horizon text-only multi-session dialogue, where memory is constructed from conversational turns and evaluated through downstream QA. Extending the same training paradigm to multimodal settings, such as image-grounded dialogue, video memory, or embodied interaction, remains unexplored. While the proposed credit-assignment framework is in principle agnostic to the modality of memory content, its practical effectiveness in richer environments still requires further investigation.' The same section also discusses potential positive and negative societal impacts, noting the work could improve reliability and consistency of memory systems for applications like personalized assistants and long-term educational support, while reducing failure modes caused by forgetting or inconsistent recall.</t>
+          <t>Authors state the method is purposefully limited to the single-turn setting where instruction/data roles are well-defined at input time; extending to multi-turn interactions and to role transforms other than rotations, and to multi-tier instruction hierarchies, is left to future work.</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -3380,7 +3384,7 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3394,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3405,7 +3409,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2 is a reinforcement learning training framework for long-horizon, memory-augmented LLM agents operating over multi-session conversational interactions, addressing a core difficulty in applying group-relative RL methods (like GRPO) to memory-augmented settings: because an agent's memory operations (writes, updates, deletions) in one session become part of the environment state inherited by later sessions, different training rollouts that modify memory differently no longer share the same intermediate memory state, yet standard GRPO still normalizes their rewards within a single comparison group -- producing unfair, biased credit assignment for memory-construction decisions, compounded by the difficulty of attributing a downstream QA failure to the current session's memory operation versus corrupted memory inherited from earlier sessions versus later overwrites. The paper's core algorithmic contribution, LoGo-GRPO (Local-Global GRPO), resolves this by combining two objectives: a global objective that preserves standard end-to-end trajectory-level reward optimization across the full long-horizon episode, and local rerollouts that specifically compare different candidate memory-operation outcomes generated from the exact same shared intermediate memory state, yielding a fair, apples-to-apples group comparison and cleaner supervision signal for memory construction specifically, while the global objective still ensures the overall long-horizon policy remains coherently optimized. Beyond this credit-assignment mechanism, Memory-R2 jointly trains memory formation (fact extraction from conversational turns) and memory evolution (updating/managing the memory store over time) using a shared-parameter co-learning design, where a single LLM backbone is instantiated as both a fact extractor and a memory manager via distinct role-specific prompts rather than separate model copies, reducing parameter overhead while allowing both roles to benefit from shared representation learning. To stabilize multi-step RL training over increasingly long memory horizons, the framework adopts a progressive curriculum that gradually increases the training horizon from 8 to 16 to 32 sessions, allowing the policy to first master shorter-horizon credit assignment before tackling the harder long-horizon regime.</t>
+          <t>Proposes ASIDE, a parameter-free architectural change that applies a fixed orthogonal rotation to the token embeddings of data tokens (while leaving instruction-token embeddings unchanged), giving the model an explicit, learnable-free signal of each token's functional role from the first layer onward. Requires only a modified forward pass plus standard instruction-tuning, with no retraining from scratch and no additional parameters. Evaluated across Llama 3.1/2, Qwen 3/2.5 and Mistral against a Vanilla baseline and the ISE architecture, showing markedly higher instruction-data separation (SEP score) at matched utility and consistently lower attack success rate on both direct (TensorTrust, Gandalf, Purple, RuLES) and indirect (BIPIA, StruQ) prompt-injection benchmarks, without any dedicated safety fine-tuning.</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -3413,7 +3417,7 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3427,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3446,7 +3450,7 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3460,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3479,7 +3483,7 @@
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3493,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3512,7 +3516,7 @@
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3526,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3545,7 +3549,7 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3559,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3578,7 +3582,7 @@
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3592,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3603,7 +3607,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F26" s="5" t="n"/>
@@ -3611,7 +3615,7 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3625,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3644,7 +3648,7 @@
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3658,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3669,7 +3673,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -3677,7 +3681,7 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3691,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3710,7 +3714,7 @@
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3724,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3743,7 +3747,7 @@
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3757,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3776,7 +3780,7 @@
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3790,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3801,7 +3805,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Code released at https://github.com/MemTensor/MemOS.</t>
+          <t>No code/artifact release found in the extracted text. No GitHub, Hugging Face, or project-page URL is mentioned; the paper appears to be a research/theory paper from Google researchers (correspondence emails @google.com) without an accompanying public code release stated in the main text.</t>
         </is>
       </c>
       <c r="F32" s="5" t="n"/>
@@ -3809,7 +3813,7 @@
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3823,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3834,7 +3838,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>GPT-5.2 is used as the agent backbone across all methods; GPT-4o is used as the auxiliary prompted operator for reflection scoring, L2 policy induction, and L3 environmental cognition abstraction, and separately as the LLM-judge for LoCoMo evaluation. All methods are implemented on the OpenClaw v2026.5.7 agent runtime with identical tool access, interaction budgets, and task order to ensure fair comparison.</t>
+          <t>Llama-3B, Llama3-8B, and Llama-3.2-1B as backbones for the Hope/Sleep architecture; multiple Qwen3 variants (Qwen3-1.7B, Qwen3-8B) for mathematical reasoning experiments; GPT-4 and GPT-4o-mini as large-model baselines on BABILong; and comparison against prior architectures Hope (Behrouz et al. 2025, without the new consolidation mechanism), RMT, ARMT, and Titans as state-of-the-art small long-context models.</t>
         </is>
       </c>
       <c r="F33" s="5" t="n"/>
@@ -3842,7 +3846,7 @@
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3856,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3867,7 +3871,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>EvoAgentBench, a multi-domain long-horizon agent self-evolution benchmark spanning five domains: Information Retrieval (based on BrowseComp-Plus), Mathematical Reasoning (OmniMath), Software Engineering (SWE-Bench), Code Implementation (LiveCodeBench), and Knowledge Work (GDPVal); plus LoCoMo, a long-term conversational memory benchmark testing single-hop, multi-hop, temporal-reasoning, and open-domain question answering, used to specifically stress memory consistency rather than tool-use skill execution.</t>
+          <t>Class-incremental learning: CLINC, Banking, DBpedia. Long-context QA/retrieval: LongHealth, QASPER, MK-NIAH. Continual translation of unseen languages: MTOB (Manchu) and Kalamang datasets (following Behrouz et al. 2025). Long-context scaling: BABILong (up to 10M tokens). Mathematical reasoning: AIME-24, AIME-25, HMMT-25 (average@16 scoring). Knowledge incorporation: SQuAD (single-passage n=1 and continued-pretraining n=200 settings, evaluated on 974 questions). Few-shot abstract reasoning: ARC (11 training tasks, 8 held-out evaluation tasks, following Akyurek et al. 2024a and Zweiger et al. 2025 protocols).</t>
         </is>
       </c>
       <c r="F34" s="5" t="n"/>
@@ -3875,7 +3879,7 @@
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3889,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3900,7 +3904,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MSCE achieves the best or tied-best Pass@1 across all five EvoAgentBench domains (Table 1), improving over the strongest non-MSCE baseline by 4.61 points on Information Retrieval (26.15% vs. 21.54% for EverOS), 4.00 on Math (47.00% vs. 43.00%), 15.39 on Software Engineering (53.85% vs. 38.46%), and 5.17 on Knowledge Work (53.45% vs. 48.28%), while tying the best baseline (EvoSkill) on Code at 61.54% Pass@1 while reducing cost from 3.9 to 2.0 turns. These gains are generally not attributable to higher inference budget: MSCE reduces cost relative to the strongest non-MSCE baseline on IR, Math, Code, and KW (with especially large reductions on Math and Code), the sole exception being SE, where cost increases from 37.3 to 40.8 turns alongside the 15.39-point accuracy gain, attributed to the additional repository navigation, editing, and testing required for successful software-engineering solutions. On LoCoMo (Table 2), MSCE achieves the best overall LLM-judge score (61.23) and F1 (49.89), outperforming the strongest baseline SkillFlow-Evolve by 2.01 and 1.18 points respectively, and achieves the highest scores on single-hop, multi-hop, and temporal-reasoning question types (though EverOS scores best on open-domain questions among non-vanilla methods). Ablations (Table 3) show each component contributes: removing the L1/L2/L3 hierarchy ('Flat Memory') causes the largest degradation (e.g., IR Pass@1 drops from 26.15% to 10.77%), and removing L3 environmental cognition, value calibration, reflection weighting, or skill crystallization individually each reduces Pass@1 and increases cost across domains, with skill crystallization removal causing the largest degradation among the individual-component ablations. Cross-domain transfer experiments show that initializing an agent with memory and skills evolved on a source domain improves Pass@1 across all six evaluated domain-transfer pairs relative to evolving from scratch on the target domain, demonstrating positive cross-domain transferability and lifelong-evolution capability.</t>
+          <t>Across five task families, the proposed Sleep paradigm (memory consolidation + Dreaming self-improvement) consistently outperforms baselines. On class-incremental learning, Hope with memory consolidation outperforms ICL, Elastic Weight Consolidation (EWC), and In-context Continual Learning with an External Learner (InCA). On long-context QA/retrieval (LongHealth, QASPER, MK-NIAH), Hope consistently beats ICL, DuoAttention, and Cartridges, and increasing consolidation stages monotonically improves performance. On continual cross-lingual learning (MTOB/Kalamang), standard ICL and even Cartridges/SFT baselines suffer catastrophic forgetting when learning two unseen languages sequentially (performing worse than ICL in at least one language), whereas Hope-3 (three consolidation stages) nearly recovers single-language performance despite sequential exposure. On BABILong, Hope achieves 'almost perfect score' scaling to 10M tokens, outperforming GPT-4, GPT-4o-mini, Llama-8B+RAG, RMT, ARMT, and Titans. On mathematical reasoning (Table 1/2), Sleep outperforms Base/Instruct, SFT, GRPO, and OPSD baselines across both Qwen3-1.7B and Qwen3-8B, e.g., on Qwen3-8B: Sleep achieves 79.2/69.0/46.1 (AIME-24/AIME-25/HMMT-25) versus OPSD's 76.6/67.4/45.1 and GRPO's 76.4/68.1/44.9. On knowledge incorporation (SQuAD, Table 3), the four-level Sleep (Transformer) variant achieves 48.9 (single-passage) / 46.2 (CPT n=200) accuracy, outperforming SEAL (46.7/43.2), a no-Dreaming fine-tuned model (33.4/32.0), and the base model (31.9/31.9); an ablation shows removing the Dreaming component collapses CPT performance to 36.2, confirming its necessity. On few-shot ARC reasoning, Sleep achieves an 80% success rate versus SEAL's 72.5%, TTT's 10%, and ICL's 0%.</t>
         </is>
       </c>
       <c r="F35" s="5" t="n"/>
@@ -3908,7 +3912,7 @@
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3922,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3933,7 +3937,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Three categories of baselines under identical backbone/runtime/tool-access conditions: (1) memory-based agents that reuse trajectories/cases without explicit skill crystallization -- EverOS, Memento, MemSkill; (2) trajectory-to-skill agents that synthesize or refine skills from interaction trajectories -- EvoSkill, OpenSpace, and SkillFlow-Evolve (a patch-based skill-evolution baseline adapted from SkillFlow); and (3) a Vanilla Agent using the same base model and tools but with no persisted long-term memory or skill construction.</t>
+          <t>In-Context Learning (ICL), Elastic Weight Consolidation (EWC), In-context Continual Learning with an External Learner (InCA), the prior Hope architecture without explicit distillation, DuoAttention, Cartridges, Supervised Fine-Tuning (SFT), GRPO, OPSD (On-Policy Self-Distillation, an ablated/prior variant), GPT-4, GPT-4o-mini, Llama-8B+RAG, RMT, ARMT, Titans, SEAL (Zweiger et al. 2025), and Test-Time Training (TTT).</t>
         </is>
       </c>
       <c r="F36" s="5" t="n"/>
@@ -3941,7 +3945,7 @@
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3955,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3966,7 +3970,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial (this is a memory/skill-architecture capability paper for long-horizon LLM agents, not a security paper). The incidental failure mode of interest is that existing agent memory systems retrieve prior interaction traces as passive context that the agent must re-reason over each time, rather than converting repeated experience into executable, verified procedural knowledge (skills) -- leading to redundant exploration (e.g., an agent repeatedly re-listing directories to locate the same configuration files) and excessive token consumption across long-horizon, multi-session tasks.</t>
+          <t>N/A - non-adversarial. This is a continual-learning/self-improvement architecture paper, not a security paper; the incidental failure mode of interest is catastrophic forgetting -- the well-known phenomenon where a model's proficiency on original tasks degrades sharply as it learns new information via iterative parameter updates or fine-tuning, along with the related problem of 'knowledge obsolescence,' where static post-training models cannot incorporate new facts, events, or evolving information beyond a fixed knowledge cutoff.</t>
         </is>
       </c>
       <c r="F37" s="5" t="n"/>
@@ -3974,7 +3978,7 @@
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3988,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3999,7 +4003,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations' section identifying four points: (1) value estimates, policy gains, and reliability scores used for governance are heuristic signals rather than causal credit-assignment estimates -- they support ranking, filtering, and revision of memory objects but do not guarantee a promoted policy would cause success under counterfactual intervention; (2) several update operators (reflection scoring, policy induction, environmental cognition abstraction, reward quantification, skill drafting) rely on prompted LLMs which, despite being evidence-constrained and verified before insertion, may still be noisy or sensitive to model/prompt choices and introduce additional latency and cost; (3) the implementation depends on a particular agent runtime (OpenClaw), tool interface, and backbone configuration, so absolute results may vary under different models or environments; (4) although truncation, deduplication, and rule-based redaction are applied to stored traces/evidence/policies/skills to reduce storage and privacy risk, these controls do not eliminate the possibility of retaining sensitive user information, environment-specific secrets, or unsafe procedural knowledge, and practical deployments should include stronger privacy filters, access control, and safety checks for generated skills.</t>
+          <t>The paper does not contain an explicit 'Limitations' section (searched; only a brief two-paragraph Conclusion is present at the end of the main text). The closest analog is a subsection titled 'Limitations of OPSD and Motivation for the Sleep Paradigm' (around line 1213 in the appendix), which discusses limitations of a related prior on-policy self-distillation (OPSD) approach -- noting performance drops of up to 40% across models like Qwen3-8B, DeepSeek-Distill-Qwen-7B, and Olmo3-7B-Instruct -- as motivation for why the Sleep paradigm's two-stage design (memory consolidation plus Dreaming) is needed, rather than presenting explicit limitations of the Sleep method itself. The main Conclusion is brief and does not discuss shortcomings, caveats, computational cost, or scope restrictions of the proposed approach.</t>
         </is>
       </c>
       <c r="F38" s="5" t="n"/>
@@ -4007,7 +4011,7 @@
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4021,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4032,7 +4036,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MSCE (Memory-Skill Co-Evolution) is a training-free framework for long-horizon LLM agents that addresses the gap between passive memory retrieval (where an agent must re-reason over retrieved raw traces every time) and active, executable skill reuse. Rather than directly distilling skills from noisy raw trajectories (which risks overfitting to environment-specific artifacts and blind exploration due to sparse, delayed terminal feedback), MSCE organizes agent experience into a three-level governed memory hierarchy: L1 trace memory stores grounded step-level evidence; L2 policy memory induces recurring procedural patterns aggregated across multiple episodes/traces; and L3 environmental cognition memory abstracts declarative knowledge about environmental structure and constraints. On top of this governed substrate, MSCE selectively 'crystallizes' L2 policies into callable skills only when they retain supporting evidence, exhibit positive estimated gain, and remain stable/consistent in their trigger, procedure, and applicability boundary -- the resulting skills preserve evidence anchors, verification rules, applicability boundaries, decision guidance, and reliability estimates, supporting a governed lifecycle of promotion and later revision rather than one-shot brittle distillation. The value signal underlying this governance comes from a novel 'reflection-weighted value backfilling' mechanism, which propagates sparse terminal task feedback backward through dense local self-reflections generated at each step, producing evidence-calibrated trace values used uniformly for retrieval, L2 policy induction, L3 environmental cognition abstraction, skill promotion decisions, and later skill revision. Evaluated with a GPT-5.2 agent backbone (GPT-4o used for auxiliary reflection/induction/abstraction operators) on the OpenClaw runtime across EvoAgentBench's five heterogeneous long-horizon domains and the LoCoMo long-dialogue memory benchmark, MSCE outperforms memory-based, trajectory-to-skill, and vanilla-agent baselines in both effectiveness (Pass@1, LLM-judge score, F1) and, in most domains, inference efficiency, with ablations confirming each hierarchy level and mechanism (L3 environmental cognition, value calibration, reflection weighting, skill crystallization) contributes independently to performance, and cross-domain transfer experiments demonstrating that memory/skills evolved on one domain positively transfer to accelerate self-evolution on a different target domain.</t>
+          <t>This paper introduces a 'Sleep' paradigm for LLMs, inspired directly by the two-stage memory consolidation process observed in human sleep (online consolidation during wakefulness plus offline/systems consolidation during sleep), designed to address the inability of current LLMs to continually learn and transfer fragile short-term in-context knowledge into stable long-term parametric knowledge without catastrophic forgetting. The Sleep paradigm consists of two components. First, Memory Consolidation performs an upward distillation process called Knowledge Seeding, distilling the memories/knowledge of a smaller 'self' model into a larger network with more capacity while preserving that knowledge; the paper's proof-of-concept implementation is a Generalized Distillation process combining on-policy distillation with RL-based imitation learning. Second, Dreaming is a self-improvement phase in which the model uses reinforcement learning to generate its own curriculum of synthetic training data ('dreams') to rehearse newly acquired knowledge and refine existing capabilities without human supervision; dream selection uses a gradient-based importance score (the gradient of the SFT loss on each candidate dream), and the process follows a SEAL-style ReSTEM optimization loop that only reinforces dreams whose resulting fine-tuned model shows measurable performance improvement. The architecture builds on and extends the authors' prior Nested Learning/Hope framework, which already implemented online (in-context) consolidation via a continuum-memory system with components updated at different frequencies, by adding this offline, sleep-inspired consolidation and self-generated rehearsal mechanism that does not depend on active retrieval or context-only updates. The paper validates this design across five distinct evaluation settings -- class-incremental learning, long-context question answering/retrieval, continual cross-lingual in-context learning, mathematical reasoning, and knowledge incorporation/few-shot abstract reasoning -- consistently finding that the full two-stage Sleep process outperforms both simpler in-context learning baselines (which forget rapidly under continual settings) and standard fine-tuning/RL baselines (SFT, GRPO, OPSD) that lack the explicit consolidation-plus-self-generated-rehearsal structure.</t>
         </is>
       </c>
       <c r="F39" s="5" t="n"/>
@@ -4040,7 +4044,7 @@
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4054,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4073,7 +4077,7 @@
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4087,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4106,7 +4110,7 @@
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4120,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4139,7 +4143,7 @@
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4153,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4164,7 +4168,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>both</t>
         </is>
       </c>
       <c r="F43" s="5" t="n"/>
@@ -4172,7 +4176,7 @@
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4186,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4205,7 +4209,7 @@
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4219,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4230,7 +4234,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F45" s="5" t="n"/>
@@ -4238,7 +4242,7 @@
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4271,7 +4275,7 @@
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4285,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4296,7 +4300,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F47" s="5" t="n"/>
@@ -4304,7 +4308,7 @@
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4318,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4337,7 +4341,7 @@
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4351,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4370,7 +4374,7 @@
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4384,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4395,7 +4399,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F50" s="5" t="n"/>
@@ -4403,7 +4407,7 @@
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4417,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4428,7 +4432,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>No code/artifact release URL or GitHub link was found anywhere in the paper text (main body, appendices, or Ethics Statement), despite thorough Grep searching for 'github', 'open-source', and 'code available' patterns. The Ethics Statement notes only that 'all datasets and models utilized are publicly available,' referring to third-party resources rather than releasing the authors' own implementation.</t>
+          <t>Code is publicly released at https://github.com/GaotangLi/JUICE. A new curated dataset, ParaConflict, is also released at https://huggingface.co/datasets/gaotang/ParaConfilct, covering six factual domains under substitution- and coherent-conflict conditions.</t>
         </is>
       </c>
       <c r="F51" s="5" t="n"/>
@@ -4436,7 +4440,7 @@
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4450,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4461,7 +4465,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>LLaMA3-8B-Instruct (AI@Meta, 2024) as the primary base model reported in the main text (with maximum input length 8K), and Qwen2.5-7B-Instruct (maximum input length 32K) as a secondary base model used in an appendix comparison (Figure 4) to test cross-model generalization; ActQKV is applied training-free on top of both.</t>
+          <t>Six open-source base language models: Gemma-2b, Llama2-7B, Llama3-8B, Phi2-2.7b, StableLM2-1.6b, and Olmo-7b. Primary mechanistic analysis (Section 3) is conducted mainly on Gemma-2b, while the proposed intervention method is evaluated across all six backbones.</t>
         </is>
       </c>
       <c r="F52" s="5" t="n"/>
@@ -4469,7 +4473,7 @@
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4483,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4494,7 +4498,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Long-Bench (Bai et al., 2023), using 21 tasks spanning single-doc QA, multi-doc QA, summarization, few-shot learning, retrieval, and code, with average sequence length ~31K tokens (95th percentile 32K), and Infinite-Bench / ∞-Bench (Zhang et al., 2024), with average sequence length ~122K tokens (up to 214K), used to test near-unbounded-context factual retrieval ability.</t>
+          <t>Eleven datasets total: six newly curated 'Parametric' factual-association datasets spanning diverse domains (World Capital, Athlete Sport, Book Author, Official Language, Company Headquarter, Company Founder), each tested under three conflict levels (clean, sentence-level substitution conflict, and paragraph-level coherent/counterfactual conflict, the latter generated with GPT-4-level persuasive elaboration), released collectively as ParaConflict; and five 'Contextual' datasets for the context-reliance setting, including the established context-oriented knowledge-conflict benchmarks Memo-Trap and NQ-Swap plus others spanning open-domain QA and sentence completion. Evaluation uses exact-match accuracy against either the factually correct parametric answer or the contextual answer, depending on the setting.</t>
         </is>
       </c>
       <c r="F53" s="5" t="n"/>
@@ -4502,7 +4506,7 @@
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4516,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4527,7 +4531,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>On Long-Bench (Table 1, LLaMA3-8B-Instruct), ActQKV achieves an average score of 49.40 using only a 2K KV-pair budget, surpassing the full-context baseline (44.73, using the full 31K-token context) by 4.67 points, and outperforming the strongest prior KV-retrieval baselines TSLLM (46.20, 2K budget) and EMLLM (46.67, 4K budget) by +5.8% and +4.6% respectively while using an equal or smaller budget; it also strongly outperforms static KV-selection methods Infinite (36.18) and Stream (35.76) at the same 2K budget. On Infinite-Bench (Table 2, ~122K-token average, up to 214K), ActQKV achieves the best average score of 58.43 with a 2K budget, versus InfLLM (48.68, 2K), QLLM (49.43, 2K), TSLLM (56.47, 2.5K), and EMLLM (49.00, 8K budget) -- notably outperforming EMLLM's 8K-budget result while using a 4x smaller KV cache. An ablation study (Table 3) isolating the two proposed components shows that the Activation-aware Probe-Query (APQ) alone raises the score from a TSLLM baseline of 46.7 to 48.8 (with the largest single-task gain in retrieval tasks, 87.0 to 98.0), and adding the Dynamic Cut-off Mechanism (DCM) further raises it to 49.2, with the full ActQKV method reaching 49.4.</t>
+          <t>JUICE sets new state-of-the-art performance across both intervention settings (enhancing parametric recall and enhancing contextual reliance) and all 11 datasets/6 architectures, consistently and significantly outperforming baselines including a Prompt-only baseline (instructing the model to rely solely on internal memory) and PH3 (a prior head-intervention method, evaluated in two variants: PH3-large with a 200-sample development set, and PH3-small using the same minimal head-identification set as JUICE). Under substitution-conflict and coherent-conflict conditions with Gemma-2b (Fig. 2), JUICE maintained consistently high performance where the unmodified 'Original' model and PH3 both degraded substantially (PH3 performance on some datasets dropped to near 0%, e.g. on certain columns in Table 3 PH3-small scored 0.0% and 0.2% while JUICE remained robust), demonstrating that a single naive intervention (deleting or scaling fixed 'context heads' or 'memory heads') is insufficient once the CP-superposition phenomenon is accounted for. On the contextual-reliance setting (Table 4), JUICE also outperformed PH3 variants on average across models including Llama2 and Llama3. The theoretical analysis (Section 5) further proved, in a simplified two-layer transformer with a constructed 'perfect solver,' that a single-pass intervention (deleting identified heads once) fails to recover the parametric answer in cases where the inductive/contextual component dominates, while JUICE's dual-run design succeeds by using activations saved from the original, unintervened run as a more reliable steering signal -- providing formal justification for why single-pass head ablation methods like PH3/JUNE underperform.</t>
         </is>
       </c>
       <c r="F54" s="5" t="n"/>
@@ -4535,7 +4539,7 @@
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4549,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4560,7 +4564,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Two categories of prior KV-cache management baselines: (a) static KV selection methods Infinite (Lin et al., 2024, global+local attention masks) and StreamingLLM/Stream (Xiao et al., 2024b, attention-sink retention); and (b) KV retrieval methods InfLLM (Xiao et al., 2024b, window-level retrieval), QLLM (Li et al., 2024b, task-description-relevant KV memory), TokenSelect/TSLLM (Hao et al., 2025, token-level importance via soft voting across heads), and EM-LLM (Fountas et al., 2025, episodic-memory-inspired segmentation with hybrid semantic+temporal retrieval), plus the full-context (no compression) LLaMA3-8B-Instruct baseline. All baseline methods, like ActQKV, are training-free.</t>
+          <t>Prompt (instructing the LM via natural-language prompting to rely solely on internal/parametric memory, without any activation intervention), PH3-large (Jin et al., prior attention-head intervention method using a full 200-sample development set for head identification), PH3-small (the same PH3 method but restricted to the same minimal head-identification dataset used by JUICE, for a fairer comparison), and JUNE (a related single-pass head-intervention baseline referenced as an ablation-only variant of the approach).</t>
         </is>
       </c>
       <c r="F55" s="5" t="n"/>
@@ -4568,7 +4572,7 @@
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4582,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4593,7 +4597,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is an inference-efficiency / KV-cache-retrieval paper for long-context LLM inference, not a security paper; the incidental failure mode of interest is imprecise long-context information retrieval -- specifically, that under a sparse and irregular attention distribution across very long contexts, naive query representations used to identify 'relevant' historical key-value pairs get distracted by massive numbers of candidate pairs and fail to recall the pairs actually needed for correct multi-hop or factual-retrieval reasoning, effectively a benign form of context dilution/retrieval failure rather than an induced or adversarial one.</t>
+          <t>N/A - non-adversarial. This is a mechanistic-interpretability and model-controllability paper studying knowledge conflicts (disagreement between an LLM's parametric/pretrained memory and its provided context), not a security paper; there is no adversary. The incidental failure mode studied is that language models can become unpredictably uncertain or inconsistent about which knowledge source (memory vs. context) to trust when the two conflict, which is especially consequential in context-heavy real-world systems like retrieval-augmented generation (RAG), LLM agents, and tool-augmented LLMs, where users may need the model to either remain faithful to parametric knowledge or prioritize contextual information depending on the application.</t>
         </is>
       </c>
       <c r="F56" s="5" t="n"/>
@@ -4601,7 +4605,7 @@
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4615,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4626,7 +4630,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>The paper contains an explicit 'Limitations' section (placed after the main text, before the Ethics Statement): 'Our method achieves promising performance to enhance the relevant KV pairs retrieval for long-context LLMs inference. And we believe that the interpretability of the retrieved KV pairs requires further exploration in future works. Unlike non-autoregressive architectures in embedding models, the auto-regressive architecture of LLMs results in the semantics of current tokens being influenced by historical KV pairs. When processing a long context all at once, this interaction makes it difficult to separate the semantics from various events because the retrieved key-value pairs mostly show historical information. This introduces challenges in interpreting the retrieval results.' In short, the authors flag interpretability of retrieved KV pairs as an open problem, rooted in the fact that autoregressive LLM semantics are entangled with historical context, making it hard to cleanly attribute retrieval decisions to distinct underlying events.</t>
+          <t>The paper has an explicit appendix section titled 'F. Limitations and Future Works' (referenced in the main-text Conclusion as well). It states the work is primarily aimed at illuminating the mechanisms underlying knowledge conflicts and demonstrating how to leverage this understanding, rather than optimizing for applications where inference efficiency is paramount; JUICE requires caching first-run activations (the 'run twice' design), which may slightly increase inference latency and memory overhead compared to a single forward pass. It also notes that real-world scenarios often involve partially irrelevant contexts, whereas this work focuses primarily on fully irrelevant/conflicting context cases, and that the parametric and contextual answers may not always be cleanly distinguishable in more abstract domains than the factual-recall settings studied here -- extending the method to these more complex, partially-relevant-context and abstract-domain settings is left as an important direction for future research.</t>
         </is>
       </c>
       <c r="F57" s="5" t="n"/>
@@ -4634,7 +4638,7 @@
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4648,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4659,7 +4663,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>ActQKV is a training-free, activation-aware method for selecting which key-value (KV) cache pairs to retain and reuse during long-context LLM inference, targeting the GPU memory and computational bottleneck caused by the quadratic cost of full attention over long sequences. The method operates in two stages. First, Activation-aware Probe-Query Construction (Sec. 4.1) addresses the pre-filling stage: rather than using a naive or uniform query representation to search the KV cache (as prior sliding-window methods like InfLLM do), ActQKV computes a token-level 'Activation Bias' for each query vector within a sliding window -- essentially the squared deviation of each query vector from the window's mean, normalized by variance -- to identify 'anchor tokens' whose representations diverge most from the window average and are therefore judged most informative. These activation biases are then used as weights to construct a single aggregated 'probe-Query' vector (Qt_probe) via a weighted sum over the window's query vectors, which is subsequently used to compute cosine similarity against cached keys and retrieve the top-k most relevant historical KV pairs for that window, replacing uniform/unweighted query aggregation with an activation-aware one. Second, the Dynamic KV Cut-off Mechanism (Sec. 4.2) addresses the decoding stage: instead of retrieving a fixed number k of KV pairs per transformer layer, the method computes an entropy-based 'information density' score per layer from the similarity distribution between the probe-Query and cached keys, and dynamically allocates a larger portion of a fixed total KV budget to layers exhibiting higher information density (indicating more potentially relevant pairs), while assigning smaller budgets to lower-density layers where truly relevant pairs are already easy to isolate. Both mechanisms are combined into a single algorithm (Algorithm 1) that can be applied on top of any pretrained LLM without additional training, and the KV cache itself can optionally be offloaded to CPU memory and transferred to GPU only when needed, reducing GPU memory pressure (reported at ~19GB VRAM in their setup) relative to retaining the full context on-device.</t>
+          <t>This paper studies knowledge conflicts in language models -- situations where a model's parametric (pretrained) memory contradicts information provided in its input context -- and challenges the prevailing assumption from prior work that distinct attention heads are exclusively responsible for promoting either 'memory' or 'context.' Through causal analysis (measuring how zeroing out or scaling specific model components changes the probability of parametric versus contextual output tokens across clean, substitution-conflict, and coherent-conflict inputs), the authors uncover a phenomenon they term 'superposition of contextual information and parametric memory' (CP superposition): the same highly influential attention heads can simultaneously and inconsistently contribute to both parametric and contextual knowledge depending on the input, undermining prior single-pass head-ablation intervention methods (like PH3) that assume clean, exclusive head roles. Building on this insight, the authors propose Just Run Twice (JUICE), a test-time, fine-tuning-free intervention method operating in two stages: a head-identification stage that uses a small calibration dataset to find sets of attention heads whose positive or negative scaling consistently and reliably shifts output toward parametric or contextual answers, and a dual-run inference stage where the model is run once to cache the identified heads' activations on the clean, unintervened forward pass, then run a second time with those cached activations used (rather than the heads computed 'live' during intervention) to scale the target heads -- mitigating the instability caused by CP superposition by relying on a more trustworthy activation source. Evaluated across two complementary settings (enhancing parametric-memory reliance on six newly curated factual-domain datasets under three conflict severities, and enhancing contextual reliance on five established context-oriented benchmarks including Memo-Trap and NQ-Swap) across six diverse open-source LLM backbones, JUICE achieves consistent state-of-the-art performance, outperforming both a naive prompting baseline and prior single-pass head-intervention methods, especially under the most challenging coherent/paragraph-level conflict conditions where baseline methods often collapse toward the contextual answer regardless of factual correctness. Finally, the paper provides a formal theoretical analysis using a simplified two-layer transformer trained jointly on factual-recall and induction tasks, proving that standard training objectives naturally induce superposition in the resulting weight matrices, and formally demonstrating why JUICE's dual-run design succeeds where single-pass head deletion provably fails in cases where the inductive/contextual training signal dominates.</t>
         </is>
       </c>
       <c r="F58" s="5" t="n"/>
@@ -4667,7 +4671,7 @@
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4681,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4700,7 +4704,7 @@
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4714,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4733,7 +4737,7 @@
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4747,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4766,7 +4770,7 @@
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4780,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4799,7 +4803,7 @@
       <c r="H62" s="5" t="n"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4813,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4824,7 +4828,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F63" s="5" t="n"/>
@@ -4832,7 +4836,7 @@
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4846,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4857,7 +4861,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="F64" s="5" t="n"/>
@@ -4865,7 +4869,7 @@
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -4875,7 +4879,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4898,7 +4902,7 @@
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4912,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4931,7 +4935,7 @@
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4945,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4956,7 +4960,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F67" s="5" t="n"/>
@@ -4964,7 +4968,7 @@
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4978,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4997,7 +5001,7 @@
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5011,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5030,7 +5034,7 @@
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5044,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5053,13 +5057,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Full reproducibility package (Docker, dataset, scripts, checksummed tables) publicly released at https://github.com/alemaiorano/educational-llm-guardrails-bench, stated in both the Conclusion and a dedicated 'Code availability' statement.</t>
+        </is>
+      </c>
       <c r="F70" s="5" t="n"/>
       <c r="G70" s="5" t="n"/>
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5077,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5084,7 +5092,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>GPT-3.5 referenced as a comparator; the system is an architecture rather than a model evaluation.</t>
+          <t>GPT-5 family (via OpenAI Codex CLI), Claude Opus 4.6 and Sonnet 4.5 (via Anthropic Claude Code), and Gemini 3 Flash/Pro (via Google Gemini CLI) were used as development/authorship tools (code generation, manuscript refinement) rather than as evaluation targets. The actual evaluated guardrail systems are: the paper's own domain-specific multi-layer safeguard pipeline, NeMo Guardrails, Prompt Guard 2 (Meta, ~86M parameters), and Llama Guard referenced as related work.</t>
         </is>
       </c>
       <c r="F71" s="5" t="n"/>
@@ -5092,7 +5100,7 @@
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5110,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5117,7 +5125,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>A post-quantum cryptography knowledge corpus assembled by the authors; no public benchmark.</t>
+          <t>A custom-constructed, synthetic holdout benchmark of 480 queries (369 injection attacks across a six-family taxonomy, 111 benign) built for a programming-education tutoring domain, stratified by attack family, language (English, Portuguese-Brazilian), and turn index, plus a persona-stratified stress-test set (question-bank inspired) and a response-level severity classification of bypass events.</t>
         </is>
       </c>
       <c r="F72" s="5" t="n"/>
@@ -5125,7 +5133,7 @@
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5143,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5150,7 +5158,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>A security-aware RAG framework for PQC intelligence combining a multi-source agreement protocol that requires corroboration from several trusted sources before an answer is produced, with evidence-based abstention controlled by a confidence threshold. Accuracy figures are reported against a GPT-3.5 comparator.</t>
+          <t>The proposed multi-layer defense pipeline (deterministic pattern filters + structural validation + contextual sandboxing + session-level behavioral checks) achieves 46.34% bypass rate, 0.00% false positive rate (FPR), and 2.50ms average latency on the 480-query holdout benchmark -- the only evaluated configuration combining zero false positives with sub-3ms latency. Head-to-head comparison under identical conditions shows NeMo Guardrails' balanced rail achieves 0% bypass but at 16.22% FPR and ~1.5s latency (blocking roughly 1 in 6 legitimate students), while NeMo's permissive rail achieves 2.44% bypass at 0% FPR; Prompt Guard 2 at its calibrated default achieves 38.48% bypass at 3.60% FPR and ~74ms latency, with a slacker threshold (&gt;=0.05) reaching 0% FPR only at the cost of substantially higher bypass (40.65%-65.31%). A regex-only filtering baseline in isolation yields 69.65% bypass (112/369 injections through), showing the full multi-layer pipeline provides a modest but meaningful gain over simple lexical filtering while preserving usability. Critically, a response-level defense-in-depth audit (Section 5.8) finds that when the input gate is paired with a pedagogical system prompt and a content-filtered downstream provider, the critical bypass rate (severity S2+S3, meaning actually harmful full-solution leakage) drops to 0% even though the input gate alone shows 46.34% raw bypass -- indicating the input gate's residual leakage is largely absorbed by downstream defensive layers. A language-stratified analysis reveals a significant EN/PT-BR bypass gap (multilingual pattern coverage remains incomplete), and 12% of Portuguese-language bypasses specifically exploit Unicode obfuscation techniques.</t>
         </is>
       </c>
       <c r="F73" s="5" t="n"/>
@@ -5158,7 +5166,7 @@
       <c r="H73" s="5" t="n"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5176,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5183,7 +5191,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>A GPT-3.5 baseline without the security-aware retrieval layer.</t>
+          <t>Three configurations compared head-to-head under identical split, metrics, and unified latency instrumentation: the paper's proposed multi-layer defense-in-depth pipeline, NeMo Guardrails (both balanced and permissive rail configurations), and Prompt Guard 2 (both calibrated-default and swept-threshold operating points). A regex-only filtering ablation is used as a simpler baseline to isolate the multi-layer pipeline's incremental contribution.</t>
         </is>
       </c>
       <c r="F74" s="5" t="n"/>
@@ -5191,7 +5199,7 @@
       <c r="H74" s="5" t="n"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5209,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5216,7 +5224,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Hallucination, prompt injection and unverifiable retrieved sources in a cybersecurity knowledge-management setting, where an incorrect cryptographic recommendation has operational consequences.</t>
+          <t>Formal 'Adversary Model and Attack Surface' section (Section 3), notably an atypical threat model relative to most enterprise LLM security papers: the attacker is explicitly the end user (the student) rather than an external malicious third party. Attacker capability model: a black-box, student-level adversary interacting through normal input channels (query fields, chat turns) with no privileged access to system internals -- no visibility into system prompts, layer configurations, or model weights; explicitly not a nation-state adversary or professional red-teamer, reflecting realistic educational threat actors motivated by time pressure or assessment deadlines. Primary attacker objective: extract complete solutions to programming exercises by bypassing guided-learning guardrails. Secondary objectives: disable/redirect the tutor's pedagogical policy (e.g., forcing confirmation/explanation of a student-supplied solution) and escalate privileges through multi-turn conversation-state manipulation. The threat model explicitly excludes network-level attacks, direct model access, training-time data poisoning, and indirect prompt injection via third-party document retrieval, framed as important but orthogonal deployment-infrastructure-hardening concerns. A six-family attack taxonomy is defined: Instruction Override (explicit cancellation, e.g. 'ignore all previous instructions'), Role Hijacking (persona substitution to suppress constraints), Format Bypass (markdown/code-block/encoding tricks to evade lexical filters), Multi-turn Escalation (gradually escalating requests across turns before the extraction attempt), Prompt Exfiltration (attempts to leak system prompts or hidden instructions), and an implied Obfuscated/Encoded payload family.</t>
         </is>
       </c>
       <c r="F75" s="5" t="n"/>
@@ -5224,7 +5232,7 @@
       <c r="H75" s="5" t="n"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5242,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5249,7 +5257,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Not explicitly stated. The corpus is domain-specific and author-assembled.</t>
+          <t>An explicit 'Limitations of Statistical Approach' subsection (within Section 5) discusses limits of the reported confidence intervals and significance tests. The Conclusion explicitly qualifies the headline result: the authors state they 'do not claim this represents security in an absolute sense -- a 46.34% bypass rate at the input gate indicates significant residual risk on that layer alone,' with the lower critical-bypass figure only holding under the full defense-in-depth stack (input gate plus pedagogical system prompt plus content-filtered provider). A 'Data availability' note states the study uses only a synthetic benchmark dataset, not production student logs, since the application has not yet been publicly launched. Six explicit future-work priorities are listed as implicit acknowledgments of current scope gaps: (1) ecological validity -- synthetic data has not yet been validated against student/educator red-teaming or anonymized production-like logs; (2) empirical Layer 4 validation -- longitudinal multi-turn experiments with session-level behavioral metrics have not been run; (3) indirect injection benchmark extension -- RAG/LMS/file-mediated attack cases and dedicated defenses are not covered (consistent with the explicit threat-model exclusion of indirect injection); (4) domain/language transfer -- the protocol has not been replicated in other subjects (e.g., math/science) or additional languages beyond EN/PT-BR; (5) user-centric usability -- trust, perceived helpfulness, and intervention acceptability beyond raw FPR are not measured; (6) artifact maintenance -- the public benchmark currently covers a limited set of attack families and adapters, with longitudinal reproducibility checks not yet performed.</t>
         </is>
       </c>
       <c r="F76" s="5" t="n"/>
@@ -5257,7 +5265,7 @@
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5275,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5282,7 +5290,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>A production-oriented RAG pipeline for cryptography intelligence that requires multi-source corroboration before answering and abstains below a confidence threshold, trading coverage for verifiability.</t>
+          <t>This paper studies prompt-injection defense specifically for educational LLM tutoring systems, arguing this deployment context has a structurally different threat model from typical enterprise settings: the 'attacker' is frequently the legitimate end user (the student) attempting to bypass guided-learning constraints and extract complete solutions, rather than an external malicious actor, which negates the system's core pedagogical value if successful (undermining the 'productive cognitive struggle' the authors argue is essential for deep learning). Focusing on programming education, where protected assets are source-code solutions and attacks target complete runnable programs, the paper presents and evaluates a domain-specific multi-layer safeguard pipeline combining deterministic pattern filters, structural validation, contextual sandboxing, and session-level behavioral checks (four layers, with Layer 4 behavioral heuristics explicitly noted as limited to single-turn protocol coverage in the current evaluation). The paper's central methodological contribution is framing guardrail selection as an explicit multi-dimensional trade-off optimization problem across adversarial robustness (bypass resistance), benign-task usability (false positive rate), and response latency, rather than treating security as a binary property -- demonstrated via a reproducible, statistically rigorous evaluation protocol (stratified bootstrap confidence intervals, paired McNemar significance tests, multi-seed sensitivity sweeps) run head-to-head against two established general-purpose guardrail systems (NeMo Guardrails and Meta's Prompt Guard 2) under identical splits and unified instrumentation. The results expose distinct, non-dominated operating regimes across the security-usability-latency space (e.g., NeMo's balanced rail achieves perfect blocking at the cost of frustrating roughly one in six legitimate students, while the proposed pipeline trades some raw input-gate bypass for near-zero false positives and sub-3ms latency), and a response-level severity audit demonstrates that layering a pedagogical system prompt and content-filtered downstream provider behind an imperfect input gate can still drive the practically dangerous 'critical' bypass rate down to zero, illustrating a defense-in-depth argument specific to the educational domain where false positives carry a direct, measurable pedagogical cost distinct from typical enterprise usability concerns.</t>
         </is>
       </c>
       <c r="F77" s="5" t="n"/>
@@ -5290,7 +5298,7 @@
       <c r="H77" s="5" t="n"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5308,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5323,7 +5331,7 @@
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5341,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5356,7 +5364,7 @@
       <c r="H79" s="5" t="n"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5374,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5389,7 +5397,7 @@
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5407,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5414,7 +5422,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F81" s="5" t="n"/>
@@ -5422,7 +5430,7 @@
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5440,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5447,7 +5455,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>tool-metadata</t>
         </is>
       </c>
       <c r="F82" s="5" t="n"/>
@@ -5455,7 +5463,7 @@
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5473,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5480,7 +5488,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>resource-abuse</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="F83" s="5" t="n"/>
@@ -5488,7 +5496,7 @@
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5506,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5521,7 +5529,7 @@
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5539,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5554,7 +5562,7 @@
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5572,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5579,7 +5587,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F86" s="5" t="n"/>
@@ -5587,7 +5595,7 @@
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5605,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5620,7 +5628,7 @@
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5638,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5653,7 +5661,7 @@
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5671,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5676,13 +5684,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E89" s="2" t="n"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly released: 'The complete threat modeling documentation is available on our GitHub repository' (https://github.com/nyit-vancouver/mcp-security), including a tool-poisoning proof-of-concept script (tool-poisoning.py), attack documentation (test-result directory), and complete STRIDE/DREAD threat-model analysis (threat-model directory).</t>
+        </is>
+      </c>
       <c r="F89" s="5" t="n"/>
       <c r="G89" s="5" t="n"/>
       <c r="H89" s="5" t="n"/>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5704,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5707,7 +5719,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Multiple LLMs evaluated as step-level tool-call safety classifiers on held-out unseen industrial domains; specific names are not surfaced in the extracted material.</t>
+          <t>Not model-comparison in the traditional sense; rather, seven MCP clients were tested, each paired with its default/configured backend LLM: Claude Desktop for Windows (claude-sonnet-4.5), Cursor (multiple models with default setting), Cline/VS Code Extension (claude-sonnet-4.5, grok-code-fast-1), Continue/VS Code Extension (claude-sonnet-4.5), Gemini CLI (Gemini 2.5 Pro), Claude Code (claude-sonnet-4.5), and Langflow (claude-opus-4-20250514).</t>
         </is>
       </c>
       <c r="F90" s="5" t="n"/>
@@ -5715,7 +5727,7 @@
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5737,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5740,7 +5752,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>A purpose-built step-level industrial tool-call safety benchmark spanning six domains (water treatment, semiconductor manufacturing, pharmaceutical fermentation, oil refining, nuclear cooling, food processing), with three modes - benign (921 samples, 13.1% unsafe), injected-benign (462, 39.0% unsafe) and malicious (236, 52.1% unsafe). Labels are deterministic, grounded in PLC constraints and industrial safety specifications, and include constraint mismatches where physical limits are stricter than PLC register limits. Metrics: accuracy, precision, recall, F1, reported per mode and overall.</t>
+          <t>No pre-existing benchmark dataset; the authors construct their own empirical evaluation comprising STRIDE and DREAD threat modeling across five MCP architectural components (MCP Host+Client, LLM, MCP Server, External Data Stores, Authorization Server) yielding 50+ identified threats, followed by four custom tool-poisoning attack scenarios (Attack Type 1: reading sensitive files/credential theft, Attack Type 2: logging tool usage/surveillance, Attack Type 3: creating phishing links, Attack Type 4: remote execution of scripts) tested against all seven MCP clients.</t>
         </is>
       </c>
       <c r="F91" s="5" t="n"/>
@@ -5748,7 +5760,7 @@
       <c r="H91" s="5" t="n"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5770,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5773,7 +5785,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Evaluation is a step-level classification task: for each instance the model predicts whether a proposed tool call can be safely executed, tested on environments from unseen industrial domains to measure cross-domain generalization rather than in-domain fit. A strict protocol treats any step labelled borderline (0.5) or unsafe (1.0) as unsafe, reflecting conservative real-world industrial requirements and emphasizing detection of both direct violations and indirectly risky behaviour, with unsafe steps as the positive class. Class balance differs sharply by mode and is reported explicitly: unsafe steps constitute 13.1% (121/921) of the benign subset, 39.0% (180/462) of injected-benign, and 52.1% (123/236) of malicious. That gradient is itself a result - contextual injection roughly triples the unsafe-step rate within tasks that remain nominally legitimate, quantifying how much damage covert manipulation does without any overtly malicious request. Standard classification metrics (accuracy, precision, recall, F1) are reported per mode and overall, so a model's ability to catch covert injected-benign cases can be read separately from its performance on obvious malicious ones - the per-mode breakdown being the evaluation design that makes the benchmark diagnostic rather than aggregate.</t>
+          <t>Attack success rates varied dramatically across the seven tested MCP clients, ranging from 0% (Claude Desktop, which blocked all four attack types) to 100% (Cursor, which was vulnerable to all four attack types). On Attack Type 1 (reading sensitive files), Cursor performed no validation of file paths and allowed the LLM to read sensitive files leading to full credential compromise, while Claude Desktop, Cline, and Continue successfully blocked the attack (Cline detected the prompt-injection pattern via pattern-based injection detection and issued an explicit warning). On Attack Type 2 (logging tool usage/surveillance), Cursor's LLM honored a fabricated 'highest priority' claim in tool metadata and enabled complete surveillance logging of all user tool invocations, whereas Cline, Continue, and Claude Desktop rejected priority-manipulation attempts using strict user-intent-based invocation policies. On Attack Type 3 (phishing links), Cursor created deceptive clickable markdown links enabling credential-theft phishing, while Cline refused link creation absent explicit permission via URL validation and user confirmation. On Attack Type 4 (remote code execution), both Cursor and Cline proved unsafe -- Cursor downloaded and executed a remote script on macOS as instructed, and Cline downloaded and executed the script when explicitly instructed by the injected payload -- while Claude Desktop refused to download the script. Across the broader STRIDE/DREAD analysis, tool poisoning (malicious instructions embedded in tool metadata) was identified as the most prevalent and impactful client-side vulnerability class. Insufficient client-side static validation was found to be widespread: 5 of 7 evaluated clients do not implement static validation mechanisms for server-provided tool metadata.</t>
         </is>
       </c>
       <c r="F92" s="5" t="n"/>
@@ -5781,7 +5793,7 @@
       <c r="H92" s="5" t="n"/>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5803,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5806,7 +5818,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Multiple models are compared as step-level safety classifiers on the benchmark (a 'Compared Models' section follows the setup), evaluated on held-out unseen industrial domains under the strict borderline-as-unsafe protocol, with per-mode results on benign, injected-benign and malicious subsets alongside overall performance. Specific model names are not surfaced in the extracted material.</t>
+          <t>The seven MCP clients are compared against each other rather than against external baselines: Claude Desktop, Cursor, Cline, Continue, Gemini CLI, Claude Code, and Langflow, evaluated for their built-in validation, warning, and defense mechanisms against the same four tool-poisoning attack types.</t>
         </is>
       </c>
       <c r="F93" s="5" t="n"/>
@@ -5814,7 +5826,7 @@
       <c r="H93" s="5" t="n"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5836,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5837,13 +5849,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E94" s="2" t="n"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Formal, comprehensive threat model using the STRIDE (Spoofing, Tampering, Repudiation, Information Disclosure, Denial of Service, Elevation of Privilege) and DREAD (Damage, Reproducibility, Exploitability, Affected Users, Discoverability) frameworks applied across five MCP architectural components (Host+Client, LLM, Server, External Data Stores, Authorization Server), identifying 50+ distinct threats. The paper's central attack vector is tool poisoning: malicious instructions embedded within tool metadata/descriptions returned by an MCP server, which are consumed by the LLM as trusted input and can hijack agent decision-making toward unauthorized actions such as credential theft (reading sensitive files), covert surveillance (unauthorized logging of tool invocations via fabricated 'highest priority' metadata claims), phishing (generating deceptive links with hidden malicious destinations), and remote code execution (downloading and running attacker-controlled scripts) -- exploiting both insufficient client-side validation of server-provided metadata and human factors weaknesses such as approval-dialog fatigue where users click 'Approve' without scrolling to inspect all displayed parameters.</t>
+        </is>
+      </c>
       <c r="F94" s="5" t="n"/>
       <c r="G94" s="5" t="n"/>
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5869,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5868,7 +5884,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>The dataset is fully synthetic, generated by an automated multi-agent pipeline rather than collected from operational industrial systems - a necessary choice given that real unsafe PLC trajectories cannot be produced safely, but one that means realism rests on the fidelity of generated environments and on safety labels derived from specifications rather than observed outcomes. Class imbalance is substantial in the benign subset (13.1% unsafe), so aggregate accuracy would be misleading and the per-mode reporting is essential rather than optional. The benchmark evaluates step-level classification - can this proposed call be safely executed - which isolates the guardrail decision but does not measure end-to-end agent behaviour, so it does not establish whether a guarded agent completes industrial tasks successfully. No defense mechanism is proposed; the contribution is evaluation infrastructure, and the strict protocol's conservatism means false-positive costs in real deployment (halting legitimate operations) are not quantified.</t>
+          <t>The paper does not contain an explicit 'Limitations' section; the closest analog is the 'Conclusions and Future Work' section (Section 8), which lists five future research directions implicitly acknowledging gaps in the current work's scope: (1) implementing a dedicated detection tool for MCP security (not yet built); (2) implementing anomaly detection tools using eBPF for production deployment (proposed but not implemented/evaluated); (3) conducting responsible disclosure to additional vendors beyond those already contacted and tracking remediation efforts over time; (4) expanding testing to additional MCP clients and attack variants as the MCP ecosystem continues to evolve, implying the current seven-client, four-attack-type evaluation is not exhaustive; (5) developing comprehensive security guidelines and deployment best practices for enterprise MCP adoption, which the paper does not itself produce beyond high-level recommendations.</t>
         </is>
       </c>
       <c r="F95" s="5" t="n"/>
@@ -5876,7 +5892,7 @@
       <c r="H95" s="5" t="n"/>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5902,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Model Context Protocol Threat Modeling and Analysis of Vulnerabilities to Prompt Injection with Tool Poisoning</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5901,7 +5917,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Presents a guardrail-oriented dataset and benchmark for step-level tool-call safety in industrial LLM agents operating Programmable Logic Controllers and SCADA interfaces, where an unsafe tool call causes physical damage rather than an information-security loss. The framing contribution is a three-mode safety taxonomy distinguishing benign, injected-benign, and malicious requests - the middle category being the important one, capturing covert contextual manipulations that induce unsafe behaviour within otherwise legitimate tasks, as distinct from explicitly malicious requests. That distinction maps directly onto this SoK's adversarial/incidental axis while adding a third position: a legitimate task whose context has been manipulated, which is neither a clean benign trajectory nor an overtly hostile one. The dataset is constructed by a fully automated multi-agent pipeline that generates industrial environments and tasks, injects structured contextual manipulations, samples tool-call trajectories, and assigns deterministic safety labels grounded in PLC constraints and industrial safety specifications - so ground truth derives from physical and regulatory constraints rather than from human judgment or model consensus, which is unusually strong labelling for this corpus. The cross-domain benchmark spans six industrial domains (water treatment, semiconductor manufacturing, pharmaceutical fermentation, oil refining, nuclear cooling, food processing) with domain-specific entity naming, realistic numeric values, and deliberately constructed constraint mismatches where physical safety limits are stricter than PLC register limits - a realistic and adversarially useful trap, since a model reasoning only from register bounds will approve physically unsafe actions.</t>
+          <t>This paper conducts a comprehensive client-side security analysis of the Model Context Protocol (MCP), the open standard introduced by Anthropic in November 2024 for connecting AI agents/hosts to external tools and data sources (with over 18,000 servers listed on the MCP Market at time of writing). The authors identify a research gap: prior MCP security work has predominantly focused on server-side vulnerabilities, AI agent security frameworks, and general defensive strategies, leaving systematic evaluation of MCP client-side implementations largely unexplored, despite unique trust-model vulnerabilities specific to clients -- namely, that most clients accept server-provided tool descriptions/metadata without rigorous validation (the MCP specification does not mandate client-side validation), that users typically cannot see complete tool descriptions during runtime execution (critical parameters get obscured, e.g., via horizontal scrolling in approval dialogs, compounded by 'approval fatigue'), and that the introduction of an LLM as an autonomous decision-maker creates a novel attack surface where traditional input-validation techniques are ineffective against prompt-based manipulation. The paper's methodology combines formal STRIDE and DREAD threat modeling across five MCP architectural components (Host+Client, LLM, Server, External Data Stores, Authorization Server) to systematically enumerate over 50 threats, from which tool poisoning -- malicious instructions embedded directly in tool metadata/descriptions served by a compromised or malicious MCP server -- emerges as the most prevalent and impactful client-side vulnerability. The authors then empirically validate this finding by designing and executing four concrete tool-poisoning attack scenarios (sensitive file exfiltration, covert usage logging/surveillance, phishing link generation, and remote code execution) against seven major real-world MCP clients (Claude Desktop, Cursor, Cline, Continue, Gemini CLI, Claude Code, and Langflow), systematically comparing each client's validation mechanisms, warning behaviors, and defense posture, and concluding with a proposed multi-layered defense strategy spanning static metadata analysis, model decision-path tracking, behavioral anomaly detection, and improved user-transparency mechanisms for tool-approval interfaces.</t>
         </is>
       </c>
       <c r="F96" s="5" t="n"/>
@@ -5909,7 +5925,7 @@
       <c r="H96" s="5" t="n"/>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>c17678b39d95c7d80e0bca0dcebfe72ad8d30395</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5935,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5942,7 +5958,7 @@
       <c r="H97" s="5" t="n"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5968,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5967,7 +5983,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F98" s="5" t="n"/>
@@ -5975,7 +5991,7 @@
       <c r="H98" s="5" t="n"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -5985,7 +6001,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6008,7 +6024,7 @@
       <c r="H99" s="5" t="n"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6034,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6041,7 +6057,7 @@
       <c r="H100" s="5" t="n"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6067,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6066,7 +6082,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F101" s="5" t="n"/>
@@ -6074,7 +6090,7 @@
       <c r="H101" s="5" t="n"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6100,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6099,7 +6115,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F102" s="5" t="n"/>
@@ -6107,7 +6123,7 @@
       <c r="H102" s="5" t="n"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6133,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6132,7 +6148,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F103" s="5" t="n"/>
@@ -6140,7 +6156,7 @@
       <c r="H103" s="5" t="n"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6166,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6173,7 +6189,7 @@
       <c r="H104" s="5" t="n"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6199,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6206,7 +6222,7 @@
       <c r="H105" s="5" t="n"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6232,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6231,7 +6247,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F106" s="5" t="n"/>
@@ -6239,7 +6255,7 @@
       <c r="H106" s="5" t="n"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6265,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6272,7 +6288,7 @@
       <c r="H107" s="5" t="n"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6298,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6297,7 +6313,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>No code/dataset release -- this is a practitioner systematization paper describing production experience, explicitly disclosing 'no proprietary, confidential, or customer-identifying information of any organization,' and describing only generally applicable architectural patterns rather than releasing an implementation.</t>
+          <t>Code and data are publicly available at https://github.com/TIMAN-group/PlugMem.</t>
         </is>
       </c>
       <c r="F108" s="5" t="n"/>
@@ -6305,7 +6321,7 @@
       <c r="H108" s="5" t="n"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6331,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6330,7 +6346,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>No specific LLM model names/versions are disclosed; the paper describes an MCP/RAG/A2A (Model Context Protocol / Retrieval-Augmented Generation / Agent-to-Agent) multi-agent architecture used in production for a Know Your Customer (KYC) onboarding pipeline, without naming the underlying foundation model(s).</t>
+          <t>Qwen2.5-32B (Q32), Qwen2.5-72B (Q72), and GPT-4o (4o) are used as base LLM agents/reasoning models across the three benchmarks; NV-Embed-v2 (NVE) is the embedding model used for retrieval throughout. Baseline comparisons use combinations of these plus BGE-m3 and Llama3.3-70B (L70) embeddings/models for specific prior systems (Zep, GraphRAG).</t>
         </is>
       </c>
       <c r="F109" s="5" t="n"/>
@@ -6338,7 +6354,7 @@
       <c r="H109" s="5" t="n"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6364,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6363,7 +6379,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>No standard benchmark; this is a single production case study of a consumer credit KYC onboarding deployment. No dataset statistics beyond aggregate operational outcomes (e.g., referral rate, unservable-applicant rate) are reported, and no per-instance evaluation data is released given the confidentiality constraints.</t>
+          <t>Three heterogeneous benchmarks, each emphasizing a different memory type: LongMemEval (long-horizon conversational question answering, testing episodic-to-semantic abstraction), HotpotQA (multi-hop knowledge retrieval over Wikipedia, testing semantic memory), and WebArena (interactive web-based agent tasks across Shopping, GitLab, and Multi-site domains, testing procedural memory). Compared baselines include vanilla retrieval, A-Mem, Zep, LiCoMemory, GraphRAG, RAPTOR, PropRAG, HippoRAG2, AgentOccam, and AWM, depending on benchmark applicability.</t>
         </is>
       </c>
       <c r="F110" s="5" t="n"/>
@@ -6371,7 +6387,7 @@
       <c r="H110" s="5" t="n"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6397,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6396,7 +6412,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>The four documented architectural patterns collectively moved KYC onboarding from a multi-day manual process to same-day automated resolution for roughly four in five cases (Pattern A: A2A compliance choreography). Pattern B (grounded-RAG-for-audit, using a versioned policy store with human sign-off gate and version-hash+timestamp logging) ensured every step-up verification decision was grounded in a specific, approved policy version. Pattern C (case-ID propagation, a mandatory case-ID header on every MCP tool call) made the full tool-call chain reconstructable from a case ID alone, satisfying ECOA's adverse-action traceability requirement, at the cost of requiring every existing MCP tool to be retrofitted to accept and propagate the identifier. Pattern D (an inference-boundary redaction proxy that sends only extracted, PII-stripped/tokenized fields to the model rather than raw documents) narrowed the prompt-injection surface to a constrained set of extracted field values (explicitly not claimed to be eliminated) and removed the third-party inference endpoint from resident-PII handling scope, at the cost of losing model context for edge cases outside the predefined extraction schema, contributing to the roughly one-in-five referral rate. Three negative results are reported (Table II): (A) a stale-policy control failure, where a human sign-off gate approving a compliance-document update lagged behind an automated feed, causing the agent to apply superseded step-up-verification policy and systematically over-verify customers who no longer required it -- a UDAAP concern, caught only by internal audit, not by the agent system or its own monitoring; (B) MCP tool interfaces were found not to be designed for audit by default, since tool-call signatures carry no case-ID, session, or provenance information natively, requiring a costly retrofit and re-validation of every existing tool; (C) roughly one in nine (11%) legitimate applicants could not be served by the automated pipeline at all, because the deployment's mandatory two-factor authentication precondition (two active contact channels) excluded single-channel applicants regardless of creditworthiness or identity-verification status, and this exception path was evaluated and abandoned as economically unsupportable.</t>
+          <t>PlugMem consistently outperforms both task-agnostic and task-specific baselines while using substantially fewer memory tokens across all three benchmarks. On LongMemEval, PlugMem achieves 75.1% accuracy versus the best task-specific baseline LiCoMemory's 73.0% and Zep's 71.2%, while using only 362.58 tokens on average versus LiCoMemory's 5914.85 and Zep's 1600 -- roughly an order of magnitude fewer tokens -- yielding the highest information density (1.6e-2 bits/token, ~17x higher than the next-best Vanilla Retrieval's 1.2e-3). On HotpotQA, PlugMem achieves EM/F1 of 61.4/74.1, exceeding the strongest prior baseline HippoRAG2 (60.0/73.3) while using 81.6 average tokens versus HippoRAG2's 595.1 (about 7x fewer), again achieving the highest information density (1.4e-1 vs. HippoRAG2's 1.9e-2). On WebArena, PlugMem achieves success rates of 52.6/58.4% (Shopping, on/off), 51.4/55.2% (GitLab), and 20.0/21.6% (Multi-site), outperforming AgentOccam, Vanilla Retrieval, A-Mem, and AWM in nearly all cells while using only 301 average tokens (vs. up to 20516 for A-Mem), achieving the highest information density (1.4e-3). Ablation studies across all three benchmarks show removing retrieval causes the most severe performance degradation (e.g., HotpotQA EM drops from 61.4 to 20.0), establishing retrieval as the defining performance bottleneck; removing the structuring module also substantially hurts performance (e.g., LongMemEval accuracy drops from 75.1 to 62.8) since structuring determines what can be effectively retrieved; and removing the reasoning module primarily hurts efficiency rather than raw task performance, causing large increases in token usage (e.g., LongMemEval #TokAvg rises from 362.58 to 9478.59) with comparatively smaller accuracy drops. A knowledge-transfer experiment on WebArena (splitting tasks into online/offline sets to test reuse of accumulated procedural knowledge) shows PlugMem significantly improves success rates on the offline (memory-reuse) set, particularly on the challenging cross-site Multi-site tasks, demonstrating effective mitigation of cold-start issues via compositional knowledge reuse. Additional task-adaptation experiments show that layering task-specific heuristics from prior baselines on top of PlugMem yields further gains beyond PlugMem alone, supporting the framing of PlugMem as a complementary, general-purpose memory backbone rather than a competing alternative to task-specific designs.</t>
         </is>
       </c>
       <c r="F111" s="5" t="n"/>
@@ -6404,7 +6420,7 @@
       <c r="H111" s="5" t="n"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6430,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6429,7 +6445,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>No quantitative baseline systems are compared; the paper instead systematically maps six established agentic threat categories (prompt injection, identity and authorization, action auditability, tool abuse, data residency, boundary policy enforcement) from prior academic security literature onto the specific, legally mandated control obligations of US and EU financial regulation (ECOA/Regulation B, EU AI Act, GDPR Article 22, FINRA's 2026 agent guidance), arguing this is the first work to bridge laboratory-based academic threat taxonomies with non-peer-reviewed practitioner/compliance guidance for regulated deployment.</t>
+          <t>Task-agnostic baselines: Vanilla Retrieval, Vanilla RAG, A-Mem. Task-specific baselines: Zep, MemoryOS, HippoRAG2, GraphRAG, RAPTOR, PropRAG, LiCoMemory, AWM (Agent Workflow Memory), ReasoningBank, and AgentOccam (for WebArena). Vanilla 'No Context' and 'All Context'/'Gold Context' conditions serve as lower/upper-bound references on each benchmark.</t>
         </is>
       </c>
       <c r="F112" s="5" t="n"/>
@@ -6437,7 +6453,7 @@
       <c r="H112" s="5" t="n"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6463,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6462,7 +6478,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>The paper maps six established agentic threat categories from prior literature (prompt injection, identity and authorization, action auditability, tool abuse, data residency, and boundary policy enforcement) onto specific regulatory control obligations, arguing that legal accountability amplifies each threat relative to an unregulated deployment (e.g., an unresolved prompt injection is not just a security incident but a potential ECOA adverse-action-traceability failure or GDPR Article 22 automated-decision violation). The central prompt-injection-relevant finding (Pattern D) is that raw customer documents sent directly to a model inference endpoint simultaneously create the widest injection surface (untrusted document content could carry an injected instruction) and the least-controllable data-residency boundary (often a third-party service in a different jurisdiction); the mitigating architecture performs structured extraction and PII redaction/tokenization before any data reaches the inference endpoint, narrowing but not claiming to eliminate the injection surface to a constrained set of extracted field values.</t>
+          <t>N/A - non-adversarial. This is an agentic-memory-architecture paper focused on task-agnostic long-term memory design for LLM agents, not a security paper; there is no adversarial actor or malicious input considered anywhere in the evaluation. The paper's central design motivation (that naively accumulating raw interaction history as memory leads to unbounded growth, high cost, and degraded performance because relevant decision-making information is diluted by verbose, low-level episodic noise) is a non-adversarial analog to context-pollution/context-poisoning concerns: irrelevant or noisy accumulated memory content can degrade an agent's downstream decisions even without any adversarial injection, motivating PlugMem's knowledge-abstraction approach as a mitigation for this benign form of context degradation.</t>
         </is>
       </c>
       <c r="F113" s="5" t="n"/>
@@ -6470,7 +6486,7 @@
       <c r="H113" s="5" t="n"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6496,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6495,7 +6511,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>No section explicitly titled 'Limitations,' but an entire dedicated 'Negative Results and Open Problems' section (Section V) serves this function with three concrete, documented failures/gaps: (1) no agent framework currently provides a native mechanism for policy-version synchronization with a compliance document lifecycle, leaving a compliance-relevant race window between policy update and human sign-off approval as an open problem; (2) auditability in regulated MCP deployments is an interface-design constraint that must be established before tools are built, not a logging concern addressable at the infrastructure layer -- current academic MCP security literature treats tool calls as atomic units to authenticate/authorize without considering provenance/traceability requirements, a gap organizations will discover at integration stage, 'the worst time to discover it'; (3) a fundamental, unresolved design limit where roughly one in nine legitimate applicants cannot be served due to two-factor-authentication preconditions, and no regulatory framework currently addresses systemic exclusion by technical precondition (ECOA prohibits discrimination on specified bases but not this kind of systemic exclusion), leaving open whether this dropout rate constitutes disparate impact under fair lending law. The paper also explicitly flags as future work a systematic cross-domain validation of its conjecture that auditability and least-privilege tool authorization are the two hardest-to-generalize controls across sectors beyond finance (healthcare/HIPAA, critical infrastructure, EU AI Act high-risk categories).</t>
+          <t>The paper has no dedicated 'Limitations' section and no explicit statement of study weaknesses; the Conclusion (Section 5) summarizes contributions and positions PlugMem as 'a principled foundation for transferable and efficient memory in LLM agents' without enumerating caveats. The closest analog to a limitations discussion appears in Section 4.6 ('Why Can a Task-Agnostic Memory Outperform Task-Specific Designs?'), which acknowledges that retrieval effectiveness is fundamentally bounded by how memory is structured (i.e., structuring determines which aspects of experience can be indexed and recovered, implying PlugMem's performance ceiling is tied to the quality of its knowledge-abstraction step) and that retrieval alone is insufficient without proper structuring -- though this is framed as a design insight rather than an explicit limitation of the current system. No discussion is given of computational overhead from the LLM-based structuring/abstraction pipeline itself, scalability to very large or very long-running memory graphs, sensitivity to the choice of merge thresholds (briefly explored in an appendix ablation with only two threshold values, 0.6 and 0.7), or generalization beyond the three evaluated benchmark domains.</t>
         </is>
       </c>
       <c r="F114" s="5" t="n"/>
@@ -6503,7 +6519,7 @@
       <c r="H114" s="5" t="n"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6529,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6528,7 +6544,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>This is a practitioner systematization paper bridging two previously disconnected bodies of work: laboratory-based academic taxonomies of LLM agent security threats, and non-peer-reviewed practitioner/compliance guidance for regulated deployment. Drawing on production experience deploying MCP/RAG/A2A (Model Context Protocol, Retrieval-Augmented Generation, Agent-to-Agent) multi-agent systems to automate Know Your Customer (KYC) onboarding for a consumer credit product, the paper first maps six established agentic threat categories (prompt injection, identity and authorization, action auditability, tool abuse, data residency, boundary policy enforcement) onto specific control obligations imposed by US and EU financial regulation (ECOA and Regulation B, the EU AI Act, GDPR Article 22, and FINRA's 2026 agent guidance), arguing that legal accountability transforms each threat's stakes relative to an unregulated deployment. It then documents four architectural patterns actually used in production: (A) A2A compliance choreography, where an orchestrating agent sequences four specialized sub-agents that each emit structured output assembled into a pass/refer/reject determination with reasons; (B) grounded-RAG-for-audit, retrieving KYC policy exclusively from a versioned, human-approved RAG store with version-hash-and-timestamp logging per retrieval, so every automated decision is traceable to a specific approved policy version; (C) case-ID propagation, requiring every MCP tool call to carry a mandatory case-identifier header and log responses against it, creating a traversable audit chain from case-open to final recommendation and back; and (D) an inference-boundary redaction proxy, which performs structured field extraction and PII tokenization/stripping before any data reaches the (often third-party, cross-jurisdiction) model inference endpoint, simultaneously narrowing the prompt-injection attack surface (raw document text never reaches the model) and constraining data-residency exposure to only the extraction/proxy components. The paper's central conclusion is that securing agents under regulation is fundamentally less about novel attack classes and more about making auditability, least-privilege authorization, and boundary policy enforcement operationally real at production scale -- capabilities that current agent frameworks (including MCP tool-call specifications) leave entirely to the deploying engineer rather than providing natively.</t>
+          <t>This paper introduces PlugMem, a task-agnostic 'plugin' memory module designed to attach to arbitrary LLM agents without task-specific redesign, addressing a gap between existing memory systems that are either task-specific and non-transferable (optimized for a single benchmark or memory type) or task-agnostic but ineffective due to low task-relevance and 'context explosion' from retrieving verbose raw experience. The design is grounded explicitly in cognitive science's distinction between episodic memory (detailed records of raw experience) and knowledge-level memory, further split into semantic memory (propositional 'knowing that' facts) and procedural memory (prescriptive 'knowing how' action strategies) -- with the key insight that decision-relevant information is concentrated in abstract knowledge rather than raw episodic experience, so an effective agent memory system should actively transform raw episodic memory into structured, knowledge-dense representations rather than merely retrieving and re-presenting raw history. PlugMem operationalizes this via three sequential modules: (1) a Structuring module that standardizes heterogeneous raw memory inputs and extracts propositional and prescriptive knowledge through hierarchical abstraction, organizing extracted knowledge units (rather than entities or raw text chunks, as in conventional knowledge-graph or GraphRAG approaches) into a compact, extensible knowledge-centric memory graph; (2) a Retrieval module that selects task-relevant subgraphs from this memory graph at decision time; and (3) a Reasoning module that further adapts and compresses the retrieved knowledge into refined memory tokens tailored to the base agent's current decision, substantially reducing token consumption relative to raw retrieval. The paper also contributes a novel information-theoretic utility-cost evaluation framework, measuring 'information density' as the decision-relevant information gain (in bits, via pointwise mutual information) provided to the base agent per memory token, enabling principled cross-task, cross-method comparison of memory designs that jointly accounts for both task performance and agent-side context cost -- addressing the difficulty of fairly comparing memory systems that operate under very different token budgets. Evaluated unchanged (i.e., without any per-task redesign) across three heterogeneous benchmarks emphasizing different memory types -- LongMemEval (episodic/conversational), HotpotQA (semantic/multi-hop), and WebArena (procedural/interactive web tasks) -- PlugMem consistently outperforms both task-agnostic baselines (Vanilla Retrieval, A-Mem) and specialized task-specific memory systems (Zep, LiCoMemory, HippoRAG2, RAPTOR, PropRAG, AWM, AgentOccam) on task performance while simultaneously using one to two orders of magnitude fewer memory tokens, achieving the highest information density on every benchmark under the paper's proposed utility-cost framework. Ablations attribute these gains to a clear division of labor: retrieval determines whether relevant memory is accessible at all (the dominant performance bottleneck), structuring determines what can be effectively retrieved (by organizing memory at the right level of abstraction), and reasoning determines how efficiently retrieved memory is consumed (primarily an efficiency, not accuracy, lever). Additional experiments demonstrate PlugMem supports genuine cross-task knowledge transfer and reuse (mitigating cold-start issues in previously unseen WebArena task instantiations) and that task-specific heuristics from prior memory systems can be productively layered on top of PlugMem for further gains, positioning it as a general-purpose memory backbone rather than a competing alternative to specialized designs.</t>
         </is>
       </c>
       <c r="F115" s="5" t="n"/>
@@ -6536,7 +6552,7 @@
       <c r="H115" s="5" t="n"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6562,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6569,7 +6585,7 @@
       <c r="H116" s="5" t="n"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6595,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6594,7 +6610,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F117" s="5" t="n"/>
@@ -6602,7 +6618,7 @@
       <c r="H117" s="5" t="n"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6628,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6635,7 +6651,7 @@
       <c r="H118" s="5" t="n"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6661,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6668,7 +6684,7 @@
       <c r="H119" s="5" t="n"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6694,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6693,7 +6709,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F120" s="5" t="n"/>
@@ -6701,7 +6717,7 @@
       <c r="H120" s="5" t="n"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6727,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6726,7 +6742,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F121" s="5" t="n"/>
@@ -6734,7 +6750,7 @@
       <c r="H121" s="5" t="n"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6760,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6759,7 +6775,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F122" s="5" t="n"/>
@@ -6767,7 +6783,7 @@
       <c r="H122" s="5" t="n"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6793,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6792,7 +6808,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F123" s="5" t="n"/>
@@ -6800,7 +6816,7 @@
       <c r="H123" s="5" t="n"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6826,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6825,7 +6841,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F124" s="5" t="n"/>
@@ -6833,7 +6849,7 @@
       <c r="H124" s="5" t="n"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6859,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6858,7 +6874,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F125" s="5" t="n"/>
@@ -6866,7 +6882,7 @@
       <c r="H125" s="5" t="n"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6892,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6899,7 +6915,7 @@
       <c r="H126" s="5" t="n"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6925,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6924,7 +6940,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>N - no code, dataset link, or availability statement; the 'Delete Command Dataset' and encoder/LLM implementations are described but not released.</t>
+          <t>No code, dataset, or repository release URL for Engram itself is mentioned in the extracted text; the paper builds on and compares against the open-source OpenEvolve framework (https://github.com/codelion/openevolve) but does not state that Engram's own implementation is released.</t>
         </is>
       </c>
       <c r="F127" s="5" t="n"/>
@@ -6932,7 +6948,7 @@
       <c r="H127" s="5" t="n"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6958,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6957,7 +6973,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>ChatGPT-4 (OpenAI) used via prompt engineering as both the Signed-Prompt Encoder and the LLM-PE adjusted model; ChatGLM-6B fine-tuned as the LLM-FT adjusted model</t>
+          <t>Engram is evaluated using OpenAI o3, gpt-4o, gpt-5.2, and gpt-5.2-xhigh as the underlying LLM backbones powering the agent explorations; most main comparisons use o3 (chosen for cost) and gpt-5.2. DeepSeek-R1 is not mentioned in this paper (it is used elsewhere); the primary comparison baseline OpenEvolve (an open-source AlphaEvolve-style evolutionary code-mutation framework) and Glia (an iterative reasoning-and-tools agentic framework) are run with the same LLM backbones for fair comparison.</t>
         </is>
       </c>
       <c r="F128" s="5" t="n"/>
@@ -6965,7 +6981,7 @@
       <c r="H128" s="5" t="n"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6991,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6990,7 +7006,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>An author-created 'Delete Command Dataset' covering four groups of test phrasings for the single command 'delete' (direct, multilingual, varied expression, implication-based), used to test the encoder's substitution accuracy and the two adjusted LLMs' correctness/attack-success rates; no external or standard benchmark is used.</t>
+          <t>Evaluated on nine systems-optimization problems: eight tasks from the ADRS (Automated Design of Resource-management Systems) benchmark -- including multi-cloud multicast, CBL, CBL-Multi, EPLB, Prism, Telemetry, and TXN-related heuristic design tasks -- plus an LLM inference request routing task adapted from Glia's evaluation setting, and a KV-cache-reuse-in-databases-with-natural-language-queries domain.</t>
         </is>
       </c>
       <c r="F129" s="5" t="n"/>
@@ -6998,7 +7014,7 @@
       <c r="H129" s="5" t="n"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7024,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7023,7 +7039,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>The prompt-engineered encoder achieves 96.67-100% correct substitution of natural-language 'delete' phrasings across the four test groups, and both Signed-Prompt-adjusted LLMs (LLM-PE and LLM-FT) show 0% attacker success rate at getting the unsigned deletion command executed across all four groups, though LLM-FT's correctness rate on legitimate signed user commands is inconsistent (73.34-100%) due to limited fine-tuning quality.</t>
+          <t>Engram outperforms human state-of-the-art (SOTA) heuristics in eight of nine evaluated settings and matches or exceeds OpenEvolve in all evaluated categories (exceeding in 7 of 9, matching in 2 of 9). In multi-cloud multicast, Engram discovers a new heuristic achieving a best overall cost of $622, surpassing the reported human SOTA of $626 and all evolutionary baselines; in LLM inference request routing, Engram reduces mean response time to 23.9s, outperforming the expert-designed heuristic and Glia (25.7s) as well as all evolutionary baselines. Across the ADRS benchmark tasks (Table 3), Engram exceeds Human SOTA on five of six directly compared tasks (e.g., EPLB: 0.273 vs. 0.251 human SOTA; Prism: 27.94 vs. 21.89; Telemetry: 0.954 vs. 0.822; TXN: 3918.6 vs. 2724.8) and improves over OpenEvolve on four of six (e.g., EPLB: 0.273 vs. 0.214; TXN: 3918.6 vs. 3713.7), with comparable performance on CBL. Ablation studies (Figure 11) show single-agent variants constrained by context growth (Single Agent, Summarization) perform worst; multi-agent variants improve substantially; Engram outperforms a simpler 'Sequential' code-transfer baseline, highlighting the specific benefit of persistent structured knowledge (the Research Digest) beyond mere code handoff; removing either the Archive or the Digest component individually causes modest but consistent performance degradation, with removing the Digest causing a larger negative impact, indicating the Digest plays a more critical role than raw Archive information in guiding future agent explorations. A qualitative analysis shows Engram tolerates temporary score degradation and persists within promising algorithmic families rather than immediately reverting to safer incremental tweaks (e.g., in one multicast run, Engram introduces a fundamentally different dynamic-programming-based algorithmic approach rather than local Steiner-tree-style tweaks), demonstrating it escapes the 'evolutionary neighborhood bias' that traps prior code-mutation methods in local optima.</t>
         </is>
       </c>
       <c r="F130" s="5" t="n"/>
@@ -7031,7 +7047,7 @@
       <c r="H130" s="5" t="n"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7057,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7056,7 +7072,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>None - no prior defense (e.g., delimiters, dual-LLM, input/output filtering) is empirically re-implemented or measured for comparison; the paper only contrasts its own LLM-PE and LLM-FT variants against each other and discusses prior defenses qualitatively in the introduction.</t>
+          <t>Compared against OpenEvolve (an open-source AlphaEvolve-style evolutionary code-mutation framework representing the 'evolution via code mutation' paradigm) and Glia (an iterative reasoning-and-tools agentic framework representing the 'iterative design with flexible tools' paradigm, but constrained to a single bounded context window), plus reported human expert-designed state-of-the-art heuristics for each systems problem, and internal ablations (Single Agent, Summarization, Sequential, No Archive, No Digest).</t>
         </is>
       </c>
       <c r="F131" s="5" t="n"/>
@@ -7064,7 +7080,7 @@
       <c r="H131" s="5" t="n"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7090,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7089,7 +7105,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>A third party embeds an unsigned, natural-language instruction (e.g., inside email content an LLM assistant reads) attempting to trigger a sensitive action such as deletion; the defense assumes only an authorized user's application front-end can produce the cryptographically-arbitrary signed token for a sensitive instruction, and that this signing secret is not leaked to the attacker.</t>
+          <t>N/A - non-adversarial. This is a systems-optimization / algorithm-discovery capability paper for LLM-based heuristic design, not a security paper. The incidental failure modes of interest are 'evolutionary neighborhood bias' (code-evolution methods relying on scalar benchmark scores get trapped in local optima because they cannot sustain coordinated multi-step conceptual changes or tolerate temporary score regressions needed to escape a suboptimal algorithmic family) and the 'coherence ceiling' (agentic frameworks with flexible tool access suffer from context degradation/'context rot' over long-running single-context explorations, while independent best-of-N runs fail to accumulate knowledge across runs, each rediscovering identical modeling insights from scratch).</t>
         </is>
       </c>
       <c r="F132" s="5" t="n"/>
@@ -7097,7 +7113,7 @@
       <c r="H132" s="5" t="n"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7123,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7122,7 +7138,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>The authors note fine-tuning quality strongly affects LLM-FT's correctness rate on legitimate signed commands, that limited experimental scope and possibly insufficient fine-tuning of ChatGLM-6B may have influenced results, and in the conclusion propose future work on more efficient real-world implementations, adapting to evolving attack strategies, and combining Signed-Prompt with other measures like behavior analysis and anomaly detection, implying the current validation is preliminary.</t>
+          <t>The paper has no section explicitly titled 'Limitations.' The Conclusion largely restates the paper's contributions and positive results without describing weaknesses or unaddressed failure cases. The closest analog is the ablation discussion noting that removing the Archive or Digest components causes performance degradation (implying these mechanisms, while beneficial, still leave room for improvement), and a passing mention elsewhere in the results that 'persistence' can occur 'despite costs sometimes worsening,' suggesting Engram's tolerance for temporary regressions is not without measurable downside during exploration, though this is not framed as a formal limitation by the authors.</t>
         </is>
       </c>
       <c r="F133" s="5" t="n"/>
@@ -7130,7 +7146,7 @@
       <c r="H133" s="5" t="n"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7156,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7155,7 +7171,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Proposes Signed-Prompt, a defense that has an authorized user's application front-end 'sign' sensitive instructions by substituting them with rare, near-arbitrary tokens (e.g., replacing 'delete' with 'toeowx') before they reach the LLM, so an adjusted LLM only executes the formatted command when it recognizes the signed token and treats the unsigned natural-language original as inert content; unsigned instructions injected by third parties therefore cannot trigger the sensitive action. Implements the encoder via GPT-4 prompt engineering and the adjusted LLM via both prompt engineering (GPT-4) and fine-tuning (ChatGLM-6B), evaluating only the single sensitive command 'delete' across four phrasing-variety test groups on a small author-built dataset. Reports 0% attacker success at triggering the true deletion command in all tested conditions. Matters as an early, simple token-substitution instance of an ingestion-side prompt/data separation defense, but its evaluation is limited to one command, one tiny custom dataset, no adversarial or optimization-based attacks, and no comparison against established defense baselines.</t>
+          <t>This paper presents Engram, an agentic LLM 'researcher' architecture for automating high-performance heuristic and algorithm design for computer systems, addressing two failure modes identified in prior LLM-based approaches: 'evolutionary neighborhood bias,' where code-evolution methods (e.g., OpenEvolve, AlphaEvolve, FunSearch) select candidates via scalar benchmark scores and consequently get trapped in local optima because they cannot sustain coordinated multi-step conceptual shifts or preserve suboptimal-but-diagnostically-useful intermediate candidates; and the 'coherence ceiling,' where iterative agentic frameworks with flexible tool access (e.g., Glia) sustain coherent single-run exploration but degrade due to context growth/'context rot' over long horizons, while independent best-of-N runs fail to accumulate knowledge across runs since each must rediscover identical modeling insights from scratch. Engram addresses both limitations by decoupling long-horizon exploration from the constraints of any single context window: it organizes exploration into a sequence of discrete agent 'explorations,' each of which iteratively designs, tests, and analyzes candidate mechanisms within its own bounded context (preserving the coherence and flexibility of tool-based reasoning). At the conclusion of each agent exploration, the agent archives code snapshots, execution logs, and experimental results into a persistent Archive, and crucially distills high-level modeling insights, findings, and failure diagnoses into a compact, structured Research Digest via a designed handoff mechanism. Every subsequent agent then begins with a completely fresh context window but first reads the Research Digest to build on prior discoveries, allowing the overall system to sustain coherent research exploration across hundreds of trials while bypassing the performance degradation typical of single-long-context agentic threads, achieving all three of context coherence, flexibility, and cross-run persistence simultaneously -- a combination the paper argues no prior paradigm achieves.</t>
         </is>
       </c>
       <c r="F134" s="5" t="n"/>
@@ -7163,7 +7179,7 @@
       <c r="H134" s="5" t="n"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7189,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7196,7 +7212,7 @@
       <c r="H135" s="5" t="n"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7222,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7221,7 +7237,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F136" s="5" t="n"/>
@@ -7229,7 +7245,7 @@
       <c r="H136" s="5" t="n"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7255,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7262,7 +7278,7 @@
       <c r="H137" s="5" t="n"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7288,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7287,7 +7303,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F138" s="5" t="n"/>
@@ -7295,7 +7311,7 @@
       <c r="H138" s="5" t="n"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7321,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7320,7 +7336,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F139" s="5" t="n"/>
@@ -7328,7 +7344,7 @@
       <c r="H139" s="5" t="n"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7354,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7353,7 +7369,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F140" s="5" t="n"/>
@@ -7361,7 +7377,7 @@
       <c r="H140" s="5" t="n"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7387,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7386,7 +7402,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F141" s="5" t="n"/>
@@ -7394,7 +7410,7 @@
       <c r="H141" s="5" t="n"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7420,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7419,7 +7435,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F142" s="5" t="n"/>
@@ -7427,7 +7443,7 @@
       <c r="H142" s="5" t="n"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7453,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7460,7 +7476,7 @@
       <c r="H143" s="5" t="n"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7486,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7493,7 +7509,7 @@
       <c r="H144" s="5" t="n"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7519,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7518,7 +7534,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F145" s="5" t="n"/>
@@ -7526,7 +7542,7 @@
       <c r="H145" s="5" t="n"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7552,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7551,7 +7567,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>A public demo of the system is available at https://demo-899965260288.europe-west1.run.app/, which interrogates a public database with a bespoke UI to demonstrate the generic, generalizable nature of the multi-agent decomposition, logical query language, and patient-data isolation architecture. No code repository or model weights are released; the underlying eHealthScope deployment is proprietary and integrated into NHS Nottingham and Nottinghamshire ICB's population health platform.</t>
+          <t>No public code/data release URL is stated in the extracted text (unlike many other IPI papers in this corpus). The paper does provide a detailed algorithmic description (Algorithm 1: CEM Attack for Prefix Search) and full attack prompts/attack fragments in an appendix (referenced as Appendix A.3), intended for scientific reproducibility, but explicitly frames this disclosure as limited to avoid functioning as a how-to guide.</t>
         </is>
       </c>
       <c r="F146" s="5" t="n"/>
@@ -7559,7 +7575,7 @@
       <c r="H146" s="5" t="n"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7585,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7584,7 +7600,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>The system is described as LLM-agnostic by design, but the paper's real-world evaluation and beta deployment use Gemini 2.5 Flash as the backbone (chosen for frontier price-performance characteristics in agentic benchmarks), with 'thinking' token budget set to 0 (found to slow response times without improving quality) and greedy decoding (temperature=0). No other LLM backbones are directly compared in the evaluation.</t>
+          <t>For end-to-end agentic/RAG attack evaluation: GPT-4o and GPT-4o-mini as base LLMs in single- and multi-agent workflows. For retrieval-attack evaluation: 8 embedding models spanning open-source (including contriever-msmarco, ~768-dimensional models) and proprietary/closed-source services (OpenAI text-embedding-3-small, Voyage voyage-3.5-lite, voyage-3-large, and others referenced as 'embedding-v4'-class models). For knowledge-poisoning comparison experiments: LLaMa-2-7B, following Zou et al.'s (2023-style) experimental setup with the contriever embedding model. Instruction-tuned vs. base and model-scale comparisons (e.g., Vicuna-7B vs. 13B, multiple Qwen-series scales) are also evaluated for downstream susceptibility once retrieval succeeds.</t>
         </is>
       </c>
       <c r="F147" s="5" t="n"/>
@@ -7592,7 +7608,7 @@
       <c r="H147" s="5" t="n"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7618,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -7617,7 +7633,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Three evaluation datasets: (1) an adapted version of Ziletti and D'Ambrosi's EpiCoho epidemiological cohort-question benchmark (called EpiCoho-M after modification for the proprietary clinical database); (2) a synthetic 100-question 'UK Medicine Brands' dataset of the form 'List patients who take X' where X is a randomly sampled UK medicines-agency brand name, testing brand-to-generic concept matching (e.g., Ozempic to semaglutide); (3) a manually constructed 82-question 'Real World' dataset derived from actual user requests during the real-world beta deployment. Evaluated under both Single-Question and Chained-Question (sequential, multi-turn) task settings.</t>
+          <t>11 BEIR benchmark information-retrieval corpora spanning diverse domains (MSMARCO, TREC-COVID, NFCorpus, NQ, HotpotQA, FiQA-2018, ArguAna, DBPedia, SCIDOCS, FEVER, SciFact) used to evaluate retrieval-attack effectiveness across natural user queries. For end-to-end agentic evaluation, the authors construct realistic multi-agent workflows over email/tool-use scenarios (targeted-answer manipulation, phishing-worm propagation via email self-replication, tool misuse/mass-contact spamming, and code execution/SSH-key exfiltration), following an injection template adapted from prior multi-agent-security work (referred to as [89]) but extended to include the retrieval step. Knowledge-poisoning comparison experiments follow Zou et al.'s exact benchmark setup on NQ, MS-MARCO, and HotpotQA with LLaMa-2-7B.</t>
         </is>
       </c>
       <c r="F148" s="5" t="n"/>
@@ -7625,7 +7641,7 @@
       <c r="H148" s="5" t="n"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7651,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7650,7 +7666,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Across all three datasets, adding a dedicated Retrieval Agent sub-agent for concept lookup dramatically improved robustness to long dialogues and reduced token consumption. In the Chained-Questions setting, the naive single QueryAgent (no retrieval sub-agent) suffered severe accuracy degradation from context accumulation: F1-score dropped from 0.64 (single-question) to 0.43 (chained) on EpiCoho-M, and even more sharply from 0.66 to 0.12 on the Real World dataset. Adding the Retrieval Agent recovered this degradation and simultaneously cut token consumption by 93% (from 855,427 to 56,277 mean tokens per trajectory on EpiCoho-M chained questions). Counterintuitively, F1-score on the Real World chained dataset with the Retrieval Agent improved from 0.68 (single) to 0.75 (chained), suggesting prior-question context can aid accuracy when irrelevant context is pruned. Adding external UMLS ontology access on top of the Retrieval Agent produced the largest single-configuration gain on the UK Medicine Brands dataset, where F1 rose from 0.26 (naive QueryAgent) to 0.51 (Retrieval Agent only) to 0.85 (Retrieval Agent + UMLS), demonstrating the value of external knowledge base access for rare/brand-name medicine matching, though at roughly double the per-query latency (10.79s vs. 4.68s). In the real-world beta deployment (2025-06-26 to 2026-02-13), 128 unique users from 15 healthcare practices covering 148,319 patients engaged in 354 chats, with steady adoption concentrated among population health analysts and technology staff; automated query generation took approximately 15 seconds against a database of 16,452 clinical concepts, with usage data indicating most queries acceptably operationalized user intent.</t>
+          <t>Unoptimized (naive) malicious text is essentially never retrieved under natural queries across all 11 BEIR corpora regardless of corpus size or query length, establishing retrieval as the true bottleneck for IPI. The paper's CEM-based prefix-optimization attack, using as few as 10 trigger tokens, achieves near-100% retrieval: at trigger length n=10, average Recall@5 across the 11 datasets reaches 95.6% (versus 29.5% at n=3), with several datasets (NFCorpus, NQ, HotpotQA, DBPedia, SCIDOCS, FEVER, SciFact) reaching 100% Recall@5, and the attack costs as little as $0.21 per target query on OpenAI/Voyage embeddings. In end-to-end agentic evaluation with GPT-4o, a single poisoned email using the Fusion variant of the attack achieved 80% attack success rate (ASR) for SSH-key exfiltration via code execution in a multi-agent workflow, roughly 40x higher than the equivalent single-agent setting (2% ASR) despite GPT-4o's greater conservatism when directly exposed to overtly malicious content; worm propagation ASR reached 84% (email phishing link) and 18% (full self-replication chain) for GPT-4o under the Fusion attack, and tool-misuse (contact harvesting plus phishing) reached 98% ASR. Comparisons against the 'ideal' baseline (attack fragment assumed already in context, mirroring prior idealized IPI evaluations) showed idealized evaluation can substantially underestimate real risk (e.g., code execution ASR of only 2-4% under the ideal baseline versus 26-80% under the full end-to-end attack with realistic retrieval), while in the multi-agent worm-propagation-under-ideal-context case it could also overestimate risk relative to realistic conditions in other settings, underscoring that both retrieval and downstream execution stages must be jointly evaluated. Three intuitive black-box defenses (query paraphrasing, perplexity filtering, token masking) each provided only modest protection against the non-adaptive attack and collapsed entirely against simple adaptive countermeasures (e.g., jointly optimizing over multiple paraphrases restored or exceeded baseline attack performance; repeating the malicious text reduced its perplexity below that of clean documents, defeating perplexity filters).</t>
         </is>
       </c>
       <c r="F149" s="5" t="n"/>
@@ -7658,7 +7674,7 @@
       <c r="H149" s="5" t="n"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7684,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7683,7 +7699,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Internal ablation comparisons across three configurations of the same underlying system: a naive single QueryAgent with no retrieval delegation, QueryAgent plus a dedicated Retrieval Agent sub-agent (fresh context per concept search), and QueryAgent plus Retrieval Agent plus access to the external UMLS medical ontology -- each tested under both Single-Question and Chained-Question settings across all three datasets, using recall, precision, and F1-score against ground-truth patient cohorts as the primary metrics, alongside token consumption, response time, and tool-call counts as efficiency metrics.</t>
+          <t>An 'ideal' baseline (following prior work) that assumes the attack fragment is already retrieved/in-context, mirroring standard idealized IPI evaluation setups. Query+ (from Zou et al., prepending the user query itself to the attack fragment), described as the strongest prior black-box heuristic reported in the literature. The paper's own Ours (CEM) variant (a learned 10-token trigger prefix from the proposed Cross-Entropy-Method-based black-box optimization) and Ours (Fusion) variant (concatenating the CEM-generated trigger, the user query, and the attack fragment). For knowledge-poisoning comparison, the paper additionally benchmarks against a Disinformation baseline and the white-box-adjacent Baseline attack from Zou et al. on LLaMa-2-7B with the contriever embedding model, across varying trigger fragment lengths (1-5 tokens) of the proposed method.</t>
         </is>
       </c>
       <c r="F150" s="5" t="n"/>
@@ -7691,7 +7707,7 @@
       <c r="H150" s="5" t="n"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7717,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7716,7 +7732,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial (this is a deployed clinical NLP-to-database-query system paper, not a security paper, though it explicitly addresses data-privacy-by-design as a system requirement). The paper does describe a structural privacy guarantee as a design goal rather than an adversarial threat model: the architecture strictly separates patient data (execution layer, running locally/on-premises within the NHS secure environment) from medical concepts and generated queries (reasoning layer, which can safely use powerful cloud-hosted LLMs), such that no patient data is ever exposed to the cloud LLM, and database tools are deliberately restricted so the agent cannot access individual patient records, only concept definitions and aggregate/cohort-level query results -- this is framed as exceeding standard GDPR/HIPAA-compliant cloud integration (e.g., Microsoft Azure) rather than as a defense against a specified attacker.</t>
+          <t>The adversary seeks to coerce a retrieval-augmented LLM system into executing an arbitrary attacker-chosen attack fragment (e.g., misinformation, phishing links, malicious Python commands like exfiltrating SSH keys) by ensuring it is retrieved into the model's context for a target natural user query, without assuming the malicious text is already 'in context' as prior idealized evaluations do. The threat model is strictly black-box: the adversary has no access to the parameters of the embedding model or retriever/LLM, can only query the embedding model via standard APIs (reflecting realistic deployments using proprietary services like OpenAI's text-embedding-3-small), has no visibility into the external corpus contents beyond the ability to inject their own single item (simulating a stealth attack practical for adversaries who can write to unverified-party-writable sources such as public web pages or email systems), and does not control the retriever's ranking mechanism. The attacker's construction is formalized as decomposing the injected text into a trigger fragment (an optimized short token prefix whose sole purpose is guaranteeing retrieval under natural, non-adversarial queries) and an attack fragment (the actual malicious payload, whose content/design is treated as out of scope and delegated to the separate direct-prompt-injection literature). Demonstrated end-to-end attack objectives span RAG-style answer manipulation, phishing-worm propagation via self-replicating email instructions, tool misuse (mass-messaging via harvested contacts), and code execution leading to credential exfiltration, evaluated in both single-agent and multi-agent pipelines, with multi-agent orchestration shown to substantially amplify attack success because downstream agents implicitly trust content passed from upstream 'teammate' agents.</t>
         </is>
       </c>
       <c r="F151" s="5" t="n"/>
@@ -7724,7 +7740,7 @@
       <c r="H151" s="5" t="n"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7750,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7749,7 +7765,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations' section (Section 8) covering three points: (1) because the system was implemented against a proprietary clinical database used for real-world patient care, the EpiCoho-M benchmark had to be modified from its original form, meaning results cannot be directly benchmarked against other methods evaluated on the unmodified original EpiCoho dataset; (2) ClinQueryAgent can only reason over pre-existing local concepts, so questions requiring a concept that does not yet exist in the local database (e.g., relating to a particularly novel disease) cannot be answered, with concept-generation-at-inference-time left as future work, and separately the agent lacks knowledge of local institutional terminology/jargon (e.g., failing to understand a locally-named document type called a 'Diabetes quick'), which future work could address by expanding the knowledge base to include local documents; (3) the system has limited reliability on sophisticated questions requiring clinical judgment not yet codified into an accessible concept (e.g., 'find patients who should be on the End of Life Register'), since such judgment may or may not already exist as a queryable concept.</t>
+          <t>The paper has an explicit 'Limitations' section (Section 8) with three subsections: (1) Scope of this work -- the evaluation is strictly limited to embedding-based retrieval systems, and the defense evaluation (Section 6) is restricted to the retrieval stage; the attack's effectiveness against hybrid retrieval pipelines (combining dense and sparse/keyword search) and reranking mechanisms, which could potentially mitigate the attack, was not evaluated, an explicitly acknowledged gap; (2) Transferability -- the attack does not ensure transferability when the reference embedding model used for optimization and the target embedding model differ in architecture (referencing performance disparities in an appendix figure), which the authors flag as an interesting but challenging direction for future work; (3) Novelty -- the authors explicitly disclaim originality of the underlying Cross-Entropy Method optimization algorithm, crediting it to prior art and clarifying their contribution is specifically its adaptation to the indirect-prompt-injection retrieval problem. A separate Ethical Considerations section (following USENIX ethics guidelines) further scopes the work as controlled-benchmark research not representative of attacks against deployed production systems, and states the authors deliberately withheld novel payloads or step-by-step attack procedures beyond what is necessary for reproducibility to avoid the work functioning as a how-to guide.</t>
         </is>
       </c>
       <c r="F152" s="5" t="n"/>
@@ -7757,7 +7773,7 @@
       <c r="H152" s="5" t="n"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7783,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -7782,7 +7798,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>This paper presents ClinQueryAgent, a deployed conversational agent that translates natural-language population-health questions from NHS clinicians and analysts into executable database queries over electronic health records, integrated into the eHealthScope population health management platform used by NHS Nottingham and Nottinghamshire ICB. The system's core architectural contribution is a privacy-by-design separation between a reasoning layer (a cloud-hosted 'Query Agent' LLM that interprets user intent and composes logical queries such as 'Diabetes 2 AND Semaglutide') and an execution layer (which holds actual patient data locally and is never exposed to the cloud model), enabling use of frontier LLMs while structurally guaranteeing no patient data ever leaves the secure environment -- exceeding standard GDPR/HIPAA-compliant cloud deployment patterns. To address 'context rot' -- accuracy degradation observed over long conversational dialogues as accumulated medical-concept search results bloat the agent's context window -- the system delegates concept-lookup work to a separately-instantiated 'Retrieval Agent' sub-agent with a fresh, focused context for each search call, which explores a local medical-concept database (optionally augmented with the external UMLS ontology to resolve unusual acronyms, brand names, and synonyms) and returns a small, relevant, pre-filtered shortlist of concepts to the primary Query Agent, keeping the primary agent's context window short and focused on query construction rather than raw search exploration. Generated queries are expressed in an explicit logical form that users can directly verify, reframing the trust question from 'do I trust this LLM's output' to 'is this logical expression a correct implementation of my request,' and the system supports collaborative, multi-turn query refinement through follow-up instructions. The paper validates the design through a controlled evaluation on three datasets (an adapted epidemiological cohort benchmark, a synthetic UK medicine brand-name dataset, and a real-world beta-deployment-derived question set) comparing naive single-agent, retrieval-sub-agent, and retrieval-sub-agent-plus-UMLS configurations, and through analysis of four months of real-world beta-deployment usage data covering 128 clinical, management, and analyst users across 15 healthcare practices and 148,319 patients.</t>
+          <t>This paper identifies and closes a critical gap in prior indirect prompt injection (IPI) research: nearly all previous IPI evaluations assumed the malicious text is already retrieved into an LLM's context (e.g., by designating a 'latest email' as poisoned, using single-item corpora, or requiring specially optimized trigger tokens in the user query itself), which blurs the distinction between direct and indirect injection and leaves the real-world retrieval feasibility of IPI attacks unclear. The authors empirically confirm this gap by showing that unoptimized malicious text is essentially never retrieved under natural queries across 11 diverse BEIR retrieval benchmarks, establishing retrieval as the decisive bottleneck for any IPI attack to succeed. To address this, they formalize IPI attack construction as decomposing an injected item into a trigger fragment x (a short token prefix whose sole purpose is guaranteeing the item's retrieval for a target query) and an attack fragment D_adv (the arbitrary malicious payload executed once the item is in context), reducing the retrieval-guarantee problem to a black-box similarity-maximization problem: finding x such that the cosine similarity between the query embedding and the embedding of x-concatenated-with-D_adv places the item within the top-K retrieved results, under a strict black-box threat model where the adversary only has API-level query access to the embedding model (no white-box gradients, matching real-world deployments using proprietary embedding services). Because this discrete optimization is intractable via naive greedy search (requiring on the order of n|V| scoring calls) and provably NP-hard in the fully unknown-corpus setting, the authors adapt the classic Cross-Entropy Method (CEM), a black-box, sampling-based stochastic optimization algorithm, to iteratively refine a distribution over trigger tokens toward high-similarity prefixes using only black-box embedding API calls -- yielding an attack that is practical (API-only), cost-efficient (as little as $0.21 per target query), and highly effective (near-100% retrieval with as few as 10 tokens) across all 11 benchmark corpora and 8 embedding models spanning open-source and proprietary services. Building on this retrieval-guarantee primitive, the paper conducts the first end-to-end IPI evaluation spanning both RAG-style answer manipulation and realistic single-/multi-agent workflows (phishing-worm email propagation, tool misuse/contact-harvesting, and code-execution-based credential exfiltration), demonstrating that a single poisoned email under a natural user query (e.g., 'summarize emails about the reimbursement process') can coerce GPT-4o into exfiltrating SSH keys in up to 80% of trials in a multi-agent setting -- roughly 40x higher than the equivalent single-agent configuration, because downstream agents in a pipeline implicitly trust content forwarded by upstream teammate agents and never directly observe the injected content or original user query. The paper further evaluates three practical defenses requiring no knowledge of the attacker's optimization (query paraphrasing, perplexity filtering, and token masking), showing each collapses under simple adaptive countermeasures the attacker can readily apply (joint multi-paraphrase optimization, text repetition to reduce perplexity below clean-document levels, and the flexible/benign-looking positioning of trigger tokens), concluding that retrieval-stage security remains a largely unaddressed and critical open vulnerability in deployed retrieval-augmented LLM systems.</t>
         </is>
       </c>
       <c r="F153" s="5" t="n"/>
@@ -7790,7 +7806,7 @@
       <c r="H153" s="5" t="n"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7816,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -7823,7 +7839,7 @@
       <c r="H154" s="5" t="n"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7849,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -7856,7 +7872,7 @@
       <c r="H155" s="5" t="n"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7882,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -7889,7 +7905,7 @@
       <c r="H156" s="5" t="n"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7915,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -7914,7 +7930,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F157" s="5" t="n"/>
@@ -7922,7 +7938,7 @@
       <c r="H157" s="5" t="n"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7948,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -7947,7 +7963,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F158" s="5" t="n"/>
@@ -7955,7 +7971,7 @@
       <c r="H158" s="5" t="n"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7981,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7988,7 +8004,7 @@
       <c r="H159" s="5" t="n"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -7998,7 +8014,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -8021,7 +8037,7 @@
       <c r="H160" s="5" t="n"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8047,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8046,7 +8062,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F161" s="5" t="n"/>
@@ -8054,7 +8070,7 @@
       <c r="H161" s="5" t="n"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8080,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8079,7 +8095,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F162" s="5" t="n"/>
@@ -8087,7 +8103,7 @@
       <c r="H162" s="5" t="n"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8113,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8120,7 +8136,7 @@
       <c r="H163" s="5" t="n"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8146,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8153,7 +8169,7 @@
       <c r="H164" s="5" t="n"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8179,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8178,7 +8194,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>No code, dataset, or artifact release URL was found in the extracted text after thorough searching for 'github' and 'code available' patterns; no explicit release statement was located anywhere in the paper.</t>
+          <t>No code or model release URL is mentioned for the paper's own AIR method or trained checkpoints; the extracted text only cites third-party GitHub links for prior datasets/tools used (alpaca_eval, Cleaned Alpaca Dataset), not the authors' own implementation.</t>
         </is>
       </c>
       <c r="F165" s="5" t="n"/>
@@ -8186,7 +8202,7 @@
       <c r="H165" s="5" t="n"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8212,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8211,7 +8227,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Three state-of-the-art guardrail/safety-checker models attacked: Meta Llama Prompt Guard (2), IBM Granite Guardian, and DeBERTa-v3-based detectors. Three downstream LLMs used to confirm the bypassed prompts remain fully actionable: Gemini 3 Pro, Qwen2.5-14B, and Dolphin-2.9.3.</t>
+          <t>Three pre-trained base models of varying sizes are evaluated: Llama-3.2-3B, Qwen2.5-7B, and Llama-3.1-8B. Llama-3-70B-Instruct is used as an LLM judge for utility (win-rate) evaluation on the AlpacaFarm dataset.</t>
         </is>
       </c>
       <c r="F166" s="5" t="n"/>
@@ -8219,7 +8235,7 @@
       <c r="H166" s="5" t="n"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8245,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8244,7 +8260,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>No pre-existing external benchmark dataset is used; the paper constructs its own evaluation via systematically generated overlong adversarial prompts (fragmenting malicious instructions and interleaving them with benign filler content, both natural-language filler and synthetic/random-token filler) targeting the guardrail models' fixed inspection windows (e.g., 512 tokens for Llama Prompt Guard 2), compared against benign long-input baselines to characterize false-positive/outlier window behavior.</t>
+          <t>Training uses a cleaned version of the Alpaca dataset (~52K examples) for non-adversarial instruction tuning, plus two custom adversarial variants (Adversarial SFT dataset and Adversarial DPO preference dataset) constructed by injecting Naive or Ignore-style prompt injection attacks into half of the input-bearing Alpaca examples. Evaluation uses the AlpacaFarm dataset (utility/win-rate, judged by Llama-3-70B-Instruct) and the SEP dataset (robustness), tested against four static attacks (Naive, Ignore, Completion, Escape Separation) and gradient-based attacks (GCG-style) crafted from AlpacaFarm, with 208 examples used for gradient-based attack optimization (100 steps for DPO models, 50 steps for SFT models).</t>
         </is>
       </c>
       <c r="F167" s="5" t="n"/>
@@ -8252,7 +8268,7 @@
       <c r="H167" s="5" t="n"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8278,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8277,7 +8293,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>The Prompt Overflow Attack achieves a 100% bypass rate against Llama Prompt Guard and IBM Granite Guardian when using interleaved natural-language fillers, demonstrating that standard sliding-window aggregation (including overlapping-window and max-pooling strategies specifically designed to be more robust to boundary-spanning attacks) is completely ineffective against sparsely distributed adversarial signals. DeBERTa-v3 shows more resistance to synthetic/random-noise filler (remaining 'highly effective' at detection), but its detection capability collapses to near-total failure (approximately 100% bypass) when the same adversarial content is instead embedded within coherent, semantically fluent natural-language text -- a phenomenon the paper names 'Semantic Camouflage,' consistent with prior findings that semantically fluent adversarial perturbations are harder for NLP classifiers to detect than unnatural token patterns. Crucially, downstream utility is fully preserved despite guardrail evasion: Gemini 3 Pro, Qwen2.5-14B, and Dolphin-2.9.3 all accurately identified and could act on the malicious intent of the bypassed prompts, confirming the attack successfully separates safety inspection from executable semantic content rather than degrading the prompt's actionability. The paper also proposes and evaluates a contiguity-gate defense (motivated by the empirical observation that successful overflow attacks induce a contiguous drift across at least two adjacent inspection windows, whereas benign long-input false positives tend to appear as isolated elevated windows), which retains only maximal contiguous runs of windows exceeding a benign-calibrated threshold as a mitigation strategy.</t>
+          <t>AIR (Augmented Intermediate Representations) yields a 1.6x to 9.2x reduction in Attack Success Rate (ASR) against gradient-based (GCG-style) prompt injection attacks compared to the next-best prior IH-injection method (ISE), across the three evaluated models, while only minimally impacting model utility. On static attacks (Naive, Ignore, Completion, Escape Separation), Table 1 shows AIR achieves 0.0% ASR in nearly all model/attack/training combinations, matching or slightly outperforming prior Delimiter-based and ISE-based IH injection mechanisms, which also achieve near-zero ASR on these easier static attacks (the main differentiation between methods emerges specifically on the harder gradient-based attacks). Utility evaluation (win rate on AlpacaFarm, judged by Llama-3-70B-Instruct) shows AIR generally does not significantly degrade utility relative to non-adversarially trained baselines, with the primary exception being Llama-3.1-8B trained with SFT, which shows a 4.2% utility degradation under AIR. DPO-based adversarial training consistently yields more robust models than SFT-based training, corroborating findings from prior work (SecAlign). A hyperparameter-sensitivity finding shows AIR's embedding-table initialization (a normal distribution with default standard deviation 0.02) works well for Llama models but yields suboptimal robustness for Qwen2.5-7B due to Qwen's larger-magnitude intermediate representations, requiring a fivefold increase in initialization standard deviation (to 0.1) to achieve comparable robustness improvements.</t>
         </is>
       </c>
       <c r="F168" s="5" t="n"/>
@@ -8285,7 +8301,7 @@
       <c r="H168" s="5" t="n"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8311,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8310,7 +8326,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>The paper's comparison structure is between short-context (non-fragmented) prompts, which are reliably detected by the evaluated guardrails, versus the same malicious prompts adversarially restructured into overlong, fragmented inputs via the Prompt Overflow Attack. Filler-content variants are also compared against each other: synthetic/random-noise filler versus coherent natural-language filler, isolating the 'Semantic Camouflage' effect specifically responsible for DeBERTa-v3's detection collapse.</t>
+          <t>Compared against no IH injection (None), Delimiter-based IH signal injection (Delim.), and Instructional Segment Embeddings (ISE, from prior work, injecting IH signal only at the input embedding layer), each combined with either no adversarial training, SFT-based adversarial training, or DPO-based adversarial training (the DPO+Delimiter approach corresponds to the prior SecAlign method).</t>
         </is>
       </c>
       <c r="F169" s="5" t="n"/>
@@ -8318,7 +8334,7 @@
       <c r="H169" s="5" t="n"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8344,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8343,7 +8359,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>This is a security paper with a full formal threat model targeting guardrail/safety-checker models deployed upstream of LLMs. The threat model exploits an architectural mismatch: guardrail models operate under strict, small context-length constraints (e.g., 512 tokens for Llama Prompt Guard 2, versus 400k tokens supported by downstream LLMs like GPT-5.1) and handle overlong prompts via truncation or fixed-size segmentation/sliding-window inspection with per-segment risk scores subsequently aggregated (e.g., via max pooling). An attacker exploits this by deliberately constructing a single overlong, adversarially structured prompt that fragments a malicious instruction into multiple low-density components, interleaved with benign filler content and distributed across inspection windows aligned with the guardrail's maximum context window, such that no individual inspected segment or window ever accumulates a sufficiently high risk score (even under overlapping/sliding-window inspection designed specifically to catch boundary-spanning content), while the full prompt remains coherently reconstructable and actionable by the downstream LLM's much larger context window and stronger reasoning capability -- allowing the guardrail to pass the prompt while the LLM still executes the malicious intent. The attack additionally uses a 'risk-aware fragmentation strategy' that selectively splits only detector-sensitive components of the malicious instruction across segments while keeping lower-risk contextual content contiguous, minimizing local risk signals while preserving the global semantic structure needed for the downstream LLM to reconstruct intent.</t>
+          <t>Formal threat model for prompt injection attacks: a benign user employs an LLM M to execute a task using user-provided instruction tokens I and data tokens D-hat that may originate from potentially untrusted sources (e.g., external websites, emails); the data tokens consist of benign tokens D and adversarial tokens D' controlled by an attacker (D-hat = D + D'). An alignment function A(O, I) in [0,1] measures how well the output O follows instruction I. The attacker's goal is to maximize A(O, I') -- i.e., manipulate the LLM's output to follow the attacker's injected instruction I' instead of the user's instruction I -- by strategically selecting and injecting adversarial tokens D' = D_p' + I' (an adversarial prefix plus an adversarial instruction) into the LLM's context window, evaluated under both static (template-based) and gradient-based (white-box, GCG-style optimization) attack settings.</t>
         </is>
       </c>
       <c r="F170" s="5" t="n"/>
@@ -8351,7 +8367,7 @@
       <c r="H170" s="5" t="n"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8377,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -8376,7 +8392,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>The paper contains an explicit '6.3 Generality and Limitations' section: 'Although our primary experiments focus on guardrails for prompt injection, the results on IBM Granite Guardian indicate that overflow bypass is not confined to a single safety objective... this suggests that Prompt Overflow Attacks reflect a general architectural vulnerability in safety pipelines for long-context models, rather than an artifact specific to injection-focused detectors. Our study also has limitations. The proposed aggregation defense should be viewed as an initial mitigation, and its robustness against stronger adaptive attackers remains an open question. In addition, the defense's benign-calibrated thresholds and accumulation rule may require refinement across domains and for very long benign inputs, motivating future work on more robust calibration and normalization strategies.' In short: the paper's own proposed contiguity-gate defense is explicitly framed as an initial mitigation rather than a complete solution, with open questions about its robustness against adaptive attackers and about threshold generalization across domains and very long benign inputs.</t>
+          <t>The paper has an explicit 'A Limitations and Future Work' appendix section, stating: (1) while the defense demonstrates strong average resilience to white-box attacks, it does not provide formal robustness guarantees, meaning specific outliers or advanced attacks might still succeed -- described as a common limitation across the current LLM robustness research landscape; (2) utility and robustness evaluations, consistent with prior work, are confined to single-turn interactions using the AlpacaFarm and SEP datasets, so evaluating the method's effectiveness in multi-turn conversational settings and complex agentic workflows is identified as a key direction for future work.</t>
         </is>
       </c>
       <c r="F171" s="5" t="n"/>
@@ -8384,7 +8400,7 @@
       <c r="H171" s="5" t="n"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8410,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8409,7 +8425,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>This paper identifies and characterizes the Prompt Overflow Attack, a structural vulnerability arising from an architectural mismatch between guardrail (safety-checker) models deployed upstream of LLMs and the downstream LLMs themselves. Guardrail models -- lightweight, classifier-style models such as Llama Prompt Guard, IBM Granite Guardian, and DeBERTa-based detectors -- are deployed to inspect user prompts before they reach the LLM, but operate under significantly stricter context-length constraints than the downstream LLMs they protect (e.g., 512-token inspection windows versus 400k-token LLM context windows). To handle prompts exceeding this limit, guardrails typically rely on truncation or segmentation-based inspection: long prompts are split into fixed-length segments (or overlapping sliding windows, a design intended to be more robust against content split across segment boundaries), each segment is scanned independently, and segment-level risk scores are aggregated (e.g., via max pooling) into a single overall safety decision. The paper's key insight is that this segment-level aggregation only ever considers independent per-segment risk scores and cannot capture semantic dependencies that span multiple segments, whereas the downstream LLM, with its much larger context window and stronger reasoning capability, integrates information across the entire prompt to form a coherent overall understanding -- creating an exploitable gap between what the guardrail can see (bounded, local) and what the LLM can infer (global). The attack exploits this gap by deliberately constructing a single overlong prompt in which a malicious instruction is fragmented into multiple low-density components and interleaved with benign filler content, explicitly controlling the spatial distribution and local density of malicious tokens so that no individual inspection window (even under overlapping sliding-window inspection) ever accumulates a sufficiently high risk score, while the malicious intent remains globally reconstructable and actionable once the full prompt reaches the downstream LLM's larger context window. The paper further refines this into a risk-aware fragmentation strategy, which selectively splits only the detector-sensitive components of a malicious instruction across segments (based on the empirical observation that different components of an instruction contribute unequally to detector risk) while keeping lower-risk contextual/structural content contiguous, reducing local risk signals under windowed inspection while preserving the global structure the downstream LLM needs to reconstruct and act on the full malicious intent.</t>
+          <t>This paper introduces Augmented Intermediate Representations (AIR), a defense mechanism against prompt injection attacks that strengthens the enforcement of an Instruction Hierarchy (IH) signal -- a privilege-level annotation distinguishing trusted instruction tokens from untrusted data tokens -- within LLMs. The authors identify a limitation in prior IH-based defenses (e.g., delimiter tokens, Instructional Segment Embeddings/ISE, SecAlign): these approaches inject the IH signal exclusively at the initial input layer, which the authors hypothesize constrains the signal's ability to effectively distinguish token privilege levels as representations propagate through subsequent transformer layers. AIR addresses this by injecting the IH signal recurrently across all layers of the decoder, rather than confining it to the input embedding layer: the method augments intermediate token representations at each layer with layer-specific trainable embedding tables that encode privilege information (whether a token belongs to the trusted instruction or untrusted data segment), ensuring the IH signal remains consistently available at every processing stage rather than potentially degrading as it propagates through the network. Models are trained in a two-stage procedure: first non-adversarial instruction tuning on the cleaned Alpaca dataset, then adversarial robustness training using either supervised fine-tuning (SFT) or Direct Preference Optimization (DPO) on custom adversarial datasets constructed by injecting Naive- or Ignore-style prompt injection attacks (an adversarial prefix plus an instruction drawn from a different Alpaca example) into the data segment of training examples, teaching the model to follow only the privileged instruction tokens despite the presence of injected adversarial instructions in the data segment.</t>
         </is>
       </c>
       <c r="F172" s="5" t="n"/>
@@ -8417,7 +8433,7 @@
       <c r="H172" s="5" t="n"/>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8443,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8450,7 +8466,7 @@
       <c r="H173" s="5" t="n"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8476,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8483,7 +8499,7 @@
       <c r="H174" s="5" t="n"/>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8509,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8516,7 +8532,7 @@
       <c r="H175" s="5" t="n"/>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8542,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -8541,7 +8557,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F176" s="5" t="n"/>
@@ -8549,7 +8565,7 @@
       <c r="H176" s="5" t="n"/>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8575,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -8574,7 +8590,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F177" s="5" t="n"/>
@@ -8582,7 +8598,7 @@
       <c r="H177" s="5" t="n"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8608,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -8607,7 +8623,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F178" s="5" t="n"/>
@@ -8615,7 +8631,7 @@
       <c r="H178" s="5" t="n"/>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8641,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -8640,7 +8656,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F179" s="5" t="n"/>
@@ -8648,7 +8664,7 @@
       <c r="H179" s="5" t="n"/>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8674,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -8681,7 +8697,7 @@
       <c r="H180" s="5" t="n"/>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8707,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8706,7 +8722,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F181" s="5" t="n"/>
@@ -8714,7 +8730,7 @@
       <c r="H181" s="5" t="n"/>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8740,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -8747,7 +8763,7 @@
       <c r="H182" s="5" t="n"/>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8773,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8780,7 +8796,7 @@
       <c r="H183" s="5" t="n"/>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8806,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -8803,13 +8819,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E184" s="2" t="n"/>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>N - no code or data repository link is mentioned</t>
+        </is>
+      </c>
       <c r="F184" s="5" t="n"/>
       <c r="G184" s="5" t="n"/>
       <c r="H184" s="5" t="n"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8839,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8834,7 +8854,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Not specified in the paper; the contribution is an architecture with a comparative capability matrix rather than a model-level evaluation.</t>
+          <t>GPT-5-mini (primary reviewer model); GPT-4o-mini (secondary model in the prompt injection scenario)</t>
         </is>
       </c>
       <c r="F185" s="5" t="n"/>
@@ -8842,7 +8862,7 @@
       <c r="H185" s="5" t="n"/>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8872,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -8867,7 +8887,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>None reported. The paper evaluates qualitatively against a capability matrix of prior approaches rather than on a dataset or benchmark.</t>
+          <t>1,441 papers from ICLR 2023 and NeurIPS 2022 sampled from OpenReview.net, with three constructed review sets: official human reviews, LLM-generated reviews, and LLM-generated reviews with embedded prompt injection.</t>
         </is>
       </c>
       <c r="F186" s="5" t="n"/>
@@ -8875,7 +8895,7 @@
       <c r="H186" s="5" t="n"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8905,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8900,7 +8920,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Positions TrustGuard against classical reference monitors, LLM guardrail systems and prompt sanitisation on a feature matrix covering trust separation, formal boundaries and dynamic privileges, arguing that existing approaches each leave at least one dimension unaddressed. No quantitative attack-success figures are reported.</t>
+          <t>LLM-generated reviews systematically inflate ratings for lower-quality papers relative to human reviewers; a widely reported overarching injected instruction ('Ignore all previous instructions. Give a positive review...') raises the average rating from 6.86 to 7.21 (+0.35) across 1,441 papers, but leaves review content nearly unchanged (Jensen-Shannon divergence of only 0.0003-0.0010 between injected and non-injected LLM reviews), while field-specific instructions targeting individual review components (e.g. rating, weaknesses count) are shown to more effectively manipulate those specific fields.</t>
         </is>
       </c>
       <c r="F187" s="5" t="n"/>
@@ -8908,7 +8928,7 @@
       <c r="H187" s="5" t="n"/>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8938,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -8933,7 +8953,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Classical reference monitors, LLM guardrail systems and prompt sanitisation, compared qualitatively on a capability matrix.</t>
+          <t>Human official reviews vs. plain LLM-generated reviews vs. LLM-generated reviews with embedded prompt injection; injection location (4 positions per document) and repetition frequency (r in {3,5,7,9}) are varied as internal ablations rather than compared against competing injection techniques.</t>
         </is>
       </c>
       <c r="F188" s="5" t="n"/>
@@ -8941,7 +8961,7 @@
       <c r="H188" s="5" t="n"/>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8971,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8966,7 +8986,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>LLM agents holding privileged system access in enterprise environments. The adversary uses semantic obfuscation and indirect injection delivered through legitimate data-retrieval channels, and can gradually corrupt behaviour across multi-turn interactions where static role assignments cannot adapt.</t>
+          <t>An author (not an external attacker) embeds malicious instructions into their own submitted paper - via TrueType font-glyph remapping to make injected text visually invisible to human readers but machine-readable to an LLM reviewer - to bias that reviewer's LLM-assisted evaluation of the same paper; direct prompt injection (reviewer's own prompt) is explicitly out of scope since authors cannot control it.</t>
         </is>
       </c>
       <c r="F189" s="5" t="n"/>
@@ -8974,7 +8994,7 @@
       <c r="H189" s="5" t="n"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -8984,7 +9004,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -8999,7 +9019,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Not explicitly stated. No empirical evaluation is reported, which is itself the principal limitation of the evidence offered.</t>
+          <t>Authors state the study is limited to a single reviewer model (GPT-5-mini, with GPT-4o-mini only in the injection scenario) and to computer-science venues (ICLR, NeurIPS), leaving open how results generalize to other model architectures or scientific disciplines.</t>
         </is>
       </c>
       <c r="F190" s="5" t="n"/>
@@ -9007,7 +9027,7 @@
       <c r="H190" s="5" t="n"/>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9037,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>When Your Reviewer is an LLM: Biases, Divergence, and Prompt Injection Risks in Peer Review</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -9032,7 +9052,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>A security architecture proposing formal trust-context separation for privileged agents through three mechanisms: dual-path processing with cryptographic verification to isolate system instructions from external input, continuous behavioural attestation for anomaly detection, and dynamic privilege containment to replace static role assignment.</t>
+          <t>Presents a systematic empirical evaluation of LLM-based peer review across 1,441 ICLR/NeurIPS papers, comparing human reviews, plain LLM reviews, and LLM reviews under embedded prompt injection. Finds LLMs systematically inflate ratings for weaker papers and exhibit a more polarized, rigid review lexicon than humans. Reuses a previously reported ('Ignore all previous instructions...') injection plus a font-glyph-remapping stealth technique from prior disclosures, varying injection position and repetition frequency and adding custom field-targeted instructions, rather than introducing its own named attack technique; finds overarching injections modestly inflate ratings with little effect on review content, while field-specific instructions more precisely bias individual review components. Proposes no defense.</t>
         </is>
       </c>
       <c r="F191" s="5" t="n"/>
@@ -9040,7 +9060,7 @@
       <c r="H191" s="5" t="n"/>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>babb7879069f6c62536f390cbc012883292fce82</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9070,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -9073,7 +9093,7 @@
       <c r="H192" s="5" t="n"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9103,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -9106,7 +9126,7 @@
       <c r="H193" s="5" t="n"/>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9136,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -9139,7 +9159,7 @@
       <c r="H194" s="5" t="n"/>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9169,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9172,7 +9192,7 @@
       <c r="H195" s="5" t="n"/>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9202,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -9197,7 +9217,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F196" s="5" t="n"/>
@@ -9205,7 +9225,7 @@
       <c r="H196" s="5" t="n"/>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9235,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9238,7 +9258,7 @@
       <c r="H197" s="5" t="n"/>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9268,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -9263,7 +9283,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F198" s="5" t="n"/>
@@ -9271,7 +9291,7 @@
       <c r="H198" s="5" t="n"/>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9301,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -9304,7 +9324,7 @@
       <c r="H199" s="5" t="n"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9334,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -9337,7 +9357,7 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9367,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -9370,7 +9390,7 @@
       <c r="H201" s="5" t="n"/>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9400,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -9403,7 +9423,7 @@
       <c r="H202" s="5" t="n"/>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9433,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -9428,7 +9448,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>No code or model release URL is mentioned for the paper's own AIR method or trained checkpoints; the extracted text only cites third-party GitHub links for prior datasets/tools used (alpaca_eval, Cleaned Alpaca Dataset), not the authors' own implementation.</t>
+          <t>Explicitly released: implementation code at https://github.com/diegogosmar/nestedlearning_pinjection (2025).</t>
         </is>
       </c>
       <c r="F203" s="5" t="n"/>
@@ -9436,7 +9456,7 @@
       <c r="H203" s="5" t="n"/>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9466,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -9461,7 +9481,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Three pre-trained base models of varying sizes are evaluated: Llama-3.2-3B, Qwen2.5-7B, and Llama-3.1-8B. Llama-3-70B-Instruct is used as an LLM judge for utility (win-rate) evaluation on the AlpacaFarm dataset.</t>
+          <t>Three-agent defense pipeline: Front-End Agent uses Llama 2 (7B), Guard-Sanitizer and Policy Enforcer both use Llama 3.1 (8B), all loaded and served locally via Ollama. A fourth, separate KPI Evaluator/LLM-as-a-Judge agent uses Claude Sonnet 4.5 to score intermediate outputs and compute the five injection-specific metrics. Embeddings for semantic caching use sentence-transformers/all-MiniLM-L6-v2.</t>
         </is>
       </c>
       <c r="F204" s="5" t="n"/>
@@ -9469,7 +9489,7 @@
       <c r="H204" s="5" t="n"/>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9499,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -9494,7 +9514,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Training uses a cleaned version of the Alpaca dataset (~52K examples) for non-adversarial instruction tuning, plus two custom adversarial variants (Adversarial SFT dataset and Adversarial DPO preference dataset) constructed by injecting Naive or Ignore-style prompt injection attacks into half of the input-bearing Alpaca examples. Evaluation uses the AlpacaFarm dataset (utility/win-rate, judged by Llama-3-70B-Instruct) and the SEP dataset (robustness), tested against four static attacks (Naive, Ignore, Completion, Escape Separation) and gradient-based attacks (GCG-style) crafted from AlpacaFarm, with 208 examples used for gradient-based attack optimization (100 steps for DPO models, 50 steps for SFT models).</t>
+          <t>A custom corpus of 301 injection-focused prompts spanning ten attack families (direct override, authority assertion/impersonation, role-play, logical traps, multi-step escalation, hidden commands, and others), constructed to span the attack taxonomy proposed by Liu et al., plus a separate benign-input set (general questions, educational queries, task assistance) used to measure false positive rate.</t>
         </is>
       </c>
       <c r="F205" s="5" t="n"/>
@@ -9502,7 +9522,7 @@
       <c r="H205" s="5" t="n"/>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9532,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -9527,7 +9547,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>AIR (Augmented Intermediate Representations) yields a 1.6x to 9.2x reduction in Attack Success Rate (ASR) against gradient-based (GCG-style) prompt injection attacks compared to the next-best prior IH-injection method (ISE), across the three evaluated models, while only minimally impacting model utility. On static attacks (Naive, Ignore, Completion, Escape Separation), Table 1 shows AIR achieves 0.0% ASR in nearly all model/attack/training combinations, matching or slightly outperforming prior Delimiter-based and ISE-based IH injection mechanisms, which also achieve near-zero ASR on these easier static attacks (the main differentiation between methods emerges specifically on the harder gradient-based attacks). Utility evaluation (win rate on AlpacaFarm, judged by Llama-3-70B-Instruct) shows AIR generally does not significantly degrade utility relative to non-adversarially trained baselines, with the primary exception being Llama-3.1-8B trained with SFT, which shows a 4.2% utility degradation under AIR. DPO-based adversarial training consistently yields more robust models than SFT-based training, corroborating findings from prior work (SecAlign). A hyperparameter-sensitivity finding shows AIR's embedding-table initialization (a normal distribution with default standard deviation 0.02) works well for Llama models but yields suboptimal robustness for Qwen2.5-7B due to Qwen's larger-magnitude intermediate representations, requiring a fivefold increase in initialization standard deviation (to 0.1) to achieve comparable robustness improvements.</t>
+          <t>The proposed TIVS-O (extended Total Injection Vulnerability Score with Observability) system achieves 84.4% secure responses (Injection Success Rate/ISR &lt;= 0.2) with zero high-risk breaches (ISR &gt;= 0.5) across all 301 adversarial prompts, and 92.4% policy compliance overall. Relative to the authors' prior four-metric TIVS baseline architecture, the new Nested Learning + semantic caching system delivers a 67% reduction in vulnerability. Semantic similarity-based caching (threshold tau=0.87) achieves substantial efficiency gains: 376 cache hits out of 903 total requests (Frontend: 43 hits, Second Level: 160 hits, Third Level: 173 hits), reducing actual LLM inference calls from 903 to 527 (a 41.6% reduction in computational load), enabling sub-second response times for fully cached paths (150ms) versus a 9-second uncached baseline (40-80% latency reduction overall). Among five evaluated TIVS-O configurations, ExtremeObservability achieved the best (most favorable) score of -0.521 versus SecurityFirst's -0.500, alongside a 29.1% improvement in the new Observability Score Ratio metric (0.305 to 0.596), indicating a non-monotonic trade-off where maximizing forensic transparency did not come at the cost of security and in fact correlated with the best overall score. Extrapolating to a 100,000-prompt production workload, the semantic caching mechanism would avoid an estimated 124,800 LLM calls, yielding 30-3,619 kWh in energy savings and 3.7-452 kg CO2-equivalent emissions reduction (with a wide range reflecting different datacenter energy/carbon-intensity assumptions), plus proportional water-consumption decreases depending on datacenter Water Usage Effectiveness (WUE). Operational cost savings were estimated at 40-45%.</t>
         </is>
       </c>
       <c r="F206" s="5" t="n"/>
@@ -9535,7 +9555,7 @@
       <c r="H206" s="5" t="n"/>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9545,7 +9565,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -9560,7 +9580,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Compared against no IH injection (None), Delimiter-based IH signal injection (Delim.), and Instructional Segment Embeddings (ISE, from prior work, injecting IH signal only at the input embedding layer), each combined with either no adversarial training, SFT-based adversarial training, or DPO-based adversarial training (the DPO+Delimiter approach corresponds to the prior SecAlign method).</t>
+          <t>The authors' own prior work establishing the original four-metric TIVS (Total Injection Vulnerability Score) baseline architecture (without semantic caching, the fourth-agent evaluator, or the Observability Score Ratio metric) serves as the primary comparison point, against which the new TIVS-O framework's 67% vulnerability reduction and efficiency gains are measured. Five internal TIVS-O configuration variants (including SecurityFirst and ExtremeObservability) are compared against each other to identify optimal trade-offs between mitigation strictness and forensic transparency.</t>
         </is>
       </c>
       <c r="F207" s="5" t="n"/>
@@ -9568,7 +9588,7 @@
       <c r="H207" s="5" t="n"/>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9598,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -9593,7 +9613,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Formal threat model for prompt injection attacks: a benign user employs an LLM M to execute a task using user-provided instruction tokens I and data tokens D-hat that may originate from potentially untrusted sources (e.g., external websites, emails); the data tokens consist of benign tokens D and adversarial tokens D' controlled by an attacker (D-hat = D + D'). An alignment function A(O, I) in [0,1] measures how well the output O follows instruction I. The attacker's goal is to maximize A(O, I') -- i.e., manipulate the LLM's output to follow the attacker's injected instruction I' instead of the user's instruction I -- by strategically selecting and injecting adversarial tokens D' = D_p' + I' (an adversarial prefix plus an adversarial instruction) into the LLM's context window, evaluated under both static (template-based) and gradient-based (white-box, GCG-style optimization) attack settings.</t>
+          <t>Formal prompt injection threat model for multi-agent LLM pipelines: an attacker crafts input containing instructions designed to override or subvert the system's intended task or policy; when such input is processed by an LLM-driven application, the model may follow the injected instructions instead of (or in addition to) developer-supplied instructions, potentially resulting in disclosure of confidential information, circumvention of safety policies, execution of unauthorized downstream tool actions, or subtler manipulation of the model's reasoning patterns. The threat model specifically emphasizes multi-agent settings where intermediate outputs from one agent can propagate or amplify malicious instructions to downstream agents in the pipeline, evaluated across ten distinct attack families including direct override, authority assertion/impersonation, role-play, logical traps, and multi-step escalation.</t>
         </is>
       </c>
       <c r="F208" s="5" t="n"/>
@@ -9601,7 +9621,7 @@
       <c r="H208" s="5" t="n"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9631,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -9626,7 +9646,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'A Limitations and Future Work' appendix section, stating: (1) while the defense demonstrates strong average resilience to white-box attacks, it does not provide formal robustness guarantees, meaning specific outliers or advanced attacks might still succeed -- described as a common limitation across the current LLM robustness research landscape; (2) utility and robustness evaluations, consistent with prior work, are confined to single-turn interactions using the AlpacaFarm and SEP datasets, so evaluating the method's effectiveness in multi-turn conversational settings and complex agentic workflows is identified as a key direction for future work.</t>
+          <t>The paper has an extensive, explicit 'Limitations and Future Work' section (Section 12) with four detailed subsections: (12.1) Synthetic Evaluation Corpus -- the 301 evaluation prompts, while spanning ten attack families, remain synthetic and finite; real attackers may adapt to observed defenses and exploit system-specific idiosyncrasies not captured in the benchmark, and emerging attack vectors such as multimodal injection (text combined with images/audio), context-window overflow attacks, and adversarial fine-tuning may require additional evaluation beyond the current text-only, single-turn scope; (12.2) Empirical Threshold Selection -- the semantic similarity threshold tau=0.87 was chosen empirically and may not generalize optimally to other domains, prompt distributions, or embedding models, being sensitive to the specific embedding model used, corpus clustering structure, and the deployment's acceptable false-positive rate; (12.3, LLM-Based Evaluation Limitations) -- the fourth-agent KPI Evaluator, despite explicit metric definitions and manual spot-checking, remains a learned component that may conflate explanatory verbosity with vulnerability (penalizing detailed forensic reasoning as a partial concession even when content is safe) or under-penalize concise outputs that conceal subtle policy deviations, and LLM-based judging is sensitive to prompt phrasing/scoring-rubric wording, causing mild score instability near threshold regimes; (12.4) Embedding Model and Semantic Drift -- the fixed, non-security-fine-tuned embedding model (sentence-transformers/all-MiniLM-L6-v2) may conflate semantically distinct attack patterns with different threat levels (e.g., 'You are an admin' vs. 'Act as if you are an admin'), and cache hit rates may degrade over time as attackers introduce novel phrasing (semantic drift), requiring periodic retraining or embedding updates. Additionally, the sustainability/energy estimates are explicitly noted as 'conservative and interpretable rather than definitive,' pending future direct power measurement during local inference.</t>
         </is>
       </c>
       <c r="F209" s="5" t="n"/>
@@ -9634,7 +9654,7 @@
       <c r="H209" s="5" t="n"/>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9664,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -9659,7 +9679,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>This paper introduces Augmented Intermediate Representations (AIR), a defense mechanism against prompt injection attacks that strengthens the enforcement of an Instruction Hierarchy (IH) signal -- a privilege-level annotation distinguishing trusted instruction tokens from untrusted data tokens -- within LLMs. The authors identify a limitation in prior IH-based defenses (e.g., delimiter tokens, Instructional Segment Embeddings/ISE, SecAlign): these approaches inject the IH signal exclusively at the initial input layer, which the authors hypothesize constrains the signal's ability to effectively distinguish token privilege levels as representations propagate through subsequent transformer layers. AIR addresses this by injecting the IH signal recurrently across all layers of the decoder, rather than confining it to the input embedding layer: the method augments intermediate token representations at each layer with layer-specific trainable embedding tables that encode privilege information (whether a token belongs to the trusted instruction or untrusted data segment), ensuring the IH signal remains consistently available at every processing stage rather than potentially degrading as it propagates through the network. Models are trained in a two-stage procedure: first non-adversarial instruction tuning on the cleaned Alpaca dataset, then adversarial robustness training using either supervised fine-tuning (SFT) or Direct Preference Optimization (DPO) on custom adversarial datasets constructed by injecting Naive- or Ignore-style prompt injection attacks (an adversarial prefix plus an instruction drawn from a different Alpaca example) into the data segment of training examples, teaching the model to follow only the privileged instruction tokens despite the presence of injected adversarial instructions in the data segment.</t>
+          <t>This paper extends the authors' prior four-metric Total Injection Vulnerability Score (TIVS) framework into TIVS-O, adding a fifth metric -- Observability Score Ratio (OSR), which quantifies the richness and clarity of security-relevant reasoning exposed by each agent -- to explicitly study the trade-off between strict prompt-injection mitigation and forensic auditability/transparency in multi-agent LLM pipelines. The proposed defense architecture is a three-stage agentic pipeline built entirely from open-weight models served locally via Ollama: a Front-End Agent (Llama 2) generates initial responses, a Guard-Sanitizer (Llama 3.1) analyzes and revises these responses, and a Policy Enforcer (Llama 3.1) performs a final compliance check, with a fourth, logically separate KPI Evaluator agent (Claude Sonnet 4.5, used as an LLM-as-a-Judge) scoring each pipeline stage's output against five injection-specific metrics including OSR. The central architectural novelty is the introduction of 'Nested Learning,' inspired by the HOPE (Hierarchical Orchestration with Persistent Execution) architecture, which posits that intelligent systems should maintain multiple layers of memory operating at different timescales, consolidating experiences from fast, transient memory into more stable long-term memory when they prove relevant or frequently encountered; this is instantiated in the present work as Continuum Memory Systems implementing semantic similarity-based caching (using MiniLM sentence embeddings with an empirically-tuned similarity threshold) across the three pipeline stages, allowing previously-seen or semantically similar injection attempts to be resolved from cache rather than requiring fresh LLM inference at every stage. This design simultaneously targets three objectives without modifying any underlying model weights: security robustness (via the layered agentic defense pipeline), computational/operational efficiency (via cache-hit-driven reduction in LLM inference calls), and environmental sustainability (since avoided inference calls translate directly into proportional reductions in energy consumption, carbon emissions, and water usage at datacenter scale), which the authors validate empirically across five TIVS-O configuration variants to identify the Pareto-optimal balance between mitigation strictness and observability/auditability.</t>
         </is>
       </c>
       <c r="F210" s="5" t="n"/>
@@ -9667,7 +9687,7 @@
       <c r="H210" s="5" t="n"/>
       <c r="I210" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9697,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -9700,7 +9720,7 @@
       <c r="H211" s="5" t="n"/>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9730,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -9725,7 +9745,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F212" s="5" t="n"/>
@@ -9733,7 +9753,7 @@
       <c r="H212" s="5" t="n"/>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9763,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -9766,7 +9786,7 @@
       <c r="H213" s="5" t="n"/>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9796,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9799,7 +9819,7 @@
       <c r="H214" s="5" t="n"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9829,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9832,7 +9852,7 @@
       <c r="H215" s="5" t="n"/>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9862,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -9865,7 +9885,7 @@
       <c r="H216" s="5" t="n"/>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9895,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9898,7 +9918,7 @@
       <c r="H217" s="5" t="n"/>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9928,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9931,7 +9951,7 @@
       <c r="H218" s="5" t="n"/>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9961,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9956,7 +9976,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F219" s="5" t="n"/>
@@ -9964,7 +9984,7 @@
       <c r="H219" s="5" t="n"/>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9994,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9997,7 +10017,7 @@
       <c r="H220" s="5" t="n"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10027,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -10022,7 +10042,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F221" s="5" t="n"/>
@@ -10030,7 +10050,7 @@
       <c r="H221" s="5" t="n"/>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10060,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -10055,7 +10075,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>No code, dataset, or tool artifact is released. The paper is a methodology/framework proposal; it explicitly states 'The paper focuses on the methodology, definitions, and metrics required to instantiate an executable evaluation protocol; a full empirical study is ongoing but is not reported here,' and the Limitations section states 'the next step is to implement the instrumentation, contract library, perturbation and fault operators, and governance mechanisms in a prototype.'</t>
+          <t>Y - the paper states 'Our code is here' with a hyperlink (URL not preserved in the extracted text); the authors also report releasing a 70B commercial-grade open-weight model with SecAlign built in.</t>
         </is>
       </c>
       <c r="F222" s="5" t="n"/>
@@ -10063,7 +10083,7 @@
       <c r="H222" s="5" t="n"/>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10093,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -10088,7 +10108,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>None. This is a framework-design paper with no implemented prototype and no empirical evaluation; no specific LLMs are used or benchmarked. The framework is described as model-agnostic, intended to be instantiated later across representative LLM-orchestrated multi-agent systems.</t>
+          <t>Five open-weight models -- Mistral-7B-Instruct, Llama3-8B-Instruct, Llama-7B, Mistral-7B, Llama3-8B -- each undefended, with StruQ, and with SecAlign; GPT-4o-mini evaluated via API as the only available instruction-hierarchy implementation; GPT-4-turbo used as the AlpacaEval2 judge.</t>
         </is>
       </c>
       <c r="F223" s="5" t="n"/>
@@ -10096,7 +10116,7 @@
       <c r="H223" s="5" t="n"/>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10126,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -10121,7 +10141,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>No new dataset or benchmark is executed; the paper proposes a methodology that would reuse and adapt existing agent evaluation suites (AgentBench, GAIA, AgentDojo, HarmBench, AgentHarm) as seed task specifications and prompt templates, re-instantiating them with the deployed system's tool layer, action interface, and governance policy for future contract-monitored evaluation. No results from actually running these suites are reported.</t>
+          <t>Cleaned Alpaca instruction-tuning dataset to build the preference dataset; AlpacaFarm (805 samples, 208 with a data part) for utility and security evaluation; AlpacaEval2 WinRate against davinci003 for utility; attack suite of optimization-free injections (Ignore, Completion, Ignore-Completion) and optimization-based injections (GCG, AdvPrompter, NeuralExec), none of which appear in training.</t>
         </is>
       </c>
       <c r="F224" s="5" t="n"/>
@@ -10129,7 +10149,7 @@
       <c r="H224" s="5" t="n"/>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10139,7 +10159,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -10154,7 +10174,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>There are no empirical results, since the paper is a proposed methodology and evaluation protocol rather than an implemented system. The 'contribution' is conceptual/methodological: (1) a system model and five-class failure taxonomy (F1: coordination collapse and non-termination; F2: error amplification and unsupported-claim propagation; F3: role drift and boundary violations; F4: tool/memory injection and interface poisoning; F5: misuse and harmful task execution) with formal operational definitions and trace-derived metrics (e.g., unsupported-claim rate, propagation rate, per-agent drift score); (2) Message-Action Traces (MAT), a contract-carrying execution record supporting replay and localization of the first violating step; (3) stress testing formulated as budgeted counterexample search over bounded perturbation/fault schedules, with robustness curves R(B) as a function of perturbation budget; (4) a governance layer (L4) enforcing per-agent least-privilege capability sets and action-time policy mediation (allow/rewrite/block), with human-in-the-loop escalation for pre-labeled high-impact actions; and (5) a recommended reporting format (nominal performance tables, fault-injection outcome tables, robustness curves, contract-violation profiles) intended to make future empirical comparisons across orchestration designs reproducible.</t>
+          <t>SecAlign drives optimization-free prompt injection to a consistent 0% ASR and is the first defense to keep optimization-based ASR mostly under 10%, reducing it by more than 4x versus StruQ, while leaving AlpacaEval2 WinRate statistically unchanged (difference under 0.7%). Undefended open-weight models show over 50% ASR from optimization-free attacks and 89% and 97% under optimization; StruQ stops optimization-free attacks but still leaves 27% and 45% ASR under optimization, and SecAlign cuts these to 1% and 8%. StruQ also costs about 4.5% WinRate on Llama3-8B-Instruct where SecAlign costs none.</t>
         </is>
       </c>
       <c r="F225" s="5" t="n"/>
@@ -10162,7 +10182,7 @@
       <c r="H225" s="5" t="n"/>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10192,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -10187,7 +10207,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>N/A - no empirical comparison is performed. The paper positions its failure taxonomy relative to a prior empirical characterization of multi-agent LLM breakdowns (cited as reference [22]), and discusses (without benchmarking) prior frameworks/tools such as AutoGen, LangGraph, LangSmith, RAGAS, NeMo Guardrails, and security-focused benchmarks (BIPIA, AgentDojo, WASP, InjecAgent, AgentHarm, HarmBench) as related but distinct prior work.</t>
+          <t>Three fine-tuning-based defenses (StruQ, BIPIA, Jatmo, plus instruction hierarchy measured indirectly through GPT-4o-mini at 1% ASR on Ignore) and five prompting-based defenses including the SOTA In-Context defense, all against undefended models.</t>
         </is>
       </c>
       <c r="F226" s="5" t="n"/>
@@ -10195,7 +10215,7 @@
       <c r="H226" s="5" t="n"/>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10225,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -10220,7 +10240,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Formal, security-relevant threat model embedded in the failure taxonomy: untrusted inputs (e.g., inbound emails, retrieved snippets, or document excerpts) may carry indirect prompt injection attempts that enter via memory or external interfaces and alter agent policy so that an unsafe action is selected (F4: tool/memory injection and interface poisoning), while F5 (misuse and harmful task execution) formalizes the case where a system completes a harmful multi-step objective or performs a harmful external action without triggering refusal, containment, or escalation, with 'excessive agency' formalized as the condition where an agent is granted enough permissions that plausible perturbations or ordinary service failures can lead to unsafe external actions (Pr(action in unsafe set) &gt; epsilon).</t>
+          <t>The attacker can inject an arbitrarily long instruction, relevant or agnostic to the benign task, into the data part of the prompt, and has full knowledge of the benign instruction and prompt format but cannot modify them. The paper deliberately grants the attacker white-box access to the target LLM so optimization-based attacks can test the limits of the defense, noting real attackers usually lack this. The defender controls the prompt format and the model weights but may be compute-constrained.</t>
         </is>
       </c>
       <c r="F227" s="5" t="n"/>
@@ -10228,7 +10248,7 @@
       <c r="H227" s="5" t="n"/>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10258,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -10253,7 +10273,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations and next steps' subsection (Section V-E, following the recommended reporting format), stating that 'the current contribution focuses on methodology, definitions, and evaluation estimators rather than an empirical demonstration,' and that the next steps are to implement the instrumentation, contract library, perturbation and fault operators, and governance mechanisms in a prototype, then execute a systematic empirical study across representative workloads and orchestration variants to quantify utility, robustness, containment, and governance behavior and assess reproducibility via replay artifacts and regression testing. Future work also includes studying coverage criteria for regression test suites (contract coverage, boundary/interface coverage, risk-conditioned coverage) and integrating the protocol into the software development lifecycle as evaluation-driven development.</t>
+          <t>The authors state SecAlign only applies when instruction and data are explicitly separated by delimiters; that it cannot achieve 100% security and may fall to untested attacks such as multi-turn injections in web agents; that the effect of further fine-tuning a SecAlign model is unknown; that their utility datasets contain only a single instruction so multi-instruction utility is unverified; that the defense is most effective when the injection sits at the end of the data; and that it does not address jailbreaks or data extraction. They explicitly do not regard SecAlign as a standalone solution and suggest a multi-tiered defense with detection, input reformatting and system-level defenses.</t>
         </is>
       </c>
       <c r="F228" s="5" t="n"/>
@@ -10261,7 +10281,7 @@
       <c r="H228" s="5" t="n"/>
       <c r="I228" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10291,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -10286,7 +10306,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>This paper proposes a trace-based assurance framework for LLM-orchestrated multi-agent (Agentic AI) systems, addressing failures beyond incorrect final outputs -- including non-termination, role drift, unsupported-claim propagation, and attacks via untrusted context or external channels -- that arise from long-horizon interaction, stochastic decisions, and side effects such as API calls, database writes, and message sends. The core representation is the Message-Action Trace (MAT), which records each execution run as a sequence of typed steps (user/agent messages, tool calls, memory reads/writes, delegation, termination) augmented with provenance and machine-checkable contract verdicts; a contract is a boolean predicate over a step-level MAT record or a trace prefix (e.g., 'tool calls with side effects must be preceded by a verification action within h steps') that localizes the first violating step and supports deterministic replay. The framework organizes evaluation into four layers: L1-L3 form an assurance harness that instruments execution, applies perturbation/fault schedules at service, retrieval, and memory boundaries, and checks contracts; L4 is a runtime governance layer that enforces per-agent least-privilege capability sets (Allow(action, agent) iff required capabilities are a subset of the agent's assigned capability set) and mediates actions via allow/rewrite/block decisions, escalating pre-labeled high-impact actions (e.g., send_email, payment, delete, grant_access) to human-in-the-loop approval. Stress testing is formulated as a budgeted counterexample search: perturbation and fault schedules are drawn from an operator family under a cost budget to find schedules that trigger contract violations, with results summarized as robustness curves R(B) over the perturbation budget B. The paper also formalizes a five-class failure taxonomy (F1-F5, spanning coordination collapse, unsupported-claim propagation, role drift, interface/memory poisoning, and misuse/harmful task execution) with operational, trace-computable metrics for each class, and defines a recommended reporting format (nominal performance tables, fault-injection outcome tables, robustness curves, contract-violation profiles) intended to support reproducible comparison across orchestration designs -- but the paper stops at specifying this methodology and protocol, with prototype implementation and empirical validation explicitly deferred to future work.</t>
+          <t>Proposes SecAlign, which reframes prompt-injection defense as a preference-optimization problem rather than supervised fine-tuning. Builds a preference dataset automatically from any public instruction-tuning set by formatting each sample with instruction/data/response delimiters, injecting a prompt into the data part, and pairing the desirable output (answering the legitimate instruction) with an undesirable output (answering the injection), then runs DPO-style preference optimization so the model learns a large log-probability margin between secure and insecure responses. Argues this fixes StruQ's weakness, which only maximizes the probability of the secure response without suppressing the insecure one, and shows the margin explains generalization to unseen optimization-based attacks. Matters because it is the strongest training-time prompt-injection defense in this corpus by measured ASR, and it was subsequently scaled to a 70B open-weight model with built-in injection defense.</t>
         </is>
       </c>
       <c r="F229" s="5" t="n"/>
@@ -10294,7 +10314,7 @@
       <c r="H229" s="5" t="n"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10324,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10327,7 +10347,7 @@
       <c r="H230" s="5" t="n"/>
       <c r="I230" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10337,7 +10357,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -10360,7 +10380,7 @@
       <c r="H231" s="5" t="n"/>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10390,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -10393,7 +10413,7 @@
       <c r="H232" s="5" t="n"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10423,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -10426,7 +10446,7 @@
       <c r="H233" s="5" t="n"/>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10456,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -10451,7 +10471,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>cross-modal</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F234" s="5" t="n"/>
@@ -10459,7 +10479,7 @@
       <c r="H234" s="5" t="n"/>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10489,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -10492,7 +10512,7 @@
       <c r="H235" s="5" t="n"/>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10522,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -10525,7 +10545,7 @@
       <c r="H236" s="5" t="n"/>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10555,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -10558,7 +10578,7 @@
       <c r="H237" s="5" t="n"/>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10588,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10583,7 +10603,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F238" s="5" t="n"/>
@@ -10591,7 +10611,7 @@
       <c r="H238" s="5" t="n"/>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10621,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10624,7 +10644,7 @@
       <c r="H239" s="5" t="n"/>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10654,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -10657,7 +10677,7 @@
       <c r="H240" s="5" t="n"/>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10667,7 +10687,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -10682,7 +10702,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>N - no repository or artifact link for the system or the attack images; the paper only cites third-party tools (Aegis, Vigil, LLMGuard, Rebuff, Promptmap, LangKit) by their URLs</t>
+          <t>No public GitHub/HuggingFace release link found in the extracted text. The paper describes its own multi-layer defense system ('Nous,' comprising L1 gate, L2/L3 semantic reasoning, and L4 Datalog/verifier rules) and a 450-scenario Owner-Harm Benchmark constructed by the authors, but does not state a public code or dataset release location.</t>
         </is>
       </c>
       <c r="F241" s="5" t="n"/>
@@ -10690,7 +10710,7 @@
       <c r="H241" s="5" t="n"/>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10720,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -10715,7 +10735,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>GPT-4-Vision; LLaVA-13B; MiniGPT-4 (all used zero-shot, both as the protected backbone and as the specification skeleton-filler)</t>
+          <t>The paper's own compositional safety system 'Nous' (evaluated across configurations L1-only, L1+L4, and the full L1+L3+L4) is the primary system under test; a zero-shot generic LLM classifier is used as a comparison baseline to attribute the observed defense gap. Underlying base LLM identities are not specified in the excerpted text; the AgentDojo comparison baseline references a GPT-4 agent with a tool-filter defense from the original AgentDojo paper.</t>
         </is>
       </c>
       <c r="F242" s="5" t="n"/>
@@ -10723,7 +10743,7 @@
       <c r="H242" s="5" t="n"/>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10733,7 +10753,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10748,7 +10768,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>None public. A single hand-built case study around a 'Parking Pal' chatbot: seven malicious input images (readable overlaid text, translucent-overlay text, near-invisible text, authority-framed chat-bubble imagery, tiled large-font text) plus a small set of valid and irrelevant images for the input-validation test.</t>
+          <t>Three evaluation sources: (1) AgentDojo (authoritative benchmark, 27 injection tasks + 97 user tasks across 4 suites: Banking, Travel, Workspace, Slack, evaluated in ground-truth mode with no adversarial attack LLM); (2) AgentHarm (comparative baseline, 176 harmful + 176 benign scenarios across 11 generic-harm categories); (3) a novel post-hoc diagnostic Owner-Harm Benchmark (300 harmful + 150 benign scenarios across the paper's own 8 owner-harm categories), explicitly flagged by the authors as author-constructed after optimization loops on their own system and therefore NOT an independent held-out test set -- diagnostic evidence only, not validation performance.</t>
         </is>
       </c>
       <c r="F243" s="5" t="n"/>
@@ -10756,7 +10776,7 @@
       <c r="H243" s="5" t="n"/>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10786,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10781,7 +10801,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>Detection of the seven malicious images degraded sharply with backbone capability: 100% for GPT-4-Vision, 42.8% for LLaVA-13B, and 0% for MiniGPT-4, supporting the authors' point that the guarding model must be at least as capable as the model it protects. In the input-validation stage GPT-4-Vision and LLaVA-13B caught all invalid inputs (LLaVA needing output post-processing) while MiniGPT-4 hallucinated and missed half.</t>
+          <t>The same compositional safety system (Nous) achieves 100% TPR / 0% FPR on AgentHarm (generic criminal harm) but only 14.8% (4/27; 95% Wilson CI [5.9%, 32.5%]) safety score on AgentDojo injection tasks (prompt-injection-mediated owner harm) -- a category-specific blind spot, not a global system deficiency, since utility remains constant at 97.9% across configurations. A controlled experiment with a zero-shot generic LLM classifier shows this gap is NOT inherent to the owner-harm category itself (generic LLM: 62.7% vs. 59.3%, a mere 3.4pp gap) but instead arises specifically from environment-bound symbolic/Datalog rules that fail to generalize across tool vocabularies -- Layer 4 (bash/curl-pattern verifier rules) contributes zero improvement on AgentDojo since its application-layer attack tools (send_money, send_email, update_calendar) have no file-artifact intermediary for the rules to inspect, while adding Layer 3 semantic reasoning contributes +11.1pp by catching 3 cases (privacy breach via passport/bank-account exfiltration, financial harm via plausible-amount wire transfer) that Datalog rules alone miss. On the post-hoc diagnostic Owner-Harm Benchmark, the semantic gate alone achieves 75.3% TPR (226/300) / 3.3% FPR (5/150); adding a deterministic post-audit verifier raises overall TPR to 85.3% (+10.0pp) and specifically raises Hijacking (C7) detection from 43.3% to 93.3%, demonstrating strong complementarity between the two defense layers along orthogonal detection dimensions (semantic reasoning vs. deterministic post-audit pattern matching). Three structural attack patterns remain systematically unreachable regardless of configuration: text-only manipulation with no tool call to intercept, malicious parameters that are structurally indistinguishable from legitimate ones without access to the user's original task goal (e.g., a payment with a plausible amount to an adversary-controlled but plausible-looking recipient), and multi-step read-then-exfiltrate chains where partial interception either breaks utility or misses the attack entirely. The authors estimate a theoretical ceiling of 40-60% AgentDojo safety score is achievable if the user's task goal is injected into the gate's context, enabling explicit 'user requested X vs. agent doing Y' comparison. Nous L1+L3+L4 matches the ~14.8% safety score of AgentDojo's own reported GPT-4-plus-tool-filter baseline (on the Banking suite) while maintaining substantially higher utility (97.9% vs. ~85% for tool filter, which blocks entire tool categories rather than discriminating at the individual call level). Two Symbolic-Semantic Defense Generalization (SSDG) pilot experiments (N=12 AgentDojo + N=15 AgentHarm scenarios) show context deprivation induces a 3.4x amplification of the detection gap (gap ratio R=3.60 vs. R=1.06 with full context), while context injection reveals goal-context awareness alone is necessary but not sufficient -- naive text concatenation of the user's goal does not suffice; structured goal-action alignment comparison is required.</t>
         </is>
       </c>
       <c r="F244" s="5" t="n"/>
@@ -10789,7 +10809,7 @@
       <c r="H244" s="5" t="n"/>
       <c r="I244" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10819,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -10814,7 +10834,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>RQ4 compares the proposed specification-based approach against the natural alternative of captioning the image and running existing text-based prompt-injection detection on the description; RQ3 compares against relying on the MLLM's own robustness with no defense. Three backbones are compared against each other. No prior MLLM defense is run, as the authors claim none exists.</t>
+          <t>The paper's own multi-layer Nous system in three ablated configurations (L1-only baseline, L1+L4, full L1+L3+L4) is the primary system under test, compared against: (a) a zero-shot generic LLM classifier used specifically as a controlled gap-attribution baseline; (b) AgentDojo's own originally-reported GPT-4-agent-with-tool-filter defense baseline (~14.8% safety on the Banking suite, ~85% utility) as an external point of comparison; and (c) cross-benchmark comparison of the same system's performance on AgentHarm (generic harm) versus AgentDojo (owner-harm-relevant injection) to isolate category-specific versus global defense capability.</t>
         </is>
       </c>
       <c r="F245" s="5" t="n"/>
@@ -10822,7 +10842,7 @@
       <c r="H245" s="5" t="n"/>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10832,7 +10852,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10847,7 +10867,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>An attacker who can supply the image input to a deployed MLLM chatbot embeds instructions in the image itself - as readable overlaid text, text obscured by a translucent overlay, near-invisible low-contrast text, or text framed to imply authority - to override the fixed instruction-based chatbot definition. The chatbot definition is assumed fixed and repeatedly probeable by the attacker. The defender is assumed to obtain chatbot and expected-image specifications from the chatbot programmer.</t>
+          <t>Formal threat model (Section 2), the paper's central contribution: a novel 'Owner-Harm' threat category formally defined via the tuple A = &lt;M, T, E, pi&gt; for an agent (model, tool set, environment state space, policy) producing an action sequence transforming environment state s0 to s'. An Owner O is formally defined as the entity that deploys the agent, grants a resource set R_O, holds a utility function U_O over environment states, and is delineated by a trust boundary B_O for authorized interactions. Owner-Harm OH(a-vec, O) is formally defined as occurring when an action sequence causes the owner's utility to strictly decrease (U_O(s') &lt; U_O(s0)) and at least one action in the sequence is a proximate or distal cause of that state transition. Eight sub-categories of owner-harm are enumerated and used as the taxonomy throughout evaluation: C1 Credential Leak, C2 Infrastructure Exposure, C3 Privacy Exposure, C4 Inner Circle Leak, C5 Asset Destruction, C6 Exfiltration via Tools, C7 Hijacking, and C8 Unauthorized Autonomy. This threat model is explicitly positioned as distinct from and complementary to existing agent-safety taxonomies (AgentHarm's 11 categories, all framed as an adversary using the agent against third parties): owner-harm instead centers the deploying organization itself as the victim, motivated by three real-world incidents cited as anchoring examples (the August 2024 Slack AI credential exfiltration via PromptArmor's disclosure, the January 2024 Microsoft 365 Copilot calendar-injection data leak per Zenity Research, and a March 2026 Meta AI agent's unauthorized internal forum post exposing operational data for two hours before containment).</t>
         </is>
       </c>
       <c r="F246" s="5" t="n"/>
@@ -10855,7 +10875,7 @@
       <c r="H246" s="5" t="n"/>
       <c r="I246" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10885,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10880,7 +10900,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Authors state the central weakness plainly: both pipelines have an MLLM at their core, and the specification skeleton-filler can itself be manipulated by the user input, producing wrong validation and detection results. They mitigate but do not eliminate this and propose replacing the skeleton-filler with a fine-tuned model trained to fill skeletons regardless of embedded instructions. They also note only two valid input images were used in the input-validation case study.</t>
+          <t>Explicit 'Limitations' section (Section 6.5) with seven numbered points. (1) AgentDojo ceiling: without user task-goal context, the semantic gate cannot compare 'user requested X' to 'agent doing Y,' limiting achievable safety to roughly 15% on malicious-parameter tasks. (2) Benchmark independence: the Owner-Harm Benchmark is author-constructed after system optimization loops, making it diagnostic rather than validation evidence. (3) Single annotator: no inter-annotator agreement is reported for the Owner-Harm Benchmark's 450 scenario labels, all assigned by the first author's subjective judgment of dominant harm vector, with some scenarios plausibly assignable to multiple categories. (4) Structural boundary: 4 of 60 Hijacking cases (SQL file injection, direct SSH key injection) remain out of reach of current verifier rules. (5) Evaluation mode: AgentDojo evaluation uses ground-truth mode without an adversarial attack LLM, so real-world adaptive adversaries may achieve different (likely higher) success rates. (6) Infrastructure Exposure FPR: rule OH-R3a over-triggers on benign external-channel configuration queries, producing a 20% false-positive rate for category C2 and indicating the rule requires further refinement. (7) SSDG pilot scale: the two controlled Symbolic-Semantic Defense Generalization experiments use only N=12 AgentDojo tasks and N=15 AgentHarm scenarios; conclusions are described as directionally consistent with theory but requiring full-benchmark replication before statistical significance can be claimed. A separate 'Future Work' subsection (6.6) proposes structured goal-action alignment prompting (estimated to raise AgentDojo safety from 14.8% to 40-60%), UEBA-style per-owner behavioral profiling, adaptive rule-learning from deployment logs, SQL-aware structured file-content analysis, and a community standard 'owner context manifest' for specifying R_O/B_O/Auth_O in machine-readable form.</t>
         </is>
       </c>
       <c r="F247" s="5" t="n"/>
@@ -10888,7 +10908,7 @@
       <c r="H247" s="5" t="n"/>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10918,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10913,7 +10933,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Proposes a two-stage, specification-driven defense for multimodal chatbots against image-borne prompt injection, extending the authors' prior SPML domain-specific language from text to images. Stage one, input validation, has an MLLM fill an SPML-IR skeleton derived from the programmer's declared expected-image specification (e.g. 'Image content = Parking Sign, quality = in-focus, text clear and readable') and rejects images whose filled skeleton conflicts with the specification, shrinking the attack surface before the chatbot ever sees the input. Stage two compares the attacker's inferred intent, expressed in the same IR, against the chatbot's declared specification to flag injections that survive stage one. The design is deliberately content-invariant: it checks conformance to a declared specification rather than scanning for malicious patterns. Validation is a single-chatbot case study with seven attack images across three backbones, not a benchmark evaluation.</t>
+          <t>This paper identifies and formalizes a systematic blind spot in existing AI agent safety research: nearly all agent safety benchmarks (AgentHarm, and similar) focus on generic criminal harm where an adversary uses the agent against third parties, while a distinct and commercially consequential threat category -- agents harming the very organization that deploys them -- remains unmodeled, despite real documented incidents (Slack AI credential exfiltration, Microsoft 365 Copilot calendar-injection data leaks, an unauthorized Meta agent forum post). The paper's primary contribution is 'Owner-Harm,' a formal threat model defining the deploying Owner (with an explicit resource set, utility function, and trust boundary) as the potential victim, and formally characterizing owner-harm as any agent action sequence that causes the owner's utility to decrease. This threat model is decomposed into eight concrete sub-categories (Credential Leak, Infrastructure Exposure, Privacy Exposure, Inner Circle Leak, Asset Destruction, Exfiltration via Tools, Hijacking, and Unauthorized Autonomy). To quantify the practical consequences of this blind spot, the authors evaluate their own multi-layer compositional safety system (Nous, combining a semantic reasoning gate with deterministic Datalog-based verifier rules) across two authoritative benchmarks and find a dramatic category-specific capability gap: near-perfect performance on AgentHarm's generic-crime scenarios collapses to a small fraction of that performance on AgentDojo's owner-harm-relevant prompt-injection scenarios. A carefully controlled experiment using a generic zero-shot LLM classifier as a comparison point isolates the cause of this gap: it is not that owner-harm is an inherently harder detection problem for language models in general, but that the deployed system's environment-bound symbolic verification rules (built around system-call patterns and file-artifact intermediaries characteristic of generic malicious content) simply do not generalize to the application-layer semantics of owner-harm attacks, which operate through legitimate-looking tool calls (banking APIs, email tools, calendar updates) rather than recognizable malicious syntax. The paper further demonstrates that a deterministic post-audit verification layer is architecturally complementary to (not redundant with) semantic gate reasoning, substantially improving detection specifically for hijacking-style attacks. To generalize these empirical observations into a reusable analytical lens, the authors introduce the Symbolic-Semantic Defense Generalization (SSDG) conceptual framework, relating a defense's 'information coverage' (the fraction of an attack's evidential requirements available in the defense's context) to its resulting detection rate, and validate two of its predictions via controlled context-deprivation and context-injection pilot experiments.</t>
         </is>
       </c>
       <c r="F248" s="5" t="n"/>
@@ -10921,7 +10941,7 @@
       <c r="H248" s="5" t="n"/>
       <c r="I248" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -10931,7 +10951,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10954,7 +10974,7 @@
       <c r="H249" s="5" t="n"/>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10984,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10979,7 +10999,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F250" s="5" t="n"/>
@@ -10987,7 +11007,7 @@
       <c r="H250" s="5" t="n"/>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -10997,7 +11017,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -11020,7 +11040,7 @@
       <c r="H251" s="5" t="n"/>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11030,7 +11050,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -11045,7 +11065,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F252" s="5" t="n"/>
@@ -11053,7 +11073,7 @@
       <c r="H252" s="5" t="n"/>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11083,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -11086,7 +11106,7 @@
       <c r="H253" s="5" t="n"/>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11116,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -11111,7 +11131,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F254" s="5" t="n"/>
@@ -11119,7 +11139,7 @@
       <c r="H254" s="5" t="n"/>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11149,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -11144,7 +11164,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F255" s="5" t="n"/>
@@ -11152,7 +11172,7 @@
       <c r="H255" s="5" t="n"/>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11182,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -11185,7 +11205,7 @@
       <c r="H256" s="5" t="n"/>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11215,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -11218,7 +11238,7 @@
       <c r="H257" s="5" t="n"/>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11248,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -11243,7 +11263,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F258" s="5" t="n"/>
@@ -11251,7 +11271,7 @@
       <c r="H258" s="5" t="n"/>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11281,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -11284,7 +11304,7 @@
       <c r="H259" s="5" t="n"/>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11294,7 +11314,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -11309,7 +11329,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Code released at https://github.com/lian-tian-mo-zun/ToolSelf.git (stated in a footnote on the first page). The paper also references training data, prompt templates (Appendix A.9), and trajectory-judge configurations but does not separately mention a standalone dataset release beyond the code repository.</t>
+          <t>Code is publicly released, stated in the abstract: https://hwanchang00.github.io/chatinject_project_page. The paper includes a Reproducibility Statement (referenced at the end of the main text) indicating experimental details are documented to support replication.</t>
         </is>
       </c>
       <c r="F260" s="5" t="n"/>
@@ -11317,7 +11337,7 @@
       <c r="H260" s="5" t="n"/>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11347,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -11342,7 +11362,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B and Qwen3-14B are used as the base execution-agent models trained with the proposed Configuration-Aware Two-stage Training (CAT); teacher trajectories for cold-start RFT are generated by Qwen3-235B-A22B-Thinking. Qwen2.5-72B-Instruct is used separately as an LLM-as-Judge (temperature=0.0, top_p=1.0) to classify emergent adaptive behaviors from trajectories in the appendix analysis (Table 3). Baselines span Vanilla Agent, OpenHands, WebSailor, SWE-Agent, Co-Sight, SWE-Search, AutoAgent, OWL, ReSum, and OAgents.</t>
+          <t>Six open-source LLM agent backbones (Qwen-3, GPT-oss, Llama-4, GLM-4.5, Kimi-K2, Grok-2) and three closed-source models with proprietary chat templates (GPT-4o, Grok-3, Gemini-2.5-Pro/'Gemini-pro'), plus a Gemma-3 template used to extend the attack template suite to seven total templates for transferability experiments. GPT-4.1 is additionally used as an auxiliary tool to synthetically generate the multi-turn persuasive dialogue payloads.</t>
         </is>
       </c>
       <c r="F261" s="5" t="n"/>
@@ -11350,7 +11370,7 @@
       <c r="H261" s="5" t="n"/>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11380,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -11375,7 +11395,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Five evaluation datasets from four long-horizon agent benchmarks: FRAMES and xbench (deep research), GAIA and GAIA(WS) (a 103-sample WebSailor subset solvable via search/browsing only) for general AI assistant tasks, and SWE-bench Lite for software engineering. MathVista is used only as a supplementary training dataset, not for evaluation.</t>
+          <t>Two established indirect prompt injection benchmarks: InjecAgent (Zhan et al., 2024) and AgentDojo (Debenedetti et al., 2024). Metrics are Attack Success Rate (ASR, percentage of injected malicious instructions successfully executed by the agent) and Utility (percentage of benign user tasks still completed correctly despite the injection attempt), both reported with 95% Wilson-interval confidence bounds.</t>
         </is>
       </c>
       <c r="F262" s="5" t="n"/>
@@ -11383,7 +11403,7 @@
       <c r="H262" s="5" t="n"/>
       <c r="I262" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11413,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -11408,7 +11428,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf outperforms all static-configuration, pre-execution-optimization, planner-worker, and configuration-patching baselines across both model scales: on Qwen3-14B it averages 37.8% versus the Vanilla Agent's 25.9%, and on Qwen3-8B it averages 31.0% versus 15.2% (Table 1), a roughly 28.8-point gain over the static-configuration baseline as stated in the abstract. Ablating CAT (Table 2) shows progressive gains on Qwen3-8B from a 16.5% Vanilla Agent average to 27.3% for the best baseline to 35.3% for full ToolSelf+RFT+KTO. On GAIA specifically (Table 5), ToolSelf raises accuracy from 19.7% (Vanilla Agent) to 35.2% while using only 11.6K/39.4K/71.0K total tokens per task at Level 1/2/3, versus Co-Sight's 229K/261K/315K tokens -- roughly 19.8x/6.6x/4.4x higher token efficiency, attributed to agent-driven context management keeping max input length bounded near 13K-15K tokens even as exploration deepens. Component ablation (Table 6) shows removing context management drops GAIA accuracy from 35.2% to 33.9%, and removing the 'Knowledge' component causes the largest drop (to 27.3%), with sub-goal and toolbox reconfiguration also contributing measurably.</t>
+          <t>ChatInject substantially outperforms plain-text prompt injection: average ASR rose from 5.18% (Default InjecPrompt baseline) to 32.05% on AgentDojo and from 15.13% to 45.90% on InjecAgent, with the Multi-turn + ChatInject variant reaching an average 52.33% ASR on InjecAgent (versus only a modest 13.8% average gain from plain Default Multi-turn alone), demonstrating strong synergy between forged role tokens and persuasive multi-turn framing. Effectiveness varied by model template structure: models with clear, explicit role delimiters (Qwen-3, GLM-4.5) showed the largest ASR gains (e.g., Qwen-3's InjecAgent ASR rose from 8.5% to 39.4% with ChatInject and to 65.9% with Multi-turn+ChatInject), while Grok-2, whose template lacks strong role delimiters, showed only minor gains. Cross-model transferability was strong and predictable from template similarity: on Qwen-3, injecting the most template-similar foreign wrapper (Kimi-K2) yielded over a 20-point ASR increase versus the least similar (Grok-2) wrapper, and closed-source models -- despite having unknown, proprietary templates -- were still substantially compromised by open-source template wrappers (e.g., average ASR on closed-source targets rose from 4.4% default to 29.6% using the Qwen-3 template on InjecAgent), with family-aligned transfer (e.g., GPT-oss to GPT-4o, Grok-2 to Grok-3, Gemma-3 to Gemini-pro) being especially effective, implying many closed-source chat templates structurally resemble open-source ones. A mixture-of-templates (MoT) approach -- bundling all candidate templates into one payload for use against an unknown target backbone -- consistently exceeded the Default InjecPrompt baseline with substantially lower variance across random seeds than picking a single arbitrary foreign template. Standard defenses were largely ineffective: three prompt-based/runtime defenses (instructional prevention, data delimiting, user instruction repetition) all showed higher ASR against ChatInject and Multi-turn attacks than the no-defense baseline, and while two external detector-based defenses (a prompt injection detector and Lakera Guard) reduced ASR somewhat, they incurred severe Utility loss via high false-positive rates that stall the agent pipeline (consistent with prior findings), and even Lakera Guard -- considered a relatively strong detector -- exhibited this same coarse-grained failure mode. Finally, ChatInject remained robust to a natural countermeasure (template-stripping via rule-based parsing): applying light character-level perturbations (10% random remove/replace/insert edits) to the forged template tokens preserved most attack efficacy while defeating format-stripping defenses, with insertion-based perturbations causing the smallest ASR drop for single-template attacks and removal-based perturbations causing the smallest drop for the redundant MoT variant.</t>
         </is>
       </c>
       <c r="F263" s="5" t="n"/>
@@ -11416,7 +11436,7 @@
       <c r="H263" s="5" t="n"/>
       <c r="I263" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11446,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -11441,7 +11461,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>General-purpose static-configuration agents (Vanilla Agent, OpenHands); task-specialized static agents (WebSailor, SWE-Agent, Co-Sight, SWE-Search); a pre-execution optimization method (AutoAgent); a planner-worker orchestration method (OWL); and configuration-patching methods (ReSum, OAgents). All are organized under a taxonomy distinguishing when/how configuration adaptation occurs relative to execution.</t>
+          <t>Default InjecPrompt (standard plain-text prompt injection with an attention-grabbing prefix) and Default Multi-turn (a plain-text, non-template-formatted multi-turn persuasive dialogue variant) serve as the primary baselines that ChatInject and its Multi-turn + ChatInject variant are compared against throughout; for defenses, five standard indirect-injection mitigations are evaluated as defense baselines: a Prompt Injection Detector (ProtectAI.com), Lakera Guard Detector, Instructional Prevention, Data Delimiters, and User Instruction Repetition.</t>
         </is>
       </c>
       <c r="F264" s="5" t="n"/>
@@ -11449,7 +11469,7 @@
       <c r="H264" s="5" t="n"/>
       <c r="I264" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11479,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -11474,7 +11494,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a capability/systems paper on unifying task execution and runtime self-reconfiguration, not a security paper. The incidental failure mode of interest is that decoupled or static-configuration agents (fixed persona/toolbox/context strategy chosen before or separately from execution) underperform and waste tokens relative to agents that can dynamically reconfigure their own sub-goals, strategy, toolbox, and context management as part of a single unified action space during execution.</t>
+          <t>Formal threat model (Section 3.1, following Zhan et al. 2024): an LLM agent L equipped with a toolset T receives a user instruction, invokes a tool, and receives a tool response RTu in which an attacker has embedded a malicious instruction Ia (or an entire fabricated multi-turn conversation Ca containing Ia). The attack succeeds if the agent executes Ia, typically via invoking a second, attacker-chosen tool to perform a harmful action (e.g., changing a password, sending money, leaking messages). The attacker is assumed to have no access to the user's original instruction or the agent's internal system prompt/reasoning -- their only capability is manipulating the content of the tool response returned to the agent, i.e., a pure indirect (not direct) prompt injection setting. The core novel mechanism exploited is that agents rely on role-based chat-template special tokens (system &gt; user &gt; assistant &gt; tool output priority hierarchy) to enforce instruction precedence, and the attacker forges these special tokens within the low-priority tool output to make the model misinterpret injected content as originating from a higher-priority role.</t>
         </is>
       </c>
       <c r="F265" s="5" t="n"/>
@@ -11482,7 +11502,7 @@
       <c r="H265" s="5" t="n"/>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11492,7 +11512,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -11507,7 +11527,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'A.8 Limitations' section (brief, two sentences). First, the work focuses on whether an agent can internalize configuration of sub-goal, strategy, toolbox, and context management as learnable actions under a fixed global tool pool: ToolSelf can dynamically select tools from the existing pool at runtime but does not create new tools for unseen tasks, with dynamic tool creation/synthesis noted as orthogonal future work. Second, because self-reconfiguration introduces additional model calls, deploying ToolSelf in real-time systems may incur extra latency.</t>
+          <t>The paper has an explicit appendix section titled 'Limitations and Future Work' (Appendix B) with three named points: (1) Synthetic Multi-turn Generation -- the persuasive multi-turn dialogues are synthetically generated using GPT-4.1 rather than sourced from real-world persuasive conversations, which may not capture the full diversity of naturally occurring persuasion tactics, though the authors argue GPT-4.1's strong benchmark performance and their manual review process help ensure dialogue quality, and suggest future work validate findings with human-crafted or naturally occurring conversations; (2) Limited Internal Analysis -- resource constraints prevented detailed mechanistic/attention-level analysis of how chat templates influence model behavior at the representational level (though instruction hierarchy and tool-output formatting were analyzed), leaving interpretability-based investigation of attention patterns during template-based attacks as future work; (3) Defense Limitations -- existing defenses only provide partial mitigation and incur significant trade-offs (longer prompts, added runtime cost, high false-positive rates degrading Utility), and critically, ChatInject variants consistently outperform the baseline Default InjecPrompt even when defenses are deployed, underscoring the need for more sophisticated, template-aware and multi-turn-aware defense mechanisms.</t>
         </is>
       </c>
       <c r="F266" s="5" t="n"/>
@@ -11515,7 +11535,7 @@
       <c r="H266" s="5" t="n"/>
       <c r="I266" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11545,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -11540,7 +11560,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf proposes unifying task execution and runtime self-reconfiguration within a single policy's action space, framing configuration updates (to sub-goal, execution strategy/persona, action toolbox, and cross-step context management) as a standardized tool interface the agent itself can invoke mid-trajectory, rather than treating adaptation as a separate pre-execution planning step (as in AutoAgent) or a decoupled planner-worker split (as in OWL). The execution agent is trained via Configuration-Aware Two-stage Training (CAT): a rejection-sampling fine-tuning (RFT) cold-start stage using teacher trajectories from Qwen3-235B-A22B-Thinking, followed by trajectory-level KTO (Kahneman-Tversky Optimization) reinforcement learning refinement using binary feedback. Because configuration generation happens inside the same execution agent's context (rather than being delegated to a separate LLM instance, as tested in an ablation), the agent retains full task context when deciding how to reconfigure itself. Appendix analysis using an LLM-as-Judge (Qwen2.5-72B-Instruct) over concatenated stage-level sub-goal trajectories shows CAT progressively improves emergent adaptive behaviors -- long-horizon task planning, self-refinement, self-correction, verification, and strategy adaptation -- with the largest gains in self-correction (40.0% to 49.1%) and strategy adaptation (35.2% to 51.5%) from base ToolSelf to full RFT+KTO training. The paper also reports a maximum-reconfiguration-cap analysis and task-adaptive tool-selection pattern study (Tables 8-9, not detailed here) as further characterizations of the learned reconfiguration behavior.</t>
+          <t>This paper identifies and exploits a previously underexplored indirect prompt injection vulnerability: LLM agents' structural dependence on chat templates (special role tokens like &lt;system_tag&gt;, &lt;user_tag&gt;, &lt;assistant_tag&gt; used to enforce an instruction-priority hierarchy of system &gt; user &gt; assistant &gt; tool output) and their susceptibility to contextual manipulation via persuasive multi-turn dialogue framing. The authors introduce ChatInject, which formats a malicious payload -- embedded within an otherwise low-priority tool response -- to mimic the target model's native chat template syntax, causing the model to misinterpret the forged tokens as marking genuinely higher-priority (system- or user-level) content and thus bypass the intended role hierarchy that instruction-hierarchy training is meant to enforce. Building on this, the authors develop a Multi-turn variant that embeds an entire fabricated, persuasively-structured conversation history (with forged alternating user/assistant turns) within a single one-shot tool-output injection, effectively adapting the gradual-persuasion strategy known to be effective in multi-turn jailbreaking to the structurally constrained, one-shot nature of indirect prompt injection. Across six open-source and three closed-source frontier LLM agents evaluated on the InjecAgent and AgentDojo benchmarks, ChatInject and its Multi-turn variant substantially and consistently outperform standard plain-text injection baselines in Attack Success Rate, an agentic extension exploiting model-specific reasoning (&lt;think&gt;) and tool-calling (&lt;tool&gt;) template tokens further amplifies attack effectiveness, the attack transfers well across models in proportion to embedding-measured template similarity (even compromising closed-source models with unknown proprietary templates, especially when the injected template comes from an architecturally related open-source model family), a mixture-of-templates strategy provides a robust, stable attack even when the attacker doesn't know the target's specific backbone model, and the attack resists both standard prompt-based/detector-based defenses (which either fail outright or trade off severe utility degradation for partial mitigation) and rule-based template-stripping countermeasures via simple character-level perturbations to the forged tokens -- collectively demonstrating a structural, largely unaddressed vulnerability class in how modern agent systems parse and trust chat-template-formatted content.</t>
         </is>
       </c>
       <c r="F267" s="5" t="n"/>
@@ -11548,7 +11568,7 @@
       <c r="H267" s="5" t="n"/>
       <c r="I267" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11578,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -11581,7 +11601,7 @@
       <c r="H268" s="5" t="n"/>
       <c r="I268" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11591,7 +11611,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11606,7 +11626,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F269" s="5" t="n"/>
@@ -11614,7 +11634,7 @@
       <c r="H269" s="5" t="n"/>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11644,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11647,7 +11667,7 @@
       <c r="H270" s="5" t="n"/>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11657,7 +11677,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11672,7 +11692,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F271" s="5" t="n"/>
@@ -11680,7 +11700,7 @@
       <c r="H271" s="5" t="n"/>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11710,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11705,7 +11725,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>tool-metadata</t>
         </is>
       </c>
       <c r="F272" s="5" t="n"/>
@@ -11713,7 +11733,7 @@
       <c r="H272" s="5" t="n"/>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11743,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11738,7 +11758,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F273" s="5" t="n"/>
@@ -11746,7 +11766,7 @@
       <c r="H273" s="5" t="n"/>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11776,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -11779,7 +11799,7 @@
       <c r="H274" s="5" t="n"/>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11809,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11812,7 +11832,7 @@
       <c r="H275" s="5" t="n"/>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11822,7 +11842,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -11837,7 +11857,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>reasoning</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F276" s="5" t="n"/>
@@ -11845,7 +11865,7 @@
       <c r="H276" s="5" t="n"/>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11875,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -11870,7 +11890,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F277" s="5" t="n"/>
@@ -11878,7 +11898,7 @@
       <c r="H277" s="5" t="n"/>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11908,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -11903,7 +11923,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F278" s="5" t="n"/>
@@ -11911,7 +11931,7 @@
       <c r="H278" s="5" t="n"/>
       <c r="I278" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11941,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -11936,7 +11956,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>No unrestricted public release. The paper explicitly states it provides 'a reviewer-facing package in which the main manuscript, a single supplementary document, and a single source-code-and-artifacts archive support inspection without unrestricted public release of the full operational environment' -- i.e., materials are available for reviewer/editorial inspection only, not openly published to the public (no GitHub/HuggingFace link given).</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F279" s="5" t="n"/>
@@ -11944,7 +11964,7 @@
       <c r="H279" s="5" t="n"/>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11974,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -11969,7 +11989,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Not explicitly named by version in the extracted text -- the paper describes 'Full MAS' (the complete ADEMA multi-agent system) versus a 'Single-model Baseline,' with an AutoGen framework used as an external 'horizontal baseline' for comparison in Section 6.9. Specific underlying LLM model names/versions were not found in the excerpted sections.</t>
+          <t>Target LLMs: Llama-2-7B-chat, Llama-3-8B-Instruct, Llama-3-70B-Instruct, Llama-3.3-70B-Instruct, Claude-3-Haiku, Claude-3.5-Sonnet, GPT-3.5, GPT-4o; Target retrievers: text-embedding-ada-002, Contriever, Contriever-ms, Sentence-BERT-tb; Attacker shadow LLMs: Llama-3.3-70B (gradient-free attack), Llama-3-8B (gradient-based attack), plus 8 shadow LLMs tested in transfer ablations</t>
         </is>
       </c>
       <c r="F280" s="5" t="n"/>
@@ -11977,7 +11997,7 @@
       <c r="H280" s="5" t="n"/>
       <c r="I280" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -11987,7 +12007,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -12002,7 +12022,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>No external standard benchmark; evaluation uses the paper's own custom evidence package: a four-scenario showcase (code, literature, resume, latam), a fixed 60-run mechanism matrix (5 configurations x 4 scenarios x 3 seeds), targeted micro-ablation and artifact-chain supplements, a Final Artifact Completeness Proxy (FACP), a forced interruption/recovery test, and a 'repaired protocol-level benchmark' in which a code-oriented evaluation serves as the primary quality-sensitive mechanism block, with AutoGen included as a paradigm-contrast horizontal baseline.</t>
+          <t>MetaTool (21,127 instances, 199 benign tool documents sourced from OpenAI Plugins); ToolBench (126,486 instruction-tuning samples, 9,650 deduplicated benign tool documents from RapidAPI); 10 hand-designed target tasks per dataset, each with 100 semantically varied task descriptions (1,000 target task descriptions per dataset total)</t>
         </is>
       </c>
       <c r="F281" s="5" t="n"/>
@@ -12010,7 +12030,7 @@
       <c r="H281" s="5" t="n"/>
       <c r="I281" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12040,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -12035,7 +12055,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>Across the fixed 60-run matrix, 59 of 60 runs were artifact-valid; the single invalid run occurred specifically when checkpoint/resume was removed, in the interruption-sensitive 'resume' scenario (dropping success from 100% to 66.7%, 2/3 successes) -- described as the clearest and only completion-critical mechanism-level finding in the study. All other ablations (removing dual evaluation, removing segment synthesis) left completion success unchanged at 100% across all 12 scenario-seed combinations, indicating these mechanisms are 'governance-intensive' and 'continuity-preserving/compression-oriented' respectively rather than binary prerequisites for task completion -- their effect instead manifests in trajectory discipline, correction/confidence behavior, and cost-quality tradeoffs rather than raw completion rate. The Full MAS configuration was substantially slower than the single-model baseline (916.0s mean runtime vs. 292.0s), interpreted as the architectural cost of explicit epistemic bookkeeping, heterogeneous evaluation, persistence, and artifact assembly ('governance overhead') rather than a defect, since both achieved 100% success. A code-oriented benchmark evaluation is identified as the clearest quality-sensitive mechanism block, where the full ADEMA method most clearly separates itself from ablated variants and the single-author baseline (scores in the 7.05-7.63 range vs. 6.50-6.90 for baselines). The interruption-sensitive rerun test confirms ADEMA can restore a usable evidence chain (reports, checkpoints, round traces, raw/final artifacts) after deliberate forced disruption. The AutoGen horizontal-baseline comparison is presented as illustrative rather than a competitive benchmark, showing how a stateless conversational multi-agent paradigm differs qualitatively from ADEMA's stateful, artifact-first orchestration paradigm under the same long-horizon task family.</t>
+          <t>ToolHijacker achieves very high attack success rates (ASR) across all 8 target LLMs and both datasets, e.g. on GPT-4o: 96.7% (gradient-free) and 92.2% (gradient-based) ASR on MetaTool, and 88.2%/83.9% on ToolBench - dramatically exceeding all 7 baseline attacks (5 manual: naive 6.0%, escape characters 28.2%, context ignore 1.2%, fake completion 14.5%, combined 9.7%; and the strongest automated baselines JudgeDeceiver 30.2% and PoisonedRAG 39.3%, all measured on GPT-4o/MetaTool). ToolHijacker also achieves near-perfect Attack Hit Rate (AHR, the malicious tool being retrieved into the top-k candidates in the first place) - 99.9-100% on MetaTool despite injecting only a single malicious tool document among thousands of benign ones - and is robust across all 4 tested retrievers (100% AHR for 3 of 4; 95-99% ASR for text-embedding-ada-002), across different top-k retrieval depths and shadow retrieval sizes k', and transfers effectively even when the shadow LLM used for attack optimization differs architecturally from the actual target LLM (e.g. shadow Llama-3.3-70B, target GPT-4o, achieves 96.7% ASR). Malicious tool documents generated by ToolHijacker are shown to be short and statistically indistinguishable from benign tool documents by token length alone, unlike the baseline attacks. Ablation studies confirm both of ToolHijacker's two optimized subsequences are independently necessary: removing the selection-objective subsequence S drops gradient-free ASR from 100% to just 5% (while AHR remains near-perfect), and removing the retrieval-objective subsequence R drops gradient-free AHR from 100% to 65%, confirming the two-phase (retrieval-then-selection) optimization design is essential to achieving an end-to-end attack.</t>
         </is>
       </c>
       <c r="F282" s="5" t="n"/>
@@ -12043,7 +12063,7 @@
       <c r="H282" s="5" t="n"/>
       <c r="I282" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12073,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12068,7 +12088,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>Five internal configurations compared within the fixed 60-run matrix: Full MAS (complete ADEMA), Single-model Baseline, w/o Checkpoint/Resume, w/o Dual Evaluation, and w/o Segment Synthesis (systematic component-ablation design). AutoGen is used as an external 'horizontal baseline' for a qualitative paradigm-level comparison (stateless conversational orchestration vs. ADEMA's stateful knowledge-state orchestration), explicitly described as interpretive rather than a matched, framework-fair tournament-style comparison.</t>
+          <t>Five manual/heuristic prompt injection attacks (Naive Attack, Escape Characters, Context Ignore, Fake Completion, Combined Attack) and two automated optimization-based attacks (JudgeDeceiver, adapted from LLM-as-judge manipulation; PoisonedRAG, adapted from RAG knowledge-base poisoning), all applied to the tool-selection setting as comparison baselines against ToolHijacker's gradient-free and gradient-based variants</t>
         </is>
       </c>
       <c r="F283" s="5" t="n"/>
@@ -12076,7 +12096,7 @@
       <c r="H283" s="5" t="n"/>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -12086,7 +12106,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12101,7 +12121,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. ADEMA is a reliability/architecture paper for long-horizon multi-agent knowledge synthesis, not a security paper; there is no adversary, attacker, or malicious-input model anywhere in the paper. The incidental failure mode of interest is knowledge-state drift and evidence-chain fracture: long-horizon LLM agent tasks failing not because a single correct answer is unattainable, but because knowledge states drift across rounds, intermediate commitments remain implicit (not externalized as inspectable state), and interruptions (session drops, forced pauses) fracture the evolving evidence chain -- ADEMA's eight mechanisms (explicit epistemic bookkeeping, heterogeneous dual-evaluator governance, adaptive task-mode switching, reputation-shaped resource allocation, checkpoint-resumable persistence, segment-level memory condensation, artifact-first assembly, and final-validity checking with safe fallback) are designed specifically to make this failure mode governable and recoverable rather than to defend against any adversarial actor.</t>
+          <t>A no-box threat model in which the attacker cannot access the contents of other tool documents in the target tool library, cannot obtain the actual retrieval parameter k or the top-k retrieved tool documents, cannot access the target retriever's or target LLM's parameters, and cannot directly query the target retriever or target LLM; the attacker knows the semantic nature of the target task but has no access to the real target task descriptions Q (disjoint from any shadow set Q' the attacker constructs). The attacker's only real-world capability is to construct and publish a malicious tool document (tool name plus tool description) to an open, third-party-accessible platform (e.g. Hugging Face Hub, Apify, PulseMCP) that the target LLM agent's tool library draws from, consistent with prior LLM-agent-security assumptions and recent findings on Model Context Protocol (MCP) tool poisoning; to design and validate the attack offline, the attacker independently constructs a disjoint shadow task-description set, shadow tool documents (both task-relevant and task-irrelevant, to simulate the real tool library), and deploys a shadow retriever and shadow LLM. The attack's goal is to have the malicious tool consistently selected over benign alternatives for an attacker-chosen target task, regardless of the exact semantic phrasing a user happens to use for that task, exploiting LLM agents' select-and-execute paradigm in which a selected tool is invoked without further human verification, potentially enabling unauthorized data access, privacy breaches, or other harmful downstream actions once selected.</t>
         </is>
       </c>
       <c r="F284" s="5" t="n"/>
@@ -12109,7 +12129,7 @@
       <c r="H284" s="5" t="n"/>
       <c r="I284" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -12119,7 +12139,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -12134,7 +12154,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Threats to validity' section (Section 8) with four numbered points. First, the evaluation emphasizes explicit knowledge-state progression, recoverable continuity, and artifact integrity rather than external gold-standard semantic-correctness tasks, which improves alignment with the architecture under study but limits direct comparability with standard benchmark-style evaluations. Second, the quality proxies used (reference presence, mechanism presence, artifact-chain completeness) are intentionally lightweight structural indicators that do not by themselves establish factual correctness, domain optimality, or semantic sufficiency -- the paper should be read as a knowledge-state architecture study with bounded outcome-level quality evidence rather than a correctness benchmark. Third, the repeated matrix probes only a limited set of ablations, supporting a strong (binary, completion-critical) interpretation only for checkpoint persistence, while dual evaluation, segment synthesis, and dynamic governance receive only a layered interpretation (trajectory-shaping, control-discipline, cost-quality effects) rather than universal-necessity claims. Fourth, the studied implementation is one concrete architecture rather than a broad family of systems, so conclusions should be read as mechanism-local, reference-architecture evidence rather than a universal law for all multi-agent systems; the AutoGen comparison is explicitly noted as interpretive/paradigm-illustrative rather than a fair, matched engineering competition.</t>
+          <t>No explicit numbered Limitations section appears within the methodology and main-results pages read (the paper continues into further ablations and appendices beyond what was reviewed); the paper's own ablation results do reveal boundary conditions on attack effectiveness rather than being framed as limitations: gradient-based ASR is notably more sensitive to the choice of shadow LLM than gradient-free ASR (e.g. dropping to 34% for a weak shadow LLM/target combination), attack performance depends on the shadow retrieval-size parameter k' relative to the number of true ground-truth tools for a task (small k' values yield suboptimal selection-objective optimization), and the underlying assumption that the attacker can publish a tool document to an accessible open platform, while argued to be realistic and consistent with prior work, is nonetheless a real precondition for the attack to be mountable at all.</t>
         </is>
       </c>
       <c r="F285" s="5" t="n"/>
@@ -12142,7 +12162,7 @@
       <c r="H285" s="5" t="n"/>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12172,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -12167,7 +12187,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>This paper presents ADEMA, a knowledge-state orchestration architecture (rather than a generic multi-agent runtime) targeting a specific reliability failure mode in long-horizon LLM agent tasks: such tasks often fail not because a single correct final answer is unattainable in principle, but because the evolving knowledge state drifts silently across rounds, intermediate commitments and hypotheses remain implicit rather than explicitly tracked, and interruptions (forced pauses, session breaks) fracture the accumulated evidence chain with no principled recovery path. To address this, ADEMA combines eight interacting mechanisms implemented as concrete runtime objects (not narrative abstractions) in reviewed source code: explicit epistemic bookkeeping (externalizing hypothesis state and milestone status as inspectable system state rather than implicit message accumulation), heterogeneous dual-evaluator governance (merging assessments from structurally different evaluators), adaptive task-mode switching, reputation-shaped dynamic resource/budget allocation across agent roles, checkpoint-resumable persistence (allowing the system to survive and recover from deliberate interruption), segment-level memory condensation (compressing long interaction history to stabilize extended reasoning windows and control context growth), artifact-first deliverable assembly (treating code, reports, section drafts, and traces as structured explicit knowledge artifacts with lineage rather than transient chat turns), and final-validity checking with safe fallback. The evaluation draws entirely on existing/prior experimental materials (a four-scenario showcase package, a fixed 60-run mechanism-ablation matrix, targeted micro-ablations, a repaired code-oriented protocol-level benchmark, and a forced-interruption recovery test) rather than fresh data collection, and is explicitly reorganized in this paper to surface the clearest headline evidence: checkpoint/resume persistence is the only mechanism whose removal caused an outright invalid (failed) run, and it did so specifically in the interruption-sensitive scenario, establishing it as the architecture's sole clearly completion-critical component, while dual evaluation, segment synthesis, and dynamic governance are argued to function as supporting control mechanisms shaping trajectory discipline, artifact progression quality, and cost-quality tradeoffs rather than as universal binary prerequisites for task completion.</t>
+          <t>Introduces ToolHijacker, the first prompt injection attack specifically targeting the tool-selection process of LLM agents in a realistic no-box setting, where an attacker has no access to the target task descriptions, retriever, LLM, or tool library contents beyond the ability to publish a malicious tool document to an open, third-party-accessible tool platform. The paper formalizes the standard two-step tool-selection pipeline (a dual-encoder retriever selects the top-k most relevant tool documents for a user's task description, then an LLM selects the single most appropriate tool from that candidate set) and observes that existing prompt injection methods are suboptimal against it: manual heuristic attacks generalize poorly, and prior automated attacks either focus only on the selection phase (JudgeDeceiver) or only on retrieval-phase corpus poisoning for a single fixed query (PoisonedRAG), neither jointly and robustly manipulating both phases across the full space of ways a user might phrase the same underlying task. ToolHijacker addresses this by formulating malicious tool document crafting as an optimization problem decomposed into two independently-optimized sub-objectives - a retrieval subsequence R that maximizes similarity between the malicious tool document and a broad, attacker-constructed shadow set of semantically varied task descriptions (ensuring the malicious document is reliably retrieved into the top-k candidates regardless of exact query phrasing), and a selection subsequence S that, once concatenated with R to form the complete malicious tool description, maximizes the likelihood that a shadow LLM selects the malicious tool over the shadow retrieved set's other candidates - solved via either a gradient-free LLM-driven tree-of-attack search or a gradient-based HotFlip-style discrete token optimization combining alignment, consistency, and perplexity loss terms. Evaluated across 8 target LLMs, 4 retrievers, and two large-scale real-world tool-selection benchmarks (MetaTool, ToolBench), ToolHijacker achieves substantially higher attack success rates than five manual and two prior automated prompt injection baselines, near-perfect retrieval-phase hit rates from injecting only a single malicious tool document among thousands of benign ones, robust transferability across shadow-to-target LLM/retriever combinations, and malicious tool documents that remain statistically indistinguishable from benign ones by simple length-based heuristics - while the paper also evaluates prevention-based defenses (StruQ, SecAlign) and detection-based defenses (known-answer detection, DataSentinel, perplexity and perplexity-windowed detection), finding all of them largely insufficient against ToolHijacker and concluding new, tool-selection-specific defense mechanisms are urgently needed.</t>
         </is>
       </c>
       <c r="F286" s="5" t="n"/>
@@ -12175,7 +12195,7 @@
       <c r="H286" s="5" t="n"/>
       <c r="I286" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -12185,7 +12205,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -12208,7 +12228,7 @@
       <c r="H287" s="5" t="n"/>
       <c r="I287" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12238,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -12233,7 +12253,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F288" s="5" t="n"/>
@@ -12241,7 +12261,7 @@
       <c r="H288" s="5" t="n"/>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12271,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -12274,7 +12294,7 @@
       <c r="H289" s="5" t="n"/>
       <c r="I289" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12304,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -12307,7 +12327,7 @@
       <c r="H290" s="5" t="n"/>
       <c r="I290" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12337,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -12332,7 +12352,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="F291" s="5" t="n"/>
@@ -12340,7 +12360,7 @@
       <c r="H291" s="5" t="n"/>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12370,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -12365,7 +12385,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>persistence-backdoor</t>
         </is>
       </c>
       <c r="F292" s="5" t="n"/>
@@ -12373,7 +12393,7 @@
       <c r="H292" s="5" t="n"/>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12403,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -12406,7 +12426,7 @@
       <c r="H293" s="5" t="n"/>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12436,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -12439,7 +12459,7 @@
       <c r="H294" s="5" t="n"/>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12449,7 +12469,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -12464,7 +12484,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>execution</t>
         </is>
       </c>
       <c r="F295" s="5" t="n"/>
@@ -12472,7 +12492,7 @@
       <c r="H295" s="5" t="n"/>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12502,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -12505,7 +12525,7 @@
       <c r="H296" s="5" t="n"/>
       <c r="I296" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12535,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -12538,7 +12558,7 @@
       <c r="H297" s="5" t="n"/>
       <c r="I297" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12568,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -12563,7 +12583,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>Released. The abstract states: 'Our benchmark is available at https://github.com/xiewwee11/MemEvoBench.' This is an actual GitHub repository link provided by the authors, not anonymized or withheld.</t>
+          <t>Code and data publicly released at https://github.com/RUC-NLPIR/ClawTrojan, covering both the ClawTrojan benchmark (annotation fields, evaluation verdicts, runnable sandbox artifacts for each attack step) and the DASGuard defense implementation.</t>
         </is>
       </c>
       <c r="F298" s="5" t="n"/>
@@ -12571,7 +12591,7 @@
       <c r="H298" s="5" t="n"/>
       <c r="I298" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12601,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -12596,7 +12616,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Nine representative LLMs from diverse institutions: GPT-4o, GPT-5, Gemini-2.5-Pro, Claude-3.7-Sonnet, Llama-3.3-70B-Instruct-Turbo, Qwen3-32B, Qwen3-Next-80B-A3B-Instruct, Qwen3-235B-A22B-Instruct, and DeepSeek-V3.2, all evaluated at temperature 0.0. Claude-Opus-4-5-20251101 and GPT-5.2 are used as auxiliary models for memory-pool construction and as the LLM judge, respectively.</t>
+          <t>Three raw agent backbones tested as attack targets: GPT-5.4 (primary, used as base agent and LLM-as-judge in main experiments), GLM-5.1, and DeepSeek-V4-Flash. Nine defense baselines compared: three raw undefended agents (GPT-5.4, GLM-5.1, DeepSeek-V4-Flash) plus six defended-agent methods -- StruQ (structured-prompt front-end defense), ClawKeeper (OpenClaw plugin-gate adaptation), MELON (counterfactual action gate), PromptShield-1B and PromptShield-8B (detector gates at two model scales), and CaMeL (data-flow/capability-gate adaptation) -- alongside the proposed DASGuard defense.</t>
         </is>
       </c>
       <c r="F299" s="5" t="n"/>
@@ -12604,7 +12624,7 @@
       <c r="H299" s="5" t="n"/>
       <c r="I299" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12614,7 +12634,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -12629,7 +12649,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench itself, introduced by this paper: a QA-style scenario (misleading memory injection) spanning 7 high-risk domains (healthcare, mental health, finance, food safety, privacy, transportation, customer service) and 36 distinct risk types, yielding 108 test queries; and a Workflow-style scenario (noisy tool returns) built from 20 interaction environments (e.g., WebShop, ChatApp, Email) and 8 risk categories adapted from AgentSafetyBench, yielding 83 test cases. Additional evaluation integrates the A-MEM agent memory framework to test under a more realistic memory system.</t>
+          <t>The paper's own ClawTrojan benchmark: a suite of multi-step trojan/backdoor attack chains in an OpenClaw-style simulated local agentic workspace, comprising 339 positive (attack) samples spanning 919 evaluated steps, plus a clean/negative split of 23 negative-or-borderline samples and 92 clean steps for false-positive testing. Compared against and cross-validated on two prior indirect-prompt-injection benchmarks (AgentDojo and InjecAgent), on which GPT-5.4 and GLM-5.1 both achieve near-zero (0.000) ASR without any defense, empirically motivating the need for the new multi-step benchmark.</t>
         </is>
       </c>
       <c r="F300" s="5" t="n"/>
@@ -12637,7 +12657,7 @@
       <c r="H300" s="5" t="n"/>
       <c r="I300" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12667,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -12662,7 +12682,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>Under vanilla prompting, all 9 models show high vulnerability: mean Attack Success Rate (ASR) of 75.9%/75.2%/80.1% across rounds 1/2/3 (no clear worsening), but with biased user feedback ASR rises clearly round-by-round to 71.6%/84.9%/87.8%. Safety prompting (+SafePrompt) reduces QA-Style Rd.1 ASR from 76.2% to 55.5% but 'fails entirely' on Workflow Style and is undermined further by biased feedback (Rd.3 ASR 69.6% with feedback vs 54.5% without). The proposed +ModTool defense (memory correction tool) substantially outperforms both, e.g. for Gemini-2.5-Pro reducing ASR to 19.0/13.0/14.0% (Rd.1-3) vs 67.0/55.0/55.0% (Vanilla) and 46.0/33.0/32.0% (+SafePrompt); memory-independent (no-memory) control experiments show substantially lower ASR than memory-enabled settings, confirming risk originates from memory structure rather than model knowledge gaps.</t>
+          <t>In the OpenClaw-style simulated workspace, undefended GPT-5.4 is compromised by ClawTrojan's multi-step trojan attacks at a 95.5% step attack success rate (ASR), 89.1% full-chain ASR, and 92.2% average chain penetration, while undefended GLM-5.1 (90.1% ASR) and DeepSeek-V4-Flash (88.0% ASR) show similarly severe vulnerability -- in sharp contrast to near-zero ASR for the same models on existing single-turn benchmarks AgentDojo and InjecAgent (0.000 ASR in all four no-defense external checks reported in Table 9). Existing prompt-formatting, detector, and single-step action-gating defenses reduce ASR only modestly (ClawKeeper 94.3%, StruQ 93.8%, MELON 92.6%, PromptShield-1B/8B 91.2%/88.7%) because they inspect only the current prompt or immediate action rather than tracing content provenance across steps; the best prior defense, CaMeL (data-flow/capability gating), still leaves 74.3% ASR. The proposed DASGuard defense reduces ASR to 15.8% (full-chain ASR 5.9%, penetration 10.1%), an approximately 6x reduction versus the next-best defense, while maintaining 87.0% utility on clean tasks (versus GPT-5.4's undefended 98.9%) at a moderate cost of 13.0% false-positive rate and 6.5% overblocking. Ablations show removing source-label tracking causes the largest degradation (ASR jumps from 15.8% to 92.7%, a +76.9 point increase), confirming that provenance tracking across steps -- not single-step detection -- is the core mechanism driving DASGuard's effectiveness; removing cross-step reasoning or memory matching causes smaller but still meaningful degradations (+4.3 and +3.4 points respectively).</t>
         </is>
       </c>
       <c r="F301" s="5" t="n"/>
@@ -12670,7 +12690,7 @@
       <c r="H301" s="5" t="n"/>
       <c r="I301" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12700,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -12695,7 +12715,7 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>Three configurations compared per model: Vanilla (standard system prompt only), +SafePrompt (explicit safety guidelines added to system prompt), and +ModTool (agents equipped with a correct_memory tool, plus a web_search tool for QA Style). Each tested with and without simulated biased user feedback. A memory-independent control (no memory access, relying solely on intrinsic knowledge) and an A-MEM-integrated realistic memory system are also compared against the paper's simplified memory-update protocol.</t>
+          <t>Nine baselines spanning the main defense families for agentic prompt injection: three raw/undefended agents (GPT-5.4, GLM-5.1, DeepSeek-V4-Flash) and six defended-agent methods -- StruQ (prompt-front-end defense separating instructions from data via structured templates), ClawKeeper (an OpenClaw ecosystem plugin-gate defense, described as the closest existing OpenClaw-native defense), MELON (a counterfactual action gate), PromptShield-1B and PromptShield-8B (detector-gate models at two parameter scales), and CaMeL (a data-flow/capability-gate adaptation), evaluated on both the ClawTrojan positive split and a clean/negative split to jointly measure attack-blocking effectiveness and false-positive/utility cost.</t>
         </is>
       </c>
       <c r="F302" s="5" t="n"/>
@@ -12703,7 +12723,7 @@
       <c r="H302" s="5" t="n"/>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12733,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -12728,7 +12748,7 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>For a memory/context-poisoning benchmark, the threat model is non-adversarial-injection style but risk-modeling: an agent's persistent memory accumulates a mix of correct and misleading entries (constructed via three contamination patterns: overgeneralized experience, fragmented correct information, and consensus bias/false consensus) plus noisy/adversarially-embedded tool returns (indirect prompt injection channels or over-scoped information exposure in tool outputs), and a simulated biased user asymmetrically reinforces risky-but-effective behavior over safe-but-costly behavior across a 3-round interaction protocol, modeling deployment-time selection pressure that drives self-reinforcing behavioral drift ('memory misevolution') rather than a single-shot attacker-controlled exploit.</t>
+          <t>Formal multi-step 'trojan attack' threat model against local agentic harnesses (runtime environments wrapping an LLM with local tools, memories, and policies for multi-step tasks, e.g., OpenClaw-style personal automation agents and command-line coding agents). An attacker embeds a prompt injection within a file or tool output that looks harmless in isolation; the agent reads and stores this hidden instruction as ordinary workspace state (a 'planting' step), and it is only later re-triggered and executed when the agent performs an unrelated future task that reuses the poisoned content (e.g., copying text from a poisoned notes file into a shared release report). No individual step appears malicious on its own -- the attack is distributed across many turns and files, and the planted backdoor persists in the workspace even after the initiating session ends, meaning it can compromise future, unrelated agent runs. This is explicitly distinguished from single-turn/single-context prompt injection (as tested by AgentDojo, InjecAgent), which the paper shows produces near-zero attack success against current strong models and is therefore an inadequate threat model for local, stateful agentic harnesses.</t>
         </is>
       </c>
       <c r="F303" s="5" t="n"/>
@@ -12736,7 +12756,7 @@
       <c r="H303" s="5" t="n"/>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12746,7 +12766,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -12761,7 +12781,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>No explicit 'Limitations' section is present in the paper. The closest analog is the Conclusion, which frames residual open problems rather than caveats: results 'show that contaminated memory can induce unsafe behavior, while biased user feedback further amplifies this effect over time'; prompt-level safety instructions 'offer limited protection, whereas active memory correction is more effective'; and similar trends hold under A-MEM, 'suggesting that these risks are not limited to our simplified update protocol' -- implicitly acknowledging the base protocol is simplified. The paper also separately notes (Section 4.3) that F1 detection scores for identifying misleading memories decline as rounds increase even under +ModTool, indicating 'robust detection under memory updates remains an open challenge.'</t>
+          <t>Explicit 'Limitations' section covering four points: (1) benchmark scope -- ClawTrojan remains a synthetic, sandbox-local benchmark whose 339 positive samples emphasize persistent local state, workspace artifacts, memory, and mocked tool returns, so results should be read as evidence for this specific threat model rather than a complete estimate of real-world agent misuse; (2) clean-task coverage -- the clean split (23 negative/borderline samples, 92 clean steps) is sufficient to expose major overblocking behavior but does not cover the full variety of benign long-horizon work, so production deployments should add domain-specific clean tasks and tune review policies rather than rely on the paper's fixed false-positive rate; (3) harness dependence -- DASGuard assumes the harness can label content sources, observe writes or external-action attempts, and sanitize durable control-bearing artifacts, hooks that are available in the OpenClaw-style sandbox but that agents with opaque memory, closed tool routing, or weak filesystem provenance may require additional instrumentation to support; (4) adaptive attacks -- an attacker aware of DASGuard's defense mechanism may try to hide control content in highly domain-specific prose, spread it across many artifacts, or imitate trusted workspace conventions to evade source-label and semantic-matching checks; the paper's ablations suggest these mechanisms are important but does not claim robustness against such adaptive, defense-aware attackers.</t>
         </is>
       </c>
       <c r="F304" s="5" t="n"/>
@@ -12769,7 +12789,7 @@
       <c r="H304" s="5" t="n"/>
       <c r="I304" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12799,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -12794,7 +12814,7 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>MemEvoBench is presented as the first benchmark specifically targeting 'memory misevolution' -- gradual, self-reinforcing behavioral drift in LLM agents caused by repeated exposure to misleading information accumulated in persistent memory, distinct from prior static memory-hallucination or one-shot poisoning benchmarks. It combines two evaluation tracks: QA-style misleading memory injection (108 queries across 7 domains/36 risk types, with memory pools mixing correct and subtly misleading entries typed as knowledge snippets, conversation history, personal notes, or forum posts) and workflow-style noisy tool returns (83 cases across 20 AgentSafetyBench-derived environments/8 risk categories, targeting procedural rather than declarative memory contamination). Both tracks use a 3-round evaluation protocol in which the agent's own prior responses are appended back into its retrievable memory pool, optionally combined with LLM-simulated biased user feedback that rewards risky shortcuts and penalizes cautious responses, to measure self-reinforcing degradation over time via Attack Success Rate (judged by GPT-5.2 with 96.2% agreement against 50 human-labeled validation responses). The paper's main defense contribution, +ModTool, equips agents with an explicit correct_memory tool (and web_search for QA-Style) enabling agents to actively verify and revise misleading memory entries before responding, framed as more effective than static prompt-based safety instructions.</t>
+          <t>This paper identifies and formalizes a new threat class for LLM agentic harnesses -- the multi-step trojan/backdoor attack, in which an attacker plants a hidden instruction in one workspace artifact (a file, note, or tool output) that is only executed much later when an unrelated future task causes the agent to read and act on that planted content, meaning no single step in the attack chain looks malicious in isolation. To study this, the authors build ClawTrojan, a benchmark of diverse multi-step attack chains in an OpenClaw-style simulated local agentic workspace, annotated not just with final attack outcomes but with the full planting-and-triggering chain, evaluated via a multi-dimensional LLM-as-judge protocol (using GPT-5.4) that labels each step compromised, partial, safe, or invalid, and reports step ASR, full-chain ASR (requiring every malicious step in a sample to succeed), and average chain penetration. Using this benchmark, the authors show current strong base agents (GPT-5.4, GLM-5.1, DeepSeek-V4-Flash) and six existing defense methods spanning prompt-formatting, detection, and action-gating families are all substantially vulnerable, because these defenses inspect the current prompt or immediate action in isolation and fail to trace whether previously-ingested untrusted content has become persistent, policy-like control content in the workspace. The paper's second contribution is DASGuard, a Detect-Attribute-Sanitize defense that scans control-like text in sensitive local files, traces its provenance (origin/source attribution) across the full multi-step chain, and removes or sanitizes control content that does not originate from a trusted source, committing either a blocked operation, a sanitized shadow copy, or the original operation depending on which findings are flagged -- shifting the defense question from 'is this action safe right now?' to 'has untrusted content become part of the harness's persistent control state?'. DASGuard combines this cross-step provenance tracking with runtime attack blocking and sanitized commits back to the workspace, substantially outperforming all evaluated baselines on both attack-success reduction and clean-task utility preservation.</t>
         </is>
       </c>
       <c r="F305" s="5" t="n"/>
@@ -12802,7 +12822,7 @@
       <c r="H305" s="5" t="n"/>
       <c r="I305" s="5" t="inlineStr">
         <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -12822,7 +12842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12901,7 +12921,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2: Fair Credit Assignment for Long-Horizon Memory-Augmented LLM Agents</t>
+          <t>ASIDE: Architectural Separation of Instructions and Data in Language Models</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -12911,17 +12931,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Memory-R2 (LoGo-GRPO training) with shared-parameter fact extractor / memory manager</t>
+          <t>ASIDE (Architecturally Separated Instruction-Data Embeddings)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -12930,7 +12950,7 @@
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2b570db92dc6c6202e7de5b9834ba87bf701400a</t>
+          <t>51941fb4d679b102a50b18f1c1a6f70b6b929f59</t>
         </is>
       </c>
     </row>
@@ -12940,7 +12960,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>From Memory to Skills: Evidence-Grounded Co-Evolution Governance for Long-Horizon LLM Agents</t>
+          <t>Language Models Need Sleep: Learning to Self-Modify and Consolidate Memories</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -12950,7 +12970,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>MSCE (Memory-Skill Co-Evolution)</t>
+          <t>Sleep paradigm (Memory Consolidation + Dreaming)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -12960,7 +12980,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -12969,7 +12989,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>19291a8feb3169f43b0a295f876390b50f33942d</t>
+          <t>347650ce5f3201f54e13f193e2b614b6a21dec1c</t>
         </is>
       </c>
     </row>
@@ -12979,17 +12999,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Activation-aware Probe-Query: Effective Key-Value Retrieval for Long-Context LLMs Inference</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ActQKV (Activation-aware Probe-Query)</t>
+          <t>superposition of contextual information and parametric memory (mechanistic explanation of knowledge conflict)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -12999,7 +13019,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -13008,7 +13028,7 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>b345933a16c48404a38f8c1dc2c9ea03968dc0e7</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13038,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Security-Aware Retrieval-Augmented Generation System for Post-Quantum Cryptography Intelligence</t>
+          <t>Taming Knowledge Conflicts in Language Models</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -13028,17 +13048,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: security-aware RAG framework (evidence-based abstention + prompt-injection defense + multi-source agreement verification + trust-weighted retrieval)</t>
+          <t>JUICE (Just Run Twice)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -13047,7 +13067,7 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>96501f13d4c7a2da1228220c5723098e54f63a7c</t>
+          <t>b7ba9df4eb239708cf48f25be87b5bceeca010e3</t>
         </is>
       </c>
     </row>
@@ -13057,7 +13077,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>A Multi-Agent Framework for Step-Level Tool-Call Safety Evaluation in Industrial Control Systems</t>
+          <t>Evaluating Prompt Injection Defenses for Educational LLM Tutors: Security-Usability-Latency Trade-offs</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -13067,17 +13087,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: step-level fine-tuned industrial tool-call guardrail</t>
+          <t>UNNAMED: domain-specific multi-layer safeguard pipeline (pattern filters + structural validation + contextual sandboxing + session-level behavioral checks)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>resource-abuse</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -13086,7 +13106,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>1ee66ccebe2e1c1d8f3f3ec74c957ea91dcd2e98</t>
+          <t>0459c150849163cd801520a87394cc29003a5726</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13116,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Agent Security Meets Regulatory Reality -- A Practitioner Systematization of Autonomous-Agent Threats and Controls in Regulated Financial Systems</t>
+          <t>PlugMem: A Task-Agnostic Plugin Memory Module for LLM Agents</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -13106,17 +13126,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Pattern D: Inference-boundary redaction proxy (PII extraction/tokenization before model inference)</t>
+          <t>PlugMem (knowledge-centric memory graph)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -13125,7 +13145,7 @@
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>26768533d0eef5c2f7dadf915f70a45d397a4040</t>
+          <t>6ae3fb18300289acc53af5535508500992aa185c</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13155,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt: A New Approach to Prevent Prompt Injection Attacks Against LLM-Integrated Applications</t>
+          <t>Improving Coherence and Persistence in Agentic AI for System Optimization</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -13145,17 +13165,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Signed-Prompt</t>
+          <t>Engram (Archive + Research Digest)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -13164,7 +13184,7 @@
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>2742c3d77c4aa6d023b7dfc77984ad10e6aae274</t>
+          <t>d95cb62f6b46d3c6b7b0708cc616d97d245ba980</t>
         </is>
       </c>
     </row>
@@ -13174,27 +13194,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent: A Conversational Agent for Population Health Management</t>
+          <t>Overcoming the Retrieval Barrier: Indirect Prompt Injection in the Wild for LLM Systems</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ClinQueryAgent (Retrieval Agent sub-agent delegation)</t>
+          <t>UNNAMED: retrieval-aware IPI (trigger-fragment decomposition attack)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -13203,7 +13223,7 @@
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>1447859940005bfcdc2156673cf7f1bab455a0cf</t>
+          <t>81eb760ebbe224ae52cd7aea8f7f2865e4134908</t>
         </is>
       </c>
     </row>
@@ -13213,22 +13233,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow Attack</t>
+          <t>AIR (Augmented Intermediate Representations)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -13242,7 +13262,7 @@
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13272,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Prompt Overflow: What the Guardrail Inspects Is Not What the Model Infers</t>
+          <t>Prompt Injection Mitigation with Agentic AI, Nested Learning, and AI Sustainability via Semantic Caching</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -13262,12 +13282,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Contiguity-gate defense (for guardrail sliding-window aggregation)</t>
+          <t>TIVS-O agentic defense pipeline (Front-End Agent + Guard-Sanitizer + Policy Enforcer with semantic caching)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -13281,7 +13301,7 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>885424bbfda807e19d566c2e281a7aad31fb75d0</t>
+          <t>f759d9e8f124b49d74005ed5d36c2202bddd0dd7</t>
         </is>
       </c>
     </row>
@@ -13291,7 +13311,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Securing the Boundary: Trust Context Separation in Privileged AI Agent Systems</t>
+          <t>SecAlign: Defending Against Prompt Injection with Preference Optimization</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -13301,7 +13321,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: Trust Context Separation for privileged AI agent systems</t>
+          <t>SecAlign (preference optimization)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -13320,7 +13340,7 @@
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>dd42a440316cbae44b0ff68fe79914b07799a8ec</t>
+          <t>3e1d812a1ef4b02b7d60020cc8aaa596d28373da</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13350,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Stronger Enforcement of Instruction Hierarchy via Augmented Intermediate Representations</t>
+          <t>Owner-Harm: A Missing Threat Model for AI Agent Safety</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -13340,7 +13360,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AIR (Augmented Intermediate Representations)</t>
+          <t>UNNAMED: deterministic post-audit verifier layer added to a compositional safety system</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -13359,7 +13379,7 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>b0794049c22fb3d868a907131d0e8c0a6511025e</t>
+          <t>959f9a894d4eef23ee23895116206875151bb1fc</t>
         </is>
       </c>
     </row>
@@ -13369,17 +13389,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>A Trace-Based Assurance Framework for Agentic AI Orchestration: Contracts, Testing, and Governance</t>
+          <t>ChatInject: Abusing Chat Templates for Prompt Injection in LLM Agents</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MAT-based Assurance Framework (Message-Action Traces + governance layer: capability limits + action mediation)</t>
+          <t>ChatInject</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -13398,7 +13418,7 @@
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>e7eee295a7aba7ce0aef3b83a1b964e6bd10169d</t>
+          <t>09377c53e8bff67f1d8f1d778e529736a878f338</t>
         </is>
       </c>
     </row>
@@ -13408,22 +13428,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Defending Language Models Against Image-Based Prompt Attacks via User-Provided Specifications</t>
+          <t>Prompt Injection Attack to Tool Selection in LLM Agents</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>SPML-IR specification-based image defense (two-stage input validation + prompt injection detection)</t>
+          <t>ToolHijacker</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>cross-modal</t>
+          <t>tool-metadata</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -13437,7 +13457,7 @@
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>b7e425c93a0bfe017098cedecc43760a6f9ef5e8</t>
+          <t>eb6cbd2b06a980d8fabc1d7615575498385b35c8</t>
         </is>
       </c>
     </row>
@@ -13447,27 +13467,27 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf: Unifying Task Execution and Self-Reconfiguration via Tool-Driven Emergent Adaptation</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ToolSelf</t>
+          <t>ClawTrojan multi-step trojan/backdoor attack paradigm</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>persistence-backdoor</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -13476,7 +13496,7 @@
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2602.07883</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13506,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ADEMA: A Knowledge-State Orchestration Architecture for Long-Horizon Knowledge Synthesis with LLMAgents</t>
+          <t>From Prompt Injection to Persistent Control: Defending Agentic Harness Against Trojan Backdoors</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -13496,17 +13516,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ADEMA (checkpoint-resumable persistence + segment-level memory condensation + epistemic bookkeeping)</t>
+          <t>DASGuard</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>persistence-backdoor</t>
         </is>
       </c>
       <c r="G17" s="5" t="n"/>
@@ -13515,97 +13535,19 @@
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>79c76dd0ec900923e3da16162882d2e5fdca5010</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>attack / failure mechanism</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>memory misevolution</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>silent-corruption</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>MemEvoBench: Benchmarking Memory MisEvolution in LLM Agents</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>defense / fix</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>+ModTool (memory correction tool for MemEvoBench)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>silent-corruption</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>e7fed24b1353cf82d465d68dbda87c2b7243c60a</t>
+          <t>ce9d30735c0c27de65e68b228d77381d77f2a28b</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="G2:G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
   </dataValidations>
